--- a/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
+++ b/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
@@ -5426,22 +5426,19 @@
     <x:t>Builds custom advanced manufacturing systems with a focus on high-speed assembly, test, and inspection of automotive electronics components</x:t>
   </x:si>
   <x:si>
-    <x:t>They are a global leader in research, development, and production of automotive power, data, and display technologies, indicating in-house engineering and manufacturing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states expertise in design, manufacturing, and testing of electronic products, indicating a need for test and measurement equipment.</x:t>
+    <x:t>Manufactures automotive wire harnesses, sensors, and electronic modules; likely has in-house R&amp;D and test engineering to validate designs and ensure quality.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Company lists in-house design, manufacturing, and testing capabilities, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Request timed out after 15s</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: HTTP 403 Forbidden</x:t>
   </x:si>
   <x:si>
-    <x:t>The company manufactures metal foils for shielding and thermal management, which are electronics-adjacent, but there is no evidence of in-house electronic hardware engineering, testing, or repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform post-production testing and quality checks on electronic automotive sensors, which likely requires test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Regitar is a major manufacturer of automotive electronic components, indicating in-house engineering, R&amp;D, and manufacturing processes that require test and measurement equipment.</x:t>
+    <x:t>Insufficient website content to determine if they have in-house electronics test or engineering functions.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception.</x:t>
@@ -5450,481 +5447,484 @@
     <x:t>Scrape failed: HTTP 301 Moved Permanently</x:t>
   </x:si>
   <x:si>
-    <x:t>The company emphasizes innovation, design, and manufacturing of custom LED lighting and smart systems, indicating in-house engineering and R&amp;D that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in the repair and refurbishment of automotive electronic control units and instrument clusters, which requires in-house diagnostics and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a manufacturer of high-performance mobile electronics, implying in-house design, development, and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company primarily provides finished electronic products and brands, with no visible evidence of in-house engineering, R&amp;D, or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house repair, calibration, and diagnostics of electronic instrument clusters, speedometers, and other vehicle electronic modules.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>While the founder historically manufactured electronics, the current business primarily focuses on installation and retail of finished automotive electronic products, with no clear evidence of in-house engineering or complex diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company sells finished electronic products for vehicles and mentions ADAS safety systems, but there is no clear evidence of in-house engineering, R&amp;D, or repair requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company designs, develops, and manufactures automotive wiring harnesses and electronic components, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company manufactures and engineers automotive electronic components, including sensors and parts for hybrid/electric vehicles, and has engineering and manufacturing facilities.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture an electronic throttle response controller that intercepts and alters vehicle signals, implying in-house engineering and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is a developer and manufacturer of automotive and electronic products, with explicit mentions of innovative engineering and manufacturing operations.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs diagnostics, programming, coding, and calibration of vehicle electronic modules, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and engineer vehicle electronics and components, indicating in-house R&amp;D and manufacturing that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They install and maintain emergency vehicle electronics, but there is no clear evidence of in-house engineering, R&amp;D, or component-level electronic repair requiring advanced test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform repair, remanufacturing, calibration, testing, and validation of automotive electronics, indicating a need for test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they are a manufacturer developing high-quality automotive electronic components, which implies in-house engineering and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and produce stamped and plated electrical connectors, implying in-house engineering and manufacturing that requires testing and measurement of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house R&amp;D and engineering for advanced automotive electronic systems like autonomous driving and infotainment, indicating a need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an automotive parts remanufacturer with stated "ENGINEERING &amp; INNOVATION" and publish content on "Calibration" and "Automotive Electronics Fundamentals," indicating in-house testing and diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They sell and equip vehicles with finished electronic accessories, but there is no clear evidence of in-house engineering, R&amp;D, or repair of the electronic hardware itself.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house design, engineering, prototyping, and rigorous testing of wiring harnesses, indicating a need for electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company sells plug-and-play remote start kits, which are finished electronic products, with no clear evidence of in-house engineering, R&amp;D, or repair of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they engineer and manufacture automotive electronics and OEM integration components, indicating in-house R&amp;D and production.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Stoneridge designs and manufactures highly engineered electrical and electronic systems, including new ECU technology and advanced vision systems, indicating in-house engineering and R&amp;D.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform thorough testing, reprogramming, flashing, and tuning of electronic control modules, indicating in-house diagnostic and engineering work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EEPod develops custom ECUs and provides ECU test, simulation, and reprogramming stations for automotive engineers, indicating in-house electronic hardware development and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Marimba Auto manufactures precision-engineered mechanical and fluid-handling automotive components, but there is no explicit mention of in-house electronic hardware design, testing, or repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs engine calibration and tuning, develops 'FutureFlex Technology' and 'electronics,' and conducts dyno pulls, indicating in-house testing and development of electronic hardware and software.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AER Technologies specializes in remanufacturing and repair of automotive electronic components, indicating a need for in-house diagnostics, testing, and engineering expertise.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in vehicle electronics installation and sales, but there is no clear evidence of in-house engineering, R&amp;D, or component-level repair work that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Request timed out after 15s</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NAL develops innovative lighting technologies and hires engineers and technicians for manufacturing and machinery repair, indicating a need for electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>As a Tier One automotive supplier manufacturing components and systems, they likely have in-house engineering and R&amp;D for electronic controls and systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company has multiple Tech Centers specializing in the development and testing of LED lighting solutions, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs electronics manufacturing, PCB assembly, and engineering &amp; DFM for electronic hardware from prototype to production.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop advanced electronic systems like Vision &amp; Radar Systems, Advanced Sensors &amp; Mechatronics, and Occupant Monitoring Systems, indicating in-house engineering and R&amp;D.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They have R&amp;D and manufacturing facilities that develop advanced control systems, sensor tech, and electronics, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is driven by engineering, has vertically integrated electronic manufacturing capabilities, and focuses on new product introductions and custom solutions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house automotive engineering, design, and development of OBD tuning solutions, engine, and turbocharger systems, and influence vehicle electronics and hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They operate as a satellite design and development center and are involved in manufacturing electrical and automotive components, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a global leader in engineering and manufacturing automotive systems and mechatronics, and have a Technical Center, indicating in-house electronic hardware development and testing.</x:t>
+    <x:t>Manufacturer of electronic automotive components (voltage regulators, rectifiers), but no direct evidence of in-house test engineering, R&amp;D, or calibration lab visible in the scraped content.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Repairs and remanufactures automotive electronic modules, which likely requires in-house testing and diagnostic equipment like oscilloscopes and power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house design and manufacturing of electronic LED lighting and smart vehicle systems implies use of test equipment for development and quality assurance.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No clear evidence of in-house electronic testing or engineering; they process metal foils for thermal management applications.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a retail installer of automotive electronics with no evidence of in-house engineering or test work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>provides in-house electronic repair and calibration services requiring test equipment like oscilloscopes and signal generators</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Website markets automotive electronics but provides no concrete evidence of in-house engineering, R&amp;D, or test lab.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design, develop, and manufacture automotive electronic components and wiring harnesses, implying in-house R&amp;D and test functions that use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consumer brand for car audio, no evidence of in-house engineering or test; may only resell/install finished products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures automotive electronic components (sensors, ignition, fuel injection) and has an Engineered Solutions division, indicating in-house engineering and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures automotive wiring and components but no clear evidence of in-house electronic test or R&amp;D lab.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No indication of in-house engineering or test; seems to sell and install finished camera products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides mobile vehicle electronics diagnostics and calibration services, uses specialized automotive tools, but unclear need for general-purpose test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They install and maintain emergency vehicle electronics but show no clear signs of on-site engineering or use of test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house repair, remanufacturing, and calibration of automotive electronics, indicating they likely use test equipment like oscilloscopes and meters.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They remanufacture electronic automotive components (e.g., engine control modules, throttle bodies) and mention calibration and repair, indicating in-house electronics testing and diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures its own electronic throttle controllers, implying in-house R&amp;D and likely use of test equipment for development and compliance testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures vehicle electronic components, implying in-house engineering and testing labs that use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped website content is garbled and unreadable, preventing any determination of in-house engineering or test equipment usage.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufacturer of electronic performance components, likely has in-house R&amp;D needing test gear.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTCA R&amp;D center and multiple manufacturing plants show in-house engineering and testing of electronic automotive systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Develops and produces stamped connectors; unclear if they perform in-house electronic testing requiring oscilloscopes or signal generators.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures electronic control units and ADAS, indicating in-house R&amp;D and test.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house engineering and rigorous testing (PPAP, FMEA) on wire harnesses indicates staff who plausibly use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sells aftermarket automotive electronics but no evidence of in-house engineering, R&amp;D, or test/repair functions visible in website content.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and tests custom ECUs and diagnostic hardware, indicating in-house electronics engineering lab work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sells programmed engine modules but shows no evidence of in-house hardware engineering or general test equipment use; likely relies on automotive-specific programmers.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Full-cycle electronics remanufacturing of automotive electronics implies in-house testing and diagnostics that require test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures only mechanical automotive components, no evidence of in-house electronics testing, calibration, or repair work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions 'deep engineering expertise' and 'Engineering Products' but no explicit in-house test/measurement or calibration functions visible in the scraped text.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Company engineers and manufactures automotive electronics, indicating likely use of test equipment for R&amp;D and quality control.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Automotive components manufacturer with no clear indication of in-house electronic R&amp;D or testing functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a tier-one automotive lighting supplier with in-house engineering and manufacturing, indicating they likely use electronic test equipment for R&amp;D and production testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Plymouth, MI location 'specializes in the development and testing' of LED lighting solutions, indicating in-house R&amp;D that likely uses test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Develops advanced sensors, radar systems, and electronic safety components, indicating in-house R&amp;D and test engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Automotive tuning shop; no evidence of in-house electronics engineering or test that would require oscilloscopes or similar gear.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Page body was empty after parsing</x:t>
   </x:si>
   <x:si>
-    <x:t>They have product development and engineering centers, and manufacture electronic-heavy automotive lighting systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They have an extensive team of engineers and technicians who perform rigorous testing and development of new electrical products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dare Auto designs and manufactures electronics, intelligent controls, and BLDC motors, indicating in-house engineering and development work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They remanufacture high-precision automotive components like diesel injection systems, which often contain electronic controls, but the text does not explicitly mention in-house electronic testing or repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The scraped website content was garbled and unreadable, preventing a determination.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ampere EV performs in-house design, engineering, testing, and calibration of electronic powertrains, VCUs, and battery modules.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in conceiving and engineering proprietary electronic sensor and control systems, indicating in-house R&amp;D and design work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company specializes in repair and remanufacturing of electronic instrument clusters, indicating in-house diagnostic and testing work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a master distributor and upfitter of public safety vehicle equipment, focusing on sales, service, and installation of finished products, with no visible in-house electronic engineering or component-level repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide technical resources and firmware solutions for vehicle electronics installation, but it's unclear if they perform in-house hardware engineering or deep diagnostics requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states it performs "Automotive Lighting Design and Manufacturing" and produces "modular electronic assemblies," indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and manufacture automotive semiconductors, engine control units, and diagnostic tools, which requires extensive in-house engineering and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they have "expert in-house engineers" committed to innovation and seamless integration of automotive technology, indicating R&amp;D and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>eSync Alliance is a trade association focused on software and standardization for automotive OTA, not directly involved in hardware engineering, testing, or repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and produce plastic components with integrated control units and power electronics, indicating in-house engineering and testing of electronic hardware.</x:t>
+    <x:t>Mentions R&amp;D, advanced electronics, sensor tech, and design of electromagnetic valves, indicating in-house engineering likely using test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house PCB assembly, EMS, and ODM with engineering support, likely using test equipment for quality control.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions product development and engineering centers, likely involving design and testing of automotive electronic components.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Installs and resells finished automotive electronics; no evidence of in-house engineering, calibration, or repair work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an engineering and manufacturing company with a technical center, likely having engineers who test and develop automotive systems and machine tools, requiring electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>insufficient scraped content to determine if they have in-house engineering/test functions</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures electronic controls, motors, and TPMS/EHPS/PEPS systems, indicating in-house R&amp;D and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Company has in-house engineering and testing lab for automotive electronic components, performing electrical testing per SAE standards.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house design, engineering and testing of EV powertrain systems including motor controllers, battery management, and VCU programming, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vertically integrated electronic manufacturer with in-house engineering and ISO 9001-2015 certification suggests need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house development and engineering of OBD tuning software and hardware, plus design and manufacturing of performance parts, suggest need for electronic test and measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They engineer proprietary sensor/control systems, implying in-house R&amp;D and testing that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a vehicle upfitter and distributor of finished public safety equipment (lights, sirens, barriers); no evidence of in-house engineering, R&amp;D, or test functions that would require T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They remanufacture and repair electronic instrument clusters, implying in-house electronics diagnostics and repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Technical resource for vehicle wiring installations and module configurations, but no evidence of in-house engineering, R&amp;D, or repair work requiring test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures modular electronic assemblies and automotive lighting products, very likely requiring in-house test, validation, or quality control with electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They list 'Testing' as a capability and manufacture electronic components and wire harnesses, typically requiring in-house electronic test equipment.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: HTTP 406 Not Acceptable</x:t>
   </x:si>
   <x:si>
-    <x:t>They are a full-service manufacturer with explicit in-house engineering and testing capabilities for electronic and electromechanical components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company primarily distributes automotive chemicals and parts, with no clear indication of in-house electronic hardware testing, diagnostics, or repair functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company sells automotive accessories and inflation products, which may involve some mechanical or pneumatic testing, but there is no clear evidence of electronic hardware engineering or testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs advanced testing, precision control with real-time current monitoring and PWM, and engineering implementation, indicating in-house electronic hardware design and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company develops and markets automotive tools and 'Test Products' but there is no evidence of in-house electronic engineering, R&amp;D, or repair work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a designer and manufacturer of LED lighting products, indicating in-house engineering and manufacturing that would require electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a wholesale distributor of automotive parts with no visible in-house engineering or test function.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Their platform optimizes electronics manufacturing, quality control, and failure analysis, implying their engineers would use test &amp; measurement equipment for development and validation.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, engineer, and prototype mechatronics products for the automotive industry, indicating a need for electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company focuses on metal wool and fiber technology with R&amp;D, but there is no explicit mention of electronic hardware or related testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they create new technologies and solutions and develop next-generation automotive accessories, indicating in-house engineering and R&amp;D for electronic products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They have an R&amp;D team for automotive technology, but their primary products are chemical additives, making it unclear if they work with electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company primarily sells automotive chemicals, but their non-profit trains young adults in auto repair, which might involve some electronic diagnostics, though not explicitly stated.</x:t>
+    <x:t>Remanufactures mechanical fuel system components; no clear evidence of in-house electronic test or diagnostics that would require general-purpose T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides a software platform for electronics manufacturing inspection and test data, but no clear evidence of in-house hardware engineering, repair, or calibration work requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions integrated modules for control units and power electronics, but website text focuses on plastic molding and assembly with no clear evidence of in-house electronic testing or engineering labs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and tests power control modules, with advanced testing indicating in-house engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content is insufficient to determine if they have in-house engineering or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufacturer with R&amp;D, but no evidence of electronic testing or equipment need.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Trade association focused on software OTA standards, no evidence of in-house electronic hardware testing, engineering, or manufacturing that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures automotive semiconductors and ECUs, indicating in-house design and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mechatronics products imply potential electronic testing, but no clear evidence of using T&amp;M equipment like oscilloscopes.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures automotive LED lighting, suggesting possible in-house electronics engineering and testing, but no explicit mention of test equipment or calibration labs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content insufficient to determine if they perform in-house electronic test/engineering work.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (omron.com:443)</x:t>
   </x:si>
   <x:si>
-    <x:t>They sell automotive components and mention engine diagnostics for repair shops, but there's no clear evidence of in-house electronic hardware engineering, R&amp;D, or repair work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The scraped content is too minimal to determine if they perform in-house electronic engineering, diagnostics, or repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop, engineer, and manufacture their own innovative LED emergency vehicle lighting products in-house, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They engineer, design, and manufacture their electronic transmission controllers and custom harnesses in-house.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide engineering and prototyping services to transform product ideas into testable designs, indicating a need for test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer custom design and manufacturing support for their automotive equipment, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They mention '1-Power Engineering' for design innovation and prototype optimization, and 'Industrial robot Manufacturing,' which could involve electronic testing, but their core business is structural automotive components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They install and program vehicle electronics, but there is no clear evidence of in-house electronic hardware engineering, R&amp;D, or deep-level diagnostics requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states it performs design, development, and manufacturing of electronic solutions, and has R&amp;D innovation, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company engages in innovation, design, and manufacturing of electrical components and systems for commercial vehicles, indicating a need for in-house testing and measurement.</x:t>
+    <x:t>No evidence of in-house test/engineering; purely a wholesale warehouse distributor of auto parts, chemicals, and oils.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Automotive parts supplier with no visible electronic engineering, R&amp;D, or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineering and prototyping lab that develops products from concept to testing, implying in-house use of test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content shows automotive chemical products, no indication of in-house electronics engineering or repair that would need test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tier 1 automotive supplier with manufacturing and custom tool development, but no mention of in-house electronic test or diagnostics; unclear if they have engineers using T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures electronic transmission controllers in-house, with custom engineering and tuning, implying use of test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No evidence of in-house electronic engineering, R&amp;D, or repair; company focuses on automotive mechanical tools and training.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (shinko.co.jp:443)</x:t>
   </x:si>
   <x:si>
-    <x:t>The company manufactures electronic brake and safety systems and other electronic components for the automotive industry, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is an electronic components manufacturer's representative, which implies they sell components rather than perform in-house engineering or testing that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTM Technologies manufactures PCBs and RF/microelectronic assemblies, operates manufacturing facilities, and achieves product qualifications like AEC-Q200, all of which require in-house engineering and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a global multi-industry manufacturing leader that designs and produces complex solutions like mechatronics, implying in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides Electronics Manufacturing Services (EMS), Contract Manufacturing, and Engineering &amp; Design Services, indicating in-house engineering and manufacturing that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides electronic circuit design, assembly, manufacturing, and prototyping services, indicating a clear need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer custom test leads and sell 'LIKE NEW USED' diagnostic equipment, suggesting in-house engineering, testing, or refurbishment capabilities.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides custom electronic hardware design, prototyping, and design verification services, which require in-house engineering and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The website text indicates "Investing in Innovation" and "Bringing Innovative Technologies to Market" for OEMs, suggesting in-house R&amp;D and engineering of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide coating services for PCBAs and establish manufacturing processes, but it's unclear if their quality control or prototyping involves electronic test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a distributor of electronic components and supply chain solutions, and while they list 'Test &amp; Measurement' as a product category, there is no evidence of in-house engineering, R&amp;D, or repair work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and build precision connectors for electronic applications like ECMs and EV charging, implying in-house engineering and testing of electronic components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states they perform electronic circuit troubleshooting, repair, and product testing as part of their services.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is an Electronic Manufacturing Service (EMS) provider performing PCB assembly, box-builds, and prototype work, indicating in-house testing and engineering needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>As a printed circuit board manufacturer with detailed technical capabilities and quality processes, they clearly have in-house engineering and testing needs for electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house R&amp;D, engineering, manufacturing, and repairs of electronic control systems, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a contract electronics manufacturer performing in-circuit testing, functional testing, burn-in testing, and using AOI and 3D X-ray inspection on electronic assemblies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They supply precision-engineered mechanical components for EV and consumer electronics, but it's unclear if their in-house engineering team performs electronic hardware testing or diagnostics.</x:t>
+    <x:t>In-house design and manufacturing of advanced electrical connectors and harness systems strongly implies engineering teams that need to validate, test, and troubleshoot electronic hardware with instruments like oscilloscopes and meters.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resells automotive diagnostic tools including lab scopes, but no clear evidence of in-house engineering, calibration, or repair work; appears primarily a reseller.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions custom design, but unclear if they do in-house electronic testing versus just assembling or reselling automotive equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Develops, engineers, and manufactures its own LED emergency lighting products, implying an internal R&amp;D and test function that likely uses electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They install aftermarket vehicle electronics but no evidence of in-house engineering or test equipment use; primarily an installation service.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design, develop, and manufacture electronic solutions with in-house R&amp;D, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers PCBA and full box-build with engineering services, indicating in-house test and measurement needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides Engineering &amp; Design Services and manufactures PCBA and electronic components, implying in-house testing and diagnostics using test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer custom electronic hardware design, prototyping, and production support with 20 years of engineering experience, indicating in-house engineers who use test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content was insufficient to make a determination</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures hydraulic brake calipers and components; no indication of electronic testing or engineering lab on site.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures PCBs, RF components, and mission systems, implying in-house engineering and testing requiring oscilloscopes, signal generators, etc.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform functional testing, in-circuit testing, and have AOI and 3D X-ray inspection, indicating in-house engineering/test work on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers electronic circuit troubleshooting, repair, design, and testing services, indicating in-house need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Distributor of electronic components; mentions test &amp; measurement products but no evidence of in-house engineering or test work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Curtis has in-house R&amp;D, engineering, and manufacturing of motor controllers and battery management systems, indicating they likely use test equipment like oscilloscopes and power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufacturer of automotive chemical additives; no indication of in-house electronics engineering, testing, or repair; likely no need for test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures mechatronic and actuator systems, implying potential in-house electronic engineering and testing, but scraped content lacks explicit mention of test labs or T&amp;M equipment usage.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures high-frequency ceramic components, indicating in-house R&amp;D and testing that likely uses RF test equipment like spectrum analyzers and network analyzers.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (hosiden.com:443)</x:t>
   </x:si>
   <x:si>
+    <x:t>Manufacturer's representative for electronic components, no evidence of in-house engineering, testing, or repair functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide PCB coating services, but no clear evidence of in-house electronic engineering or test functions that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>scraped content only shows generic marketing language, no mention of engineering, R&amp;D, or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions developing products from ground up and extensive testing tailored to application, indicating in-house engineering/R&amp;D that likely requires test equipment.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (foster-electric.com:443)</x:t>
   </x:si>
   <x:si>
-    <x:t>They develop all their products from the ground up and perform extensive in-house testing tailored to specific application requirements.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer powertrain calibration, embedded systems, and product development, which indicates a need for electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QMS is an Electronics Manufacturing Services (EMS) provider with in-house engineering, manufacturing, testing, and repair services.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a manufacturer sales representative providing technical sales and engineering support, but there is no clear evidence of in-house engineering, R&amp;D, or testing requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toshiba is a manufacturer and developer of semiconductors, power electronics, and other advanced electronic systems, indicating in-house engineering, R&amp;D, and manufacturing that require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cohu develops and supplies semiconductor test equipment and ATE platforms, indicating in-house engineering and R&amp;D that would utilize test &amp; measurement gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PalPilot provides integrated engineering and manufacturing solutions for PCBs and electronic components from prototype to production, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, engineer, and manufacture custom electronic motor and motion control systems, indicating a need for in-house testing and measurement.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nidec produces electronic components and lists "Inspection and measuring equipment" and "Processing / Inspection Equipment" among their products, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides contract manufacturing and engineering services, including design, prototyping, and R&amp;D for electronic components and assemblies, indicating in-house testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house design, prototyping, PCBA manufacturing, system assembly, testing, and repair of electronic products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sanmina provides design, engineering, manufacturing, test system development, and repair services for complex electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide engineering R&amp;D and design technical support services, suggesting in-house technical staff who may use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs rigorous performance testing, a wide range of tests to industry specifications, and analytical testing on their proprietary materials.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The website is a retail storefront for finished electronic products and does not show evidence of in-house engineering, R&amp;D, or testing functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ark Electronics provides design engineering, PCB design, and electronics manufacturing services, indicating in-house engineering and production that requires test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company offers electronic design, PCB layout, embedded firmware, R&amp;D, and electronic manufacturing, including through-hole and surface mount assembly, indicating a need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house electronic design, rapid prototyping, hardware calibration, troubleshooting, and EMI/EMC pre-screening, all requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides electronic design, assembly, and advanced test engineering services, indicating in-house testing and development needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an electronic components supplier with engineering staff and manage quality testing, but it's unclear if they perform in-house testing or primarily outsource it.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer engineering services including design, prototyping, and testing, along with manufacturing and quality control for complex electronic systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide electronics design, manufacturing, development, and reverse-engineering services, which inherently require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide Electronic Manufacturing Services including PCB assembly, prototype development, and expert engineering support, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture flexible and rigid-flex circuit boards, which requires in-house engineering and testing functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide additive manufacturing solutions for applications like power electronics, but there is no clear evidence of in-house electronic hardware testing or R&amp;D requiring test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corelis develops and provides embedded hardware test and development solutions, including JTAG boundary-scan software and hardware, indicating strong in-house engineering and testing functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides turnkey design and manufacturing services for electronic hardware, including in-house engineering, product development, and assembly.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a contract electronics manufacturer building PCBA, wire harnesses, and cable assemblies, which requires in-house testing and quality control.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KTTS is a manufacturer's representative and distributor, providing technical expertise and sales support for various electronic components, but there is no clear evidence of in-house electronic hardware engineering, R&amp;D, or testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company develops advanced nano coatings for PCBs, with in-house engineering and R&amp;D focused on signal integrity and thermal management in complex electronics, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CheckSum designs and engineers complex automated test systems for electronics manufacturing, indicating in-house R&amp;D and engineering teams that would use test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a global manufacturer of advanced electronic components with extensive R&amp;D, design, and manufacturing facilities, indicating a strong need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an "Engineering Driven Manufacturer" of custom electro-mechanical assemblies and wire harnesses for the electronics, medical, and analytical instrumentation industries, indicating a need for in-house testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and upgrade their own coating equipment and technologies, indicating in-house engineering and R&amp;D that would use test &amp; measurement gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lectronix performs in-house hardware engineering, product development, PCB assembly, and functional testing of electronic systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide advanced electronics manufacturing services, including prototyping, NPI, and engineering services, indicating in-house testing and validation needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BPM Microsystems designs and manufactures complex automated device programming systems, indicating in-house electronic engineering, R&amp;D, and manufacturing functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company specializes in automotive audio/visual electronics, which involves electronics, but the provided text only lists consumer goods and brands, with no explicit mention of in-house engineering, R&amp;D, or repair work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is a PCB manufacturer with in-house engineering, prototype development, DFM feedback, and production facilities, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Thomas Instrumentation offers in-house PCB design, hardware development, and electronics manufacturing services, employing PCB designers and hardware experts who would use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, develop, and manufacture flexible circuits and electronic materials, explicitly mentioning engineers and a Director of Innovation and Technology.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer electrical assembly services with extensive testing protocols and manufacture critical metal components for high-tech energy systems and battery packs, indicating a need for in-house electrical testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states 'Our engineers provide pragmatic solutions' and 'engineer intelligent control systems' for their electronic hardware products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer electronic design, PCB design, rapid prototyping, and thorough electronics testing services, indicating in-house engineering and test functions.</x:t>
+    <x:t>PCB manufacturer implies some in-house testing, but no explicit mention of test equipment, engineering, or R&amp;D functions that would need oscilloscopes, signal generators, etc.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMS company performing PCB assembly, likely has in-house test and debug engineers who use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture electronic components (sensors, LED lighting, power distribution) with in-house R&amp;D and labs, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Makes connectors for ECUs and sensors, but site emphasizes mechanical manufacturing (casting, stamping) without indication of electronic test or engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMS provider with in-house engineering, testing (DFT), PCB assembly, and repair depot, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cohu designs and manufactures semiconductor test equipment, indicating in-house R&amp;D and engineering teams that use test and measurement instruments for development and validation.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures custom motor and motion control systems, indicating in-house engineering and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures power semiconductors (Si, SiC, GaN), MOSFETs, and digital isolators, implying in-house R&amp;D and test labs requiring oscilloscopes, signal generators, and other T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides PCB design and manufacturing but no explicit mention of in-house test, calibration, or repair work on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Contract manufacturer offering PCBA, box build, testing, and repair services, indicating in-house use of test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufacturers' sales representative firm offering technical sales and engineering support, but no indication of in-house testing, repair, or R&amp;D labs that would use T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mechanical parts manufacturer with no visible in-house electronic engineering or test function requiring T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer in-house test engineering, design, and manufacturing services, clearly needing T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufacturer's rep providing engineering support, but no evidence of in-house test/measurement lab or hardware engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMS provider with in-house design engineering and high-volume PCBA manufacturing, implying test and quality control using T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They manufacture automotive electronic components like ECUs and sensors, have inspection/measuring equipment, and operate smart factories, indicating in-house R&amp;D and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Contract manufacturer of precision mechanical components, no evidence of in-house electronic engineering or test work that would require T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Electronics contract manufacturer with in-house assembly, testing to IPC standards, design, and reverse-engineering, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions 'Advanced Test Engineering' and performs PCBA-to-complete electronic modules manufacture, indicating in-house testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house PCB assembly and antenna design with engineering support, requiring test and measurement equipment for quality assurance.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house rigorous performance testing and analytical testing services for laminate materials likely require electronic test equipment for characterization.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a distributor of electronic components, not a manufacturer; no clear evidence of in-house engineering or testing labs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers turnkey manufacturing, design, and engineering services involving electronic hardware, indicating in-house test and measurement needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers in-house embedded hardware design, PCB layout, prototype testing, and hardware calibration, requiring oscilloscopes and other T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Develops boundary-scan test hardware and software, clearly has in-house engineering and testing functions that require test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Develops and applies nano coatings for electronics protection but no clear evidence of in-house electronic testing, R&amp;D, or engineering teams using T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consumer car audio sales site, no visible in-house engineering, repair, or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture vehicle safety electronics and subject them to rigorous testing, indicating an in-house engineering and test function that likely requires test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers in-house electronics manufacturing services including assembly, testing, engineering support, and depot repair, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Engineering services explicitly include testing and prototyping, indicating in-house use of test equipment for complex electronics manufacturing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mentions product development and engineering of LED lighting controls, suggesting possible in-house electronics design, but no explicit evidence of test equipment usage.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures components with in-house R&amp;D and testing, clearly employs engineers who need test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer's representative, and while they mention technical expertise and engineering solutions, there is no clear evidence of in-house test, calibration, or repair work that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture flexible circuits in-house for mission-critical applications, implying need for electrical testing equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs electronic hardware for 3D printers but no explicit evidence of in-house test/calibration work on electronics, only general manufacturing and services mentioned.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures automated programming systems, indicating in-house engineering and hardware testing requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house engineering, PCB assembly, system integration, and functional testing indicate active use of test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures their own automated test systems, implying in-house engineering and testing teams.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer in-house PCB design and electronics manufacturing services, indicating engineering and test functions that require test equipment.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: No connection could be made because the target machine actively refused it. (jebconet.com:443)</x:t>
   </x:si>
   <x:si>
-    <x:t>They provide remanufacturing and repair solutions for automotive and consumer electronics, which requires in-house diagnostics and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The scraped website content was insufficient to make a determination.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kelco Industries designs and manufactures custom electronic components like solenoids and relays, with in-house engineering and dedicated testing labs for product development and quality assurance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they are inventing and producing parts for next-generation space vehicles and developing innovative products in their electronics segment, indicating in-house engineering and R&amp;D.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They engineer, manufacture, and rigorously test custom electronic components and assemblies, including thermal shock, dielectric, and corona testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a sales representative for electronic components with no visible in-house engineering, R&amp;D, or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unigen provides OEM product design and manufacturing, including PCB assembly and test, and offers 'Test-as-a-Service', indicating a clear need for electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, build, and debug custom automated test and inspection systems for automotive electronics, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prototek provides advanced manufacturing for electronics and semiconductors, including assemblies and micro-components, implying in-house engineering and quality control that would use test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company designs and manufactures complex electronic radar/laser detectors, with detailed discussions of signal processing, radar bands, and ongoing firmware development, indicating in-house engineering and R&amp;D.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a leading provider of digital non-contact optical inspection systems, which implies in-house electronic hardware design, manufacturing, and testing.</x:t>
+    <x:t>Manufactures custom magnetics and electronic assemblies with in-house rigorous testing (thermal shock, dielectric, corona) and holds AS9100D certification, indicating need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Makes electro-mechanical assemblies and wire harnesses, but scraped text shows no explicit in-house engineering, test, or calibration functions that would clearly require oscilloscopes or signal generators.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers design, prototyping, and box-build integration services, indicating in-house engineering that likely uses test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture electronic controllers and displays, implying in-house engineering and test functions that require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sheldahl designs and manufactures flexible circuits and printed electronics, requiring in-house engineering and testing of electronic hardware, as evidenced by their R&amp;D collaboration, innovation videos, and custom solutions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides electronic manufacturing services with in-house test capabilities likely requiring oscilloscopes and power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They apply conformal coatings to electronics but no evidence of in-house electronic testing, repair, or R&amp;D that would require oscilloscopes or similar T&amp;M gear.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer contract manufacturing with electrical assembly and extensive testing protocols, likely requiring oscilloscopes and other test gear.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer electronics testing and design-for-test services, indicating in-house use of test equipment like oscilloscopes and signal generators.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and test custom electromagnetic components (coils, solenoids, relays) in-house, with dedicated testing labs, indicating a need for electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content only shows JavaScript requirement message, no meaningful company information available.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offers PCB assembly and test services, and designs OEM electronic products, indicating in-house engineering and test functions likely requiring oscilloscopes, signal generators, and power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer remanufacturing and repair services for automotive and consumer electronics, indicating in-house diagnostic and repair work requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufacturer sales rep firm providing technical sales and marketing, no evidence of in-house engineering or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and builds custom test and inspection systems for automotive electronics, implying in-house engineering likely using test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content only shows consumer goods categories, no evidence of in-house engineering or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides mechanical manufacturing services to electronics industry but no evidence of in-house electronic test or engineering functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sells optical inspection systems and does metal fabrication, but no clear evidence of in-house electronic test, repair, or R&amp;D using T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures magnetic components for automotive electronics, implying some R&amp;D and production testing, but scraped text lacks explicit mention of in-house test/measurement functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PCB manufacturer with engineering support and DFM feedback, but no clear evidence of in-house electronic testing or use of oscilloscopes/signal generators.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -7297,10 +7297,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M24" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N24" s="0" t="s">
-        <x:v>1805</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -7344,7 +7344,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N25" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1805</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -7388,7 +7388,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1811</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -7432,7 +7432,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -7473,10 +7473,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M28" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N28" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1808</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -7520,7 +7520,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -7564,7 +7564,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N30" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -7608,7 +7608,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N31" s="0" t="s">
-        <x:v>1808</x:v>
+        <x:v>1807</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -7652,7 +7652,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
-        <x:v>1810</x:v>
+        <x:v>1809</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -7696,7 +7696,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N33" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -7737,10 +7737,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M34" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>1811</x:v>
+        <x:v>1816</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -7784,7 +7784,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N35" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1814</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -7828,7 +7828,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
-        <x:v>1814</x:v>
+        <x:v>1812</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -7913,7 +7913,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
-        <x:v>1816</x:v>
+        <x:v>1815</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -8001,7 +8001,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1819</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -8045,7 +8045,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N41" s="0" t="s">
-        <x:v>1808</x:v>
+        <x:v>1807</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -8086,7 +8086,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1824</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -8127,10 +8127,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M43" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>1819</x:v>
+        <x:v>1818</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -8171,7 +8171,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M44" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
         <x:v>1820</x:v>
@@ -8218,7 +8218,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>1821</x:v>
+        <x:v>1825</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -8259,7 +8259,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>1822</x:v>
+        <x:v>1821</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -8303,7 +8303,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N47" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -8344,10 +8344,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M48" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>1825</x:v>
+        <x:v>1829</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -8388,7 +8388,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N49" s="0" t="s">
-        <x:v>1824</x:v>
+        <x:v>1827</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -8429,7 +8429,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N50" s="0" t="s">
-        <x:v>1823</x:v>
+        <x:v>1822</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -8473,7 +8473,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>1827</x:v>
+        <x:v>1823</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -8517,7 +8517,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>1826</x:v>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -8561,7 +8561,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N53" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -8605,7 +8605,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N54" s="0" t="s">
-        <x:v>1855</x:v>
+        <x:v>1826</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -8649,7 +8649,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N55" s="0" t="s">
-        <x:v>1828</x:v>
+        <x:v>1832</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -8687,10 +8687,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M56" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1837</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -8734,7 +8734,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N57" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -8778,7 +8778,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N58" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -8822,7 +8822,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N59" s="0" t="s">
-        <x:v>1831</x:v>
+        <x:v>1838</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -8866,7 +8866,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N60" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1831</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -8907,7 +8907,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N61" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -8945,10 +8945,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M62" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N62" s="0" t="s">
-        <x:v>1833</x:v>
+        <x:v>1834</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -8992,7 +8992,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N63" s="0" t="s">
-        <x:v>1832</x:v>
+        <x:v>1830</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -9030,10 +9030,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M64" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>1830</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -9077,7 +9077,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>1834</x:v>
+        <x:v>1833</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -9121,7 +9121,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N66" s="0" t="s">
-        <x:v>1835</x:v>
+        <x:v>1836</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -9162,10 +9162,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M67" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N67" s="0" t="s">
-        <x:v>1836</x:v>
+        <x:v>1843</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -9209,7 +9209,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>1837</x:v>
+        <x:v>1835</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -9253,7 +9253,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>1838</x:v>
+        <x:v>1848</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -9294,10 +9294,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N70" s="0" t="s">
-        <x:v>1841</x:v>
+        <x:v>1839</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -9385,7 +9385,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N72" s="0" t="s">
-        <x:v>1844</x:v>
+        <x:v>1842</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:14" x14ac:dyDescent="0.25">
@@ -9429,7 +9429,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N73" s="0" t="s">
-        <x:v>1842</x:v>
+        <x:v>1841</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -9473,7 +9473,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N74" s="0" t="s">
-        <x:v>1843</x:v>
+        <x:v>1846</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -9561,7 +9561,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N76" s="0" t="s">
-        <x:v>1846</x:v>
+        <x:v>1854</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -9605,7 +9605,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N77" s="0" t="s">
-        <x:v>1847</x:v>
+        <x:v>1855</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -9649,7 +9649,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N78" s="0" t="s">
-        <x:v>1851</x:v>
+        <x:v>1847</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -9690,10 +9690,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M79" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N79" s="0" t="s">
-        <x:v>1848</x:v>
+        <x:v>1850</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -9781,7 +9781,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N81" s="0" t="s">
-        <x:v>1859</x:v>
+        <x:v>1857</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -9825,7 +9825,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N82" s="0" t="s">
-        <x:v>1850</x:v>
+        <x:v>1844</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -9869,7 +9869,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N83" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -9954,7 +9954,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N85" s="0" t="s">
-        <x:v>1853</x:v>
+        <x:v>1851</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -9998,7 +9998,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N86" s="0" t="s">
-        <x:v>1856</x:v>
+        <x:v>1853</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -10039,7 +10039,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N87" s="0" t="s">
-        <x:v>1860</x:v>
+        <x:v>1859</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -10080,7 +10080,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N88" s="0" t="s">
-        <x:v>1854</x:v>
+        <x:v>1863</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -10162,7 +10162,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N90" s="0" t="s">
-        <x:v>1857</x:v>
+        <x:v>1856</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -10200,10 +10200,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M91" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N91" s="0" t="s">
-        <x:v>1863</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -10244,7 +10244,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N92" s="0" t="s">
-        <x:v>1861</x:v>
+        <x:v>1860</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -10288,7 +10288,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N93" s="0" t="s">
-        <x:v>1864</x:v>
+        <x:v>1869</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -10332,7 +10332,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N94" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -10376,7 +10376,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N95" s="0" t="s">
-        <x:v>1862</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -10420,7 +10420,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N96" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M97" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N97" s="0" t="s">
         <x:v>1865</x:v>
@@ -10505,10 +10505,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M98" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N98" s="0" t="s">
-        <x:v>1874</x:v>
+        <x:v>1864</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -10552,7 +10552,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N99" s="0" t="s">
-        <x:v>1870</x:v>
+        <x:v>1866</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -10596,7 +10596,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N100" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1861</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -10637,10 +10637,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M101" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N101" s="0" t="s">
-        <x:v>1873</x:v>
+        <x:v>1867</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -10681,10 +10681,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M102" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N102" s="0" t="s">
-        <x:v>1869</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -10725,10 +10725,10 @@
         <x:v>855</x:v>
       </x:c>
       <x:c r="M103" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N103" s="0" t="s">
-        <x:v>1868</x:v>
+        <x:v>1875</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -10769,10 +10769,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M104" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N104" s="0" t="s">
-        <x:v>1871</x:v>
+        <x:v>1881</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -10813,7 +10813,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M105" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N105" s="0" t="s">
         <x:v>1872</x:v>
@@ -10860,7 +10860,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N106" s="0" t="s">
-        <x:v>1866</x:v>
+        <x:v>1862</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:14" x14ac:dyDescent="0.25">
@@ -10901,10 +10901,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M107" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N107" s="0" t="s">
-        <x:v>1877</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -10945,10 +10945,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M108" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N108" s="0" t="s">
-        <x:v>1875</x:v>
+        <x:v>1871</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -10992,7 +10992,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N109" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:14" x14ac:dyDescent="0.25">
@@ -11036,7 +11036,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N110" s="0" t="s">
-        <x:v>1881</x:v>
+        <x:v>1876</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -11080,7 +11080,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N111" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1873</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:14" x14ac:dyDescent="0.25">
@@ -11124,7 +11124,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N112" s="0" t="s">
-        <x:v>1876</x:v>
+        <x:v>1868</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -11168,7 +11168,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N113" s="0" t="s">
-        <x:v>1878</x:v>
+        <x:v>1899</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -11212,7 +11212,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N114" s="0" t="s">
-        <x:v>1879</x:v>
+        <x:v>1878</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:14" x14ac:dyDescent="0.25">
@@ -11256,7 +11256,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N115" s="0" t="s">
-        <x:v>1887</x:v>
+        <x:v>1879</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:14" x14ac:dyDescent="0.25">
@@ -11300,7 +11300,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N116" s="0" t="s">
-        <x:v>1850</x:v>
+        <x:v>1844</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:14" x14ac:dyDescent="0.25">
@@ -11341,10 +11341,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M117" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N117" s="0" t="s">
-        <x:v>1886</x:v>
+        <x:v>1885</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:14" x14ac:dyDescent="0.25">
@@ -11385,7 +11385,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N118" s="0" t="s">
-        <x:v>1883</x:v>
+        <x:v>1886</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:14" x14ac:dyDescent="0.25">
@@ -11429,7 +11429,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N119" s="0" t="s">
-        <x:v>1884</x:v>
+        <x:v>1880</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -11470,10 +11470,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M120" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N120" s="0" t="s">
-        <x:v>1892</x:v>
+        <x:v>1893</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:14" x14ac:dyDescent="0.25">
@@ -11517,7 +11517,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N121" s="0" t="s">
-        <x:v>1885</x:v>
+        <x:v>1877</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:14" x14ac:dyDescent="0.25">
@@ -11558,7 +11558,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N122" s="0" t="s">
-        <x:v>1880</x:v>
+        <x:v>1874</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:14" x14ac:dyDescent="0.25">
@@ -11596,10 +11596,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M123" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N123" s="0" t="s">
-        <x:v>1898</x:v>
+        <x:v>1884</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -11643,7 +11643,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N124" s="0" t="s">
-        <x:v>1890</x:v>
+        <x:v>1883</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -11684,7 +11684,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N125" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1887</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:14" x14ac:dyDescent="0.25">
@@ -11725,7 +11725,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N126" s="0" t="s">
-        <x:v>1889</x:v>
+        <x:v>1888</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:14" x14ac:dyDescent="0.25">
@@ -11769,7 +11769,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N127" s="0" t="s">
-        <x:v>1901</x:v>
+        <x:v>1904</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:14" x14ac:dyDescent="0.25">
@@ -11813,7 +11813,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N128" s="0" t="s">
-        <x:v>1893</x:v>
+        <x:v>1903</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -11898,10 +11898,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M130" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N130" s="0" t="s">
-        <x:v>1895</x:v>
+        <x:v>1900</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:14" x14ac:dyDescent="0.25">
@@ -11945,7 +11945,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N131" s="0" t="s">
-        <x:v>1896</x:v>
+        <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -11989,7 +11989,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N132" s="0" t="s">
-        <x:v>1897</x:v>
+        <x:v>1889</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:14" x14ac:dyDescent="0.25">
@@ -12033,7 +12033,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N133" s="0" t="s">
-        <x:v>1891</x:v>
+        <x:v>1882</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:14" x14ac:dyDescent="0.25">
@@ -12074,10 +12074,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M134" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N134" s="0" t="s">
-        <x:v>1900</x:v>
+        <x:v>1905</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:14" x14ac:dyDescent="0.25">
@@ -12121,7 +12121,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N135" s="0" t="s">
-        <x:v>1899</x:v>
+        <x:v>1891</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -12165,7 +12165,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N136" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:14" x14ac:dyDescent="0.25">
@@ -12209,7 +12209,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N137" s="0" t="s">
-        <x:v>1902</x:v>
+        <x:v>1897</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:14" x14ac:dyDescent="0.25">
@@ -12250,10 +12250,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M138" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N138" s="0" t="s">
-        <x:v>1903</x:v>
+        <x:v>1911</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:14" x14ac:dyDescent="0.25">
@@ -12297,7 +12297,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N139" s="0" t="s">
-        <x:v>1908</x:v>
+        <x:v>1895</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -12341,7 +12341,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N140" s="0" t="s">
-        <x:v>1917</x:v>
+        <x:v>1913</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:14" x14ac:dyDescent="0.25">
@@ -12385,7 +12385,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N141" s="0" t="s">
-        <x:v>1904</x:v>
+        <x:v>1896</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:14" x14ac:dyDescent="0.25">
@@ -12426,10 +12426,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M142" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N142" s="0" t="s">
-        <x:v>1913</x:v>
+        <x:v>1892</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -12473,7 +12473,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N143" s="0" t="s">
-        <x:v>1907</x:v>
+        <x:v>1898</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:14" x14ac:dyDescent="0.25">
@@ -12517,7 +12517,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N144" s="0" t="s">
-        <x:v>1905</x:v>
+        <x:v>1909</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:14" x14ac:dyDescent="0.25">
@@ -12558,10 +12558,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M145" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N145" s="0" t="s">
-        <x:v>1906</x:v>
+        <x:v>1908</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:14" x14ac:dyDescent="0.25">
@@ -12602,10 +12602,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M146" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N146" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1901</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:14" x14ac:dyDescent="0.25">
@@ -12649,7 +12649,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N147" s="0" t="s">
-        <x:v>1909</x:v>
+        <x:v>1919</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:14" x14ac:dyDescent="0.25">
@@ -12693,7 +12693,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N148" s="0" t="s">
-        <x:v>1912</x:v>
+        <x:v>1906</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:14" x14ac:dyDescent="0.25">
@@ -12737,7 +12737,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N149" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:14" x14ac:dyDescent="0.25">
@@ -12781,7 +12781,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N150" s="0" t="s">
-        <x:v>1914</x:v>
+        <x:v>1912</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:14" x14ac:dyDescent="0.25">
@@ -12822,10 +12822,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M151" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N151" s="0" t="s">
-        <x:v>1918</x:v>
+        <x:v>1916</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:14" x14ac:dyDescent="0.25">
@@ -12869,7 +12869,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N152" s="0" t="s">
-        <x:v>1916</x:v>
+        <x:v>1915</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:14" x14ac:dyDescent="0.25">
@@ -12910,10 +12910,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M153" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N153" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1910</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:14" x14ac:dyDescent="0.25">
@@ -12957,7 +12957,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N154" s="0" t="s">
-        <x:v>1931</x:v>
+        <x:v>1929</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:14" x14ac:dyDescent="0.25">
@@ -13001,7 +13001,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N155" s="0" t="s">
-        <x:v>1915</x:v>
+        <x:v>1918</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:14" x14ac:dyDescent="0.25">
@@ -13045,7 +13045,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N156" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:14" x14ac:dyDescent="0.25">
@@ -13089,7 +13089,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N157" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:14" x14ac:dyDescent="0.25">
@@ -13133,7 +13133,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N158" s="0" t="s">
-        <x:v>1910</x:v>
+        <x:v>1902</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:14" x14ac:dyDescent="0.25">
@@ -13177,7 +13177,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N159" s="0" t="s">
-        <x:v>1850</x:v>
+        <x:v>1844</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:14" x14ac:dyDescent="0.25">
@@ -13218,10 +13218,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M160" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N160" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1921</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -13265,7 +13265,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N161" s="0" t="s">
-        <x:v>1911</x:v>
+        <x:v>1907</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:14" x14ac:dyDescent="0.25">
@@ -13309,7 +13309,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N162" s="0" t="s">
-        <x:v>1920</x:v>
+        <x:v>1923</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:14" x14ac:dyDescent="0.25">
@@ -13353,7 +13353,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N163" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:14" x14ac:dyDescent="0.25">
@@ -13394,10 +13394,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M164" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N164" s="0" t="s">
-        <x:v>1921</x:v>
+        <x:v>1924</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:14" x14ac:dyDescent="0.25">
@@ -13441,7 +13441,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N165" s="0" t="s">
-        <x:v>1919</x:v>
+        <x:v>1914</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:14" x14ac:dyDescent="0.25">
@@ -13485,7 +13485,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N166" s="0" t="s">
-        <x:v>1927</x:v>
+        <x:v>1922</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:14" x14ac:dyDescent="0.25">
@@ -13529,7 +13529,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N167" s="0" t="s">
-        <x:v>1922</x:v>
+        <x:v>1917</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:14" x14ac:dyDescent="0.25">
@@ -13573,7 +13573,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N168" s="0" t="s">
-        <x:v>1925</x:v>
+        <x:v>1928</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:14" x14ac:dyDescent="0.25">
@@ -13617,7 +13617,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N169" s="0" t="s">
-        <x:v>1930</x:v>
+        <x:v>1926</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:14" x14ac:dyDescent="0.25">
@@ -13661,7 +13661,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N170" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:14" x14ac:dyDescent="0.25">
@@ -13705,7 +13705,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N171" s="0" t="s">
-        <x:v>1923</x:v>
+        <x:v>1920</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:14" x14ac:dyDescent="0.25">
@@ -13749,7 +13749,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N172" s="0" t="s">
-        <x:v>1926</x:v>
+        <x:v>1934</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -13790,10 +13790,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M173" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N173" s="0" t="s">
-        <x:v>1928</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:14" x14ac:dyDescent="0.25">
@@ -13837,7 +13837,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N174" s="0" t="s">
-        <x:v>1929</x:v>
+        <x:v>1931</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:14" x14ac:dyDescent="0.25">
@@ -13881,7 +13881,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N175" s="0" t="s">
-        <x:v>1933</x:v>
+        <x:v>1925</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:14" x14ac:dyDescent="0.25">
@@ -13925,7 +13925,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N176" s="0" t="s">
-        <x:v>1850</x:v>
+        <x:v>1844</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:14" x14ac:dyDescent="0.25">
@@ -13966,10 +13966,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M177" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N177" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1938</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:14" x14ac:dyDescent="0.25">
@@ -14013,7 +14013,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N178" s="0" t="s">
-        <x:v>1934</x:v>
+        <x:v>1927</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:14" x14ac:dyDescent="0.25">
@@ -14057,7 +14057,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N179" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:14" x14ac:dyDescent="0.25">
@@ -14101,7 +14101,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N180" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:14" x14ac:dyDescent="0.25">
@@ -14145,7 +14145,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N181" s="0" t="s">
-        <x:v>1937</x:v>
+        <x:v>1932</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:14" x14ac:dyDescent="0.25">
@@ -14189,7 +14189,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N182" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:14" x14ac:dyDescent="0.25">
@@ -14277,7 +14277,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N184" s="0" t="s">
-        <x:v>1932</x:v>
+        <x:v>1937</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:14" x14ac:dyDescent="0.25">
@@ -14321,7 +14321,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N185" s="0" t="s">
-        <x:v>1938</x:v>
+        <x:v>1930</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:14" x14ac:dyDescent="0.25">
@@ -14365,7 +14365,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N186" s="0" t="s">
-        <x:v>1936</x:v>
+        <x:v>1942</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -14409,7 +14409,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N187" s="0" t="s">
-        <x:v>1935</x:v>
+        <x:v>1941</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:14" x14ac:dyDescent="0.25">
@@ -14450,10 +14450,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M188" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N188" s="0" t="s">
-        <x:v>1939</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:14" x14ac:dyDescent="0.25">
@@ -14494,10 +14494,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M189" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N189" s="0" t="s">
-        <x:v>1941</x:v>
+        <x:v>1933</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:14" x14ac:dyDescent="0.25">
@@ -14538,10 +14538,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M190" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N190" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1935</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:14" x14ac:dyDescent="0.25">
@@ -14585,7 +14585,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N191" s="0" t="s">
-        <x:v>1942</x:v>
+        <x:v>1945</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:14" x14ac:dyDescent="0.25">
@@ -14629,7 +14629,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N192" s="0" t="s">
-        <x:v>1943</x:v>
+        <x:v>1939</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:14" x14ac:dyDescent="0.25">
@@ -14673,7 +14673,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N193" s="0" t="s">
-        <x:v>1946</x:v>
+        <x:v>1944</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:14" x14ac:dyDescent="0.25">
@@ -14717,7 +14717,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N194" s="0" t="s">
-        <x:v>1948</x:v>
+        <x:v>1943</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:14" x14ac:dyDescent="0.25">
@@ -14758,10 +14758,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M195" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N195" s="0" t="s">
-        <x:v>1950</x:v>
+        <x:v>1967</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -14802,10 +14802,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M196" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N196" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1936</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:14" x14ac:dyDescent="0.25">
@@ -14849,7 +14849,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N197" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:14" x14ac:dyDescent="0.25">
@@ -14890,10 +14890,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M198" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N198" s="0" t="s">
-        <x:v>1945</x:v>
+        <x:v>1954</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:14" x14ac:dyDescent="0.25">
@@ -14934,10 +14934,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M199" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N199" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1950</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:14" x14ac:dyDescent="0.25">
@@ -14981,7 +14981,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N200" s="0" t="s">
-        <x:v>1951</x:v>
+        <x:v>1946</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -15025,7 +15025,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N201" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:14" x14ac:dyDescent="0.25">
@@ -15069,7 +15069,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N202" s="0" t="s">
-        <x:v>1961</x:v>
+        <x:v>1948</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:14" x14ac:dyDescent="0.25">
@@ -15110,10 +15110,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M203" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N203" s="0" t="s">
-        <x:v>1944</x:v>
+        <x:v>1949</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:14" x14ac:dyDescent="0.25">
@@ -15157,7 +15157,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N204" s="0" t="s">
-        <x:v>1947</x:v>
+        <x:v>1953</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:14" x14ac:dyDescent="0.25">
@@ -15201,7 +15201,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N205" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:14" x14ac:dyDescent="0.25">
@@ -15242,10 +15242,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M206" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N206" s="0" t="s">
-        <x:v>1949</x:v>
+        <x:v>1963</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:14" x14ac:dyDescent="0.25">
@@ -15289,7 +15289,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N207" s="0" t="s">
-        <x:v>1953</x:v>
+        <x:v>1955</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:14" x14ac:dyDescent="0.25">
@@ -15377,7 +15377,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N209" s="0" t="s">
-        <x:v>1954</x:v>
+        <x:v>1951</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:14" x14ac:dyDescent="0.25">
@@ -15421,7 +15421,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N210" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:14" x14ac:dyDescent="0.25">
@@ -15465,7 +15465,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N211" s="0" t="s">
-        <x:v>1955</x:v>
+        <x:v>1956</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:14" x14ac:dyDescent="0.25">
@@ -15509,7 +15509,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N212" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:14" x14ac:dyDescent="0.25">
@@ -15553,7 +15553,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N213" s="0" t="s">
-        <x:v>1962</x:v>
+        <x:v>1961</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:14" x14ac:dyDescent="0.25">
@@ -15594,10 +15594,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M214" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N214" s="0" t="s">
-        <x:v>1967</x:v>
+        <x:v>1965</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:14" x14ac:dyDescent="0.25">
@@ -15641,7 +15641,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N215" s="0" t="s">
-        <x:v>1957</x:v>
+        <x:v>1960</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:14" x14ac:dyDescent="0.25">
@@ -15685,7 +15685,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N216" s="0" t="s">
-        <x:v>1963</x:v>
+        <x:v>1959</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:14" x14ac:dyDescent="0.25">
@@ -15729,7 +15729,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N217" s="0" t="s">
-        <x:v>1959</x:v>
+        <x:v>1957</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:14" x14ac:dyDescent="0.25">
@@ -15773,7 +15773,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N218" s="0" t="s">
-        <x:v>1956</x:v>
+        <x:v>1947</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:14" x14ac:dyDescent="0.25">
@@ -15814,10 +15814,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M219" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N219" s="0" t="s">
-        <x:v>1965</x:v>
+        <x:v>1964</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:14" x14ac:dyDescent="0.25">
@@ -15858,10 +15858,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M220" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N220" s="0" t="s">
-        <x:v>1960</x:v>
+        <x:v>1966</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:14" x14ac:dyDescent="0.25">
@@ -15946,10 +15946,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M222" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N222" s="0" t="s">
-        <x:v>1966</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:14" x14ac:dyDescent="0.25">
@@ -15993,7 +15993,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N223" s="0" t="s">
-        <x:v>1964</x:v>
+        <x:v>1962</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
+++ b/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
@@ -5426,505 +5426,139 @@
     <x:t>Builds custom advanced manufacturing systems with a focus on high-speed assembly, test, and inspection of automotive electronics components</x:t>
   </x:si>
   <x:si>
-    <x:t>Manufactures automotive wire harnesses, sensors, and electronic modules; likely has in-house R&amp;D and test engineering to validate designs and ensure quality.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Company lists in-house design, manufacturing, and testing capabilities, indicating need for test equipment.</x:t>
+    <x:t>Manufactures automotive wire harnesses and sensors, indicating in-house test/quality control functions that require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Site explicitly lists 'testing' as a core capability alongside design and manufacturing of electronics, indicating in-house test engineers.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Automotive supplier of seating and electrical systems; no clear evidence of in-house electronic test or R&amp;D labs that would use oscilloscopes or similar equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No clear evidence of in-house electronic test or measurement work, just metal foil processing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>States parts undergo advanced testing (vibration, thermal shock) but unclear if they have in-house labs or just resell sensors; no explicit engineering/R&amp;D team mentioned.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 301 Moved Permanently</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures electronic components like voltage regulators and rectifiers, implying in-house production testing with equipment like oscilloscopes or power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 403 Forbidden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures LED lighting and smart trailer systems, implying in-house electronics R&amp;D and testing.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Request timed out after 15s</x:t>
   </x:si>
   <x:si>
-    <x:t>Scrape failed: HTTP 403 Forbidden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Insufficient website content to determine if they have in-house electronics test or engineering functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: HTTP 301 Moved Permanently</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer of electronic automotive components (voltage regulators, rectifiers), but no direct evidence of in-house test engineering, R&amp;D, or calibration lab visible in the scraped content.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Repairs and remanufactures automotive electronic modules, which likely requires in-house testing and diagnostic equipment like oscilloscopes and power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house design and manufacturing of electronic LED lighting and smart vehicle systems implies use of test equipment for development and quality assurance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No clear evidence of in-house electronic testing or engineering; they process metal foils for thermal management applications.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a retail installer of automotive electronics with no evidence of in-house engineering or test work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>provides in-house electronic repair and calibration services requiring test equipment like oscilloscopes and signal generators</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Website markets automotive electronics but provides no concrete evidence of in-house engineering, R&amp;D, or test lab.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, develop, and manufacture automotive electronic components and wiring harnesses, implying in-house R&amp;D and test functions that use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Consumer brand for car audio, no evidence of in-house engineering or test; may only resell/install finished products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures automotive electronic components (sensors, ignition, fuel injection) and has an Engineered Solutions division, indicating in-house engineering and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures automotive wiring and components but no clear evidence of in-house electronic test or R&amp;D lab.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No indication of in-house engineering or test; seems to sell and install finished camera products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides mobile vehicle electronics diagnostics and calibration services, uses specialized automotive tools, but unclear need for general-purpose test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They install and maintain emergency vehicle electronics but show no clear signs of on-site engineering or use of test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house repair, remanufacturing, and calibration of automotive electronics, indicating they likely use test equipment like oscilloscopes and meters.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They remanufacture electronic automotive components (e.g., engine control modules, throttle bodies) and mention calibration and repair, indicating in-house electronics testing and diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures its own electronic throttle controllers, implying in-house R&amp;D and likely use of test equipment for development and compliance testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures vehicle electronic components, implying in-house engineering and testing labs that use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped website content is garbled and unreadable, preventing any determination of in-house engineering or test equipment usage.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer of electronic performance components, likely has in-house R&amp;D needing test gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTCA R&amp;D center and multiple manufacturing plants show in-house engineering and testing of electronic automotive systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Develops and produces stamped connectors; unclear if they perform in-house electronic testing requiring oscilloscopes or signal generators.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures electronic control units and ADAS, indicating in-house R&amp;D and test.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house engineering and rigorous testing (PPAP, FMEA) on wire harnesses indicates staff who plausibly use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sells aftermarket automotive electronics but no evidence of in-house engineering, R&amp;D, or test/repair functions visible in website content.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and tests custom ECUs and diagnostic hardware, indicating in-house electronics engineering lab work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sells programmed engine modules but shows no evidence of in-house hardware engineering or general test equipment use; likely relies on automotive-specific programmers.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Full-cycle electronics remanufacturing of automotive electronics implies in-house testing and diagnostics that require test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures only mechanical automotive components, no evidence of in-house electronics testing, calibration, or repair work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions 'deep engineering expertise' and 'Engineering Products' but no explicit in-house test/measurement or calibration functions visible in the scraped text.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Company engineers and manufactures automotive electronics, indicating likely use of test equipment for R&amp;D and quality control.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Automotive components manufacturer with no clear indication of in-house electronic R&amp;D or testing functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a tier-one automotive lighting supplier with in-house engineering and manufacturing, indicating they likely use electronic test equipment for R&amp;D and production testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The Plymouth, MI location 'specializes in the development and testing' of LED lighting solutions, indicating in-house R&amp;D that likely uses test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Develops advanced sensors, radar systems, and electronic safety components, indicating in-house R&amp;D and test engineering.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Automotive tuning shop; no evidence of in-house electronics engineering or test that would require oscilloscopes or similar gear.</x:t>
+    <x:t>Repair and refurbishment of automotive electronic control units likely requires in-house use of test equipment like oscilloscopes and power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped content shows product categories but no evidence of in-house engineering or test lab; they design/integrate automotive electronics but it's unclear if they own test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Only consumer-facing sales of finished car audio products visible; no evidence of in-house engineering, R&amp;D, or test labs on this page.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 429 Too Many Requests</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Performs in-house repair and calibration of electronic instrument clusters, PCMs, and modules, requiring electronic test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house design, development, and manufacturing of automotive electronics and wiring harnesses likely requires test equipment for validation and quality assurance.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 520 &lt;none&gt;</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Installs finished auto electronics (alarms, audio) with no evidence of in-house engineering, testing, or repair that requires T&amp;M equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Site suggests product development but no clear evidence of in-house engineering or test hardware usage.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Manufactures electronic automotive parts (sensors, engine management) at their engineering and manufacturing facilities, indicating in-house R&amp;D and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>In-house manufacturing and development of electronic components like wire harnesses and battery sensors requires R&amp;D and test equipment such as oscilloscopes and power supplies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Performs in-house repair, remanufacturing, calibration, and testing of automotive electronics, indicating use of test equipment like oscilloscopes and signal generators.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design, develop, and manufacture automotive electronics, ECUs, and provide testing services; their MxSuite integrates with test equipment, indicating in-house use of measurement gear.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Primarily installs finished electronic components into vehicles, with no visible in-house engineering or test lab for electronic diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Provides vehicle electronics diagnostics and calibration services, but not clear if they use general-purpose test equipment; likely uses specialized automotive tools.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They remanufacture electronic control modules and perform calibration, indicating in-house test and diagnostic work on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Site shows they design and sell automotive performance electronics but no clear evidence of in-house engineering lab or test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch, RemoteCertificateChainErrors)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Develops and produces connectors; development may involve testing, but no explicit test/engineering lab or equipment use is evident.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTCA R&amp;D center develops ADAS and infotainment systems, and manufacturing includes hybrid battery modules, indicating in-house electronic testing and calibration.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: An error occurred while sending the request. (The response ended prematurely. (ResponseEnded))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>U.S. manufacturer of electronic control systems; likely has in-house R&amp;D/engineering that uses test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designs and manufactures electronic systems, implying in-house R&amp;D and testing that requires test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scraped text shows deep engineering expertise and custom manufacturing, suggesting in-house electronic design and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 502 Bad Gateway</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sells pre-programmed automotive control modules and offers reprogramming, but no clear evidence of in-house engineering or hardware-level diagnostics requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FlexStation-IOT ECU test station and custom ECU development indicate in-house hardware engineering likely using test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Describes in-house engineering and manufacturing of automotive electronics, implying need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Primarily mechanical component manufacturer; no evidence of in-house electronics testing or R&amp;D requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Installs finished vehicle electronics, no visible engineering or test function.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Primarily resells and installs aftermarket automotive accessories, no indication of in-house engineering or testing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Automotive lighting manufacturer with in-house engineering and R&amp;D, likely using test equipment for design and validation of electronic lighting components.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Page body was empty after parsing</x:t>
   </x:si>
   <x:si>
-    <x:t>Mentions R&amp;D, advanced electronics, sensor tech, and design of electromagnetic valves, indicating in-house engineering likely using test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house PCB assembly, EMS, and ODM with engineering support, likely using test equipment for quality control.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions product development and engineering centers, likely involving design and testing of automotive electronic components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Installs and resells finished automotive electronics; no evidence of in-house engineering, calibration, or repair work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an engineering and manufacturing company with a technical center, likely having engineers who test and develop automotive systems and machine tools, requiring electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>insufficient scraped content to determine if they have in-house engineering/test functions</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures electronic controls, motors, and TPMS/EHPS/PEPS systems, indicating in-house R&amp;D and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Company has in-house engineering and testing lab for automotive electronic components, performing electrical testing per SAE standards.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house design, engineering and testing of EV powertrain systems including motor controllers, battery management, and VCU programming, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vertically integrated electronic manufacturer with in-house engineering and ISO 9001-2015 certification suggests need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house development and engineering of OBD tuning software and hardware, plus design and manufacturing of performance parts, suggest need for electronic test and measurement.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They engineer proprietary sensor/control systems, implying in-house R&amp;D and testing that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a vehicle upfitter and distributor of finished public safety equipment (lights, sirens, barriers); no evidence of in-house engineering, R&amp;D, or test functions that would require T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They remanufacture and repair electronic instrument clusters, implying in-house electronics diagnostics and repair requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Technical resource for vehicle wiring installations and module configurations, but no evidence of in-house engineering, R&amp;D, or repair work requiring test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures modular electronic assemblies and automotive lighting products, very likely requiring in-house test, validation, or quality control with electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They list 'Testing' as a capability and manufacture electronic components and wire harnesses, typically requiring in-house electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: HTTP 406 Not Acceptable</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Remanufactures mechanical fuel system components; no clear evidence of in-house electronic test or diagnostics that would require general-purpose T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides a software platform for electronics manufacturing inspection and test data, but no clear evidence of in-house hardware engineering, repair, or calibration work requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions integrated modules for control units and power electronics, but website text focuses on plastic molding and assembly with no clear evidence of in-house electronic testing or engineering labs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and tests power control modules, with advanced testing indicating in-house engineering.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content is insufficient to determine if they have in-house engineering or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer with R&amp;D, but no evidence of electronic testing or equipment need.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Trade association focused on software OTA standards, no evidence of in-house electronic hardware testing, engineering, or manufacturing that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures automotive semiconductors and ECUs, indicating in-house design and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mechatronics products imply potential electronic testing, but no clear evidence of using T&amp;M equipment like oscilloscopes.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures automotive LED lighting, suggesting possible in-house electronics engineering and testing, but no explicit mention of test equipment or calibration labs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content insufficient to determine if they perform in-house electronic test/engineering work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (omron.com:443)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No evidence of in-house test/engineering; purely a wholesale warehouse distributor of auto parts, chemicals, and oils.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Automotive parts supplier with no visible electronic engineering, R&amp;D, or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineering and prototyping lab that develops products from concept to testing, implying in-house use of test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content shows automotive chemical products, no indication of in-house electronics engineering or repair that would need test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tier 1 automotive supplier with manufacturing and custom tool development, but no mention of in-house electronic test or diagnostics; unclear if they have engineers using T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures electronic transmission controllers in-house, with custom engineering and tuning, implying use of test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No evidence of in-house electronic engineering, R&amp;D, or repair; company focuses on automotive mechanical tools and training.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (shinko.co.jp:443)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house design and manufacturing of advanced electrical connectors and harness systems strongly implies engineering teams that need to validate, test, and troubleshoot electronic hardware with instruments like oscilloscopes and meters.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resells automotive diagnostic tools including lab scopes, but no clear evidence of in-house engineering, calibration, or repair work; appears primarily a reseller.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions custom design, but unclear if they do in-house electronic testing versus just assembling or reselling automotive equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Develops, engineers, and manufactures its own LED emergency lighting products, implying an internal R&amp;D and test function that likely uses electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They install aftermarket vehicle electronics but no evidence of in-house engineering or test equipment use; primarily an installation service.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, develop, and manufacture electronic solutions with in-house R&amp;D, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers PCBA and full box-build with engineering services, indicating in-house test and measurement needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides Engineering &amp; Design Services and manufactures PCBA and electronic components, implying in-house testing and diagnostics using test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer custom electronic hardware design, prototyping, and production support with 20 years of engineering experience, indicating in-house engineers who use test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content was insufficient to make a determination</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures hydraulic brake calipers and components; no indication of electronic testing or engineering lab on site.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures PCBs, RF components, and mission systems, implying in-house engineering and testing requiring oscilloscopes, signal generators, etc.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform functional testing, in-circuit testing, and have AOI and 3D X-ray inspection, indicating in-house engineering/test work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers electronic circuit troubleshooting, repair, design, and testing services, indicating in-house need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Distributor of electronic components; mentions test &amp; measurement products but no evidence of in-house engineering or test work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Curtis has in-house R&amp;D, engineering, and manufacturing of motor controllers and battery management systems, indicating they likely use test equipment like oscilloscopes and power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer of automotive chemical additives; no indication of in-house electronics engineering, testing, or repair; likely no need for test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures mechatronic and actuator systems, implying potential in-house electronic engineering and testing, but scraped content lacks explicit mention of test labs or T&amp;M equipment usage.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures high-frequency ceramic components, indicating in-house R&amp;D and testing that likely uses RF test equipment like spectrum analyzers and network analyzers.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (hosiden.com:443)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer's representative for electronic components, no evidence of in-house engineering, testing, or repair functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide PCB coating services, but no clear evidence of in-house electronic engineering or test functions that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>scraped content only shows generic marketing language, no mention of engineering, R&amp;D, or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions developing products from ground up and extensive testing tailored to application, indicating in-house engineering/R&amp;D that likely requires test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (foster-electric.com:443)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCB manufacturer implies some in-house testing, but no explicit mention of test equipment, engineering, or R&amp;D functions that would need oscilloscopes, signal generators, etc.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMS company performing PCB assembly, likely has in-house test and debug engineers who use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture electronic components (sensors, LED lighting, power distribution) with in-house R&amp;D and labs, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Makes connectors for ECUs and sensors, but site emphasizes mechanical manufacturing (casting, stamping) without indication of electronic test or engineering.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMS provider with in-house engineering, testing (DFT), PCB assembly, and repair depot, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cohu designs and manufactures semiconductor test equipment, indicating in-house R&amp;D and engineering teams that use test and measurement instruments for development and validation.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures custom motor and motion control systems, indicating in-house engineering and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures power semiconductors (Si, SiC, GaN), MOSFETs, and digital isolators, implying in-house R&amp;D and test labs requiring oscilloscopes, signal generators, and other T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides PCB design and manufacturing but no explicit mention of in-house test, calibration, or repair work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Contract manufacturer offering PCBA, box build, testing, and repair services, indicating in-house use of test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturers' sales representative firm offering technical sales and engineering support, but no indication of in-house testing, repair, or R&amp;D labs that would use T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mechanical parts manufacturer with no visible in-house electronic engineering or test function requiring T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer in-house test engineering, design, and manufacturing services, clearly needing T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer's rep providing engineering support, but no evidence of in-house test/measurement lab or hardware engineering.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMS provider with in-house design engineering and high-volume PCBA manufacturing, implying test and quality control using T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They manufacture automotive electronic components like ECUs and sensors, have inspection/measuring equipment, and operate smart factories, indicating in-house R&amp;D and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Contract manufacturer of precision mechanical components, no evidence of in-house electronic engineering or test work that would require T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Electronics contract manufacturer with in-house assembly, testing to IPC standards, design, and reverse-engineering, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions 'Advanced Test Engineering' and performs PCBA-to-complete electronic modules manufacture, indicating in-house testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house PCB assembly and antenna design with engineering support, requiring test and measurement equipment for quality assurance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house rigorous performance testing and analytical testing services for laminate materials likely require electronic test equipment for characterization.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a distributor of electronic components, not a manufacturer; no clear evidence of in-house engineering or testing labs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers turnkey manufacturing, design, and engineering services involving electronic hardware, indicating in-house test and measurement needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers in-house embedded hardware design, PCB layout, prototype testing, and hardware calibration, requiring oscilloscopes and other T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Develops boundary-scan test hardware and software, clearly has in-house engineering and testing functions that require test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Develops and applies nano coatings for electronics protection but no clear evidence of in-house electronic testing, R&amp;D, or engineering teams using T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Consumer car audio sales site, no visible in-house engineering, repair, or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture vehicle safety electronics and subject them to rigorous testing, indicating an in-house engineering and test function that likely requires test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers in-house electronics manufacturing services including assembly, testing, engineering support, and depot repair, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Engineering services explicitly include testing and prototyping, indicating in-house use of test equipment for complex electronics manufacturing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mentions product development and engineering of LED lighting controls, suggesting possible in-house electronics design, but no explicit evidence of test equipment usage.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures components with in-house R&amp;D and testing, clearly employs engineers who need test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a manufacturer's representative, and while they mention technical expertise and engineering solutions, there is no clear evidence of in-house test, calibration, or repair work that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture flexible circuits in-house for mission-critical applications, implying need for electrical testing equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs electronic hardware for 3D printers but no explicit evidence of in-house test/calibration work on electronics, only general manufacturing and services mentioned.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures automated programming systems, indicating in-house engineering and hardware testing requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house engineering, PCB assembly, system integration, and functional testing indicate active use of test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures their own automated test systems, implying in-house engineering and testing teams.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer in-house PCB design and electronics manufacturing services, indicating engineering and test functions that require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: No connection could be made because the target machine actively refused it. (jebconet.com:443)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures custom magnetics and electronic assemblies with in-house rigorous testing (thermal shock, dielectric, corona) and holds AS9100D certification, indicating need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Makes electro-mechanical assemblies and wire harnesses, but scraped text shows no explicit in-house engineering, test, or calibration functions that would clearly require oscilloscopes or signal generators.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers design, prototyping, and box-build integration services, indicating in-house engineering that likely uses test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture electronic controllers and displays, implying in-house engineering and test functions that require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sheldahl designs and manufactures flexible circuits and printed electronics, requiring in-house engineering and testing of electronic hardware, as evidenced by their R&amp;D collaboration, innovation videos, and custom solutions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides electronic manufacturing services with in-house test capabilities likely requiring oscilloscopes and power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They apply conformal coatings to electronics but no evidence of in-house electronic testing, repair, or R&amp;D that would require oscilloscopes or similar T&amp;M gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer contract manufacturing with electrical assembly and extensive testing protocols, likely requiring oscilloscopes and other test gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer electronics testing and design-for-test services, indicating in-house use of test equipment like oscilloscopes and signal generators.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and test custom electromagnetic components (coils, solenoids, relays) in-house, with dedicated testing labs, indicating a need for electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content only shows JavaScript requirement message, no meaningful company information available.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offers PCB assembly and test services, and designs OEM electronic products, indicating in-house engineering and test functions likely requiring oscilloscopes, signal generators, and power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer remanufacturing and repair services for automotive and consumer electronics, indicating in-house diagnostic and repair work requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufacturer sales rep firm providing technical sales and marketing, no evidence of in-house engineering or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and builds custom test and inspection systems for automotive electronics, implying in-house engineering likely using test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content only shows consumer goods categories, no evidence of in-house engineering or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides mechanical manufacturing services to electronics industry but no evidence of in-house electronic test or engineering functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sells optical inspection systems and does metal fabrication, but no clear evidence of in-house electronic test, repair, or R&amp;D using T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures magnetic components for automotive electronics, implying some R&amp;D and production testing, but scraped text lacks explicit mention of in-house test/measurement functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PCB manufacturer with engineering support and DFM feedback, but no clear evidence of in-house electronic testing or use of oscilloscopes/signal generators.</x:t>
+    <x:t>Scrape failed: Cancelled by user</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -7297,10 +6931,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N24" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1805</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -7341,10 +6975,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N25" s="0" t="s">
-        <x:v>1805</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -7388,7 +7022,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>1811</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -7432,7 +7066,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1811</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -7473,7 +7107,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M28" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N28" s="0" t="s">
         <x:v>1808</x:v>
@@ -7564,7 +7198,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N30" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1807</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -7608,7 +7242,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N31" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -7652,7 +7286,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1812</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -7696,7 +7330,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N33" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1809</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -7740,7 +7374,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>1816</x:v>
+        <x:v>1814</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -7784,7 +7418,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N35" s="0" t="s">
-        <x:v>1814</x:v>
+        <x:v>1813</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -7828,7 +7462,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1819</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -7869,7 +7503,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
-        <x:v>1813</x:v>
+        <x:v>1816</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -7913,7 +7547,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1817</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -7957,7 +7591,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N39" s="0" t="s">
-        <x:v>1817</x:v>
+        <x:v>1821</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -8001,7 +7635,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>1819</x:v>
+        <x:v>1820</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -8045,7 +7679,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N41" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -8083,10 +7717,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M42" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>1824</x:v>
+        <x:v>1815</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -8127,10 +7761,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M43" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1822</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -8174,7 +7808,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>1820</x:v>
+        <x:v>1826</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -8215,10 +7849,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M45" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>1825</x:v>
+        <x:v>1818</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -8259,7 +7893,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>1821</x:v>
+        <x:v>1825</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -8300,10 +7934,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M47" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N47" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1824</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -8347,7 +7981,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1830</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -8385,10 +8019,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M49" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N49" s="0" t="s">
-        <x:v>1827</x:v>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -8429,7 +8063,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N50" s="0" t="s">
-        <x:v>1822</x:v>
+        <x:v>1823</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -8473,7 +8107,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>1823</x:v>
+        <x:v>1827</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -8517,7 +8151,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>1828</x:v>
+        <x:v>1831</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -8561,7 +8195,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N53" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1811</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -8602,10 +8236,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M54" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N54" s="0" t="s">
-        <x:v>1826</x:v>
+        <x:v>1833</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -8649,7 +8283,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N55" s="0" t="s">
-        <x:v>1832</x:v>
+        <x:v>1842</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -8687,10 +8321,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M56" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>1837</x:v>
+        <x:v>1835</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -8734,7 +8368,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N57" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1811</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -8778,7 +8412,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N58" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1829</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -8822,7 +8456,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N59" s="0" t="s">
-        <x:v>1838</x:v>
+        <x:v>1839</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -8863,10 +8497,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M60" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N60" s="0" t="s">
-        <x:v>1831</x:v>
+        <x:v>1832</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -8948,7 +8582,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N62" s="0" t="s">
-        <x:v>1834</x:v>
+        <x:v>1837</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -8992,7 +8626,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N63" s="0" t="s">
-        <x:v>1830</x:v>
+        <x:v>1834</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -9033,7 +8667,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1815</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -9077,7 +8711,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>1833</x:v>
+        <x:v>1838</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -9121,7 +8755,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N66" s="0" t="s">
-        <x:v>1836</x:v>
+        <x:v>1840</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -9161,12 +8795,6 @@
       <x:c r="L67" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M67" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N67" s="0" t="s">
-        <x:v>1843</x:v>
-      </x:c>
     </x:row>
     <x:row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A68" s="0" t="s">
@@ -9206,10 +8834,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M68" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>1835</x:v>
+        <x:v>1818</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -9253,7 +8881,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>1848</x:v>
+        <x:v>1841</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -9294,10 +8922,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N70" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1836</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -9341,7 +8969,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N71" s="0" t="s">
-        <x:v>1840</x:v>
+        <x:v>1843</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -9381,12 +9009,6 @@
       <x:c r="L72" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M72" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N72" s="0" t="s">
-        <x:v>1842</x:v>
-      </x:c>
     </x:row>
     <x:row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A73" s="0" t="s">
@@ -9426,10 +9048,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M73" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N73" s="0" t="s">
-        <x:v>1841</x:v>
+        <x:v>1818</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -9469,12 +9091,6 @@
       <x:c r="L74" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M74" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N74" s="0" t="s">
-        <x:v>1846</x:v>
-      </x:c>
     </x:row>
     <x:row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A75" s="0" t="s">
@@ -9513,12 +9129,6 @@
       <x:c r="L75" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M75" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N75" s="0" t="s">
-        <x:v>1845</x:v>
-      </x:c>
     </x:row>
     <x:row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A76" s="0" t="s">
@@ -9557,12 +9167,6 @@
       <x:c r="L76" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M76" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N76" s="0" t="s">
-        <x:v>1854</x:v>
-      </x:c>
     </x:row>
     <x:row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A77" s="0" t="s">
@@ -9602,10 +9206,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M77" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N77" s="0" t="s">
-        <x:v>1855</x:v>
+        <x:v>1815</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -9645,12 +9249,6 @@
       <x:c r="L78" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M78" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N78" s="0" t="s">
-        <x:v>1847</x:v>
-      </x:c>
     </x:row>
     <x:row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A79" s="0" t="s">
@@ -9689,12 +9287,6 @@
       <x:c r="L79" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M79" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N79" s="0" t="s">
-        <x:v>1850</x:v>
-      </x:c>
     </x:row>
     <x:row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A80" s="0" t="s">
@@ -9733,12 +9325,6 @@
       <x:c r="L80" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M80" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N80" s="0" t="s">
-        <x:v>1849</x:v>
-      </x:c>
     </x:row>
     <x:row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A81" s="0" t="s">
@@ -9777,12 +9363,6 @@
       <x:c r="L81" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M81" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N81" s="0" t="s">
-        <x:v>1857</x:v>
-      </x:c>
     </x:row>
     <x:row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A82" s="0" t="s">
@@ -9869,7 +9449,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N83" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1809</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -9909,12 +9489,6 @@
       <x:c r="L84" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M84" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N84" s="0" t="s">
-        <x:v>1852</x:v>
-      </x:c>
     </x:row>
     <x:row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A85" s="0" t="s">
@@ -9950,12 +9524,6 @@
       <x:c r="L85" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M85" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N85" s="0" t="s">
-        <x:v>1851</x:v>
-      </x:c>
     </x:row>
     <x:row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A86" s="0" t="s">
@@ -9994,12 +9562,6 @@
       <x:c r="L86" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M86" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N86" s="0" t="s">
-        <x:v>1853</x:v>
-      </x:c>
     </x:row>
     <x:row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A87" s="0" t="s">
@@ -10035,12 +9597,6 @@
       <x:c r="L87" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M87" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N87" s="0" t="s">
-        <x:v>1859</x:v>
-      </x:c>
     </x:row>
     <x:row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A88" s="0" t="s">
@@ -10077,10 +9633,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M88" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N88" s="0" t="s">
-        <x:v>1863</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -10118,10 +9674,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M89" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N89" s="0" t="s">
-        <x:v>1858</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -10159,10 +9715,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M90" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N90" s="0" t="s">
-        <x:v>1856</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -10203,7 +9759,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N91" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -10241,10 +9797,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M92" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N92" s="0" t="s">
-        <x:v>1860</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -10285,10 +9841,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M93" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N93" s="0" t="s">
-        <x:v>1869</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -10332,7 +9888,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N94" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -10373,10 +9929,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M95" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N95" s="0" t="s">
-        <x:v>1870</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -10420,7 +9976,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N96" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -10461,10 +10017,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M97" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N97" s="0" t="s">
-        <x:v>1865</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -10505,10 +10061,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M98" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N98" s="0" t="s">
-        <x:v>1864</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -10549,10 +10105,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M99" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N99" s="0" t="s">
-        <x:v>1866</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -10593,10 +10149,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M100" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N100" s="0" t="s">
-        <x:v>1861</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -10640,7 +10196,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N101" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -10684,7 +10240,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N102" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -10728,7 +10284,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N103" s="0" t="s">
-        <x:v>1875</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -10772,7 +10328,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N104" s="0" t="s">
-        <x:v>1881</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -10812,12 +10368,6 @@
       <x:c r="L105" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M105" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N105" s="0" t="s">
-        <x:v>1872</x:v>
-      </x:c>
     </x:row>
     <x:row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A106" s="0" t="s">
@@ -10856,12 +10406,6 @@
       <x:c r="L106" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M106" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N106" s="0" t="s">
-        <x:v>1862</x:v>
-      </x:c>
     </x:row>
     <x:row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A107" s="0" t="s">
@@ -10900,12 +10444,6 @@
       <x:c r="L107" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M107" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N107" s="0" t="s">
-        <x:v>1803</x:v>
-      </x:c>
     </x:row>
     <x:row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A108" s="0" t="s">
@@ -10944,12 +10482,6 @@
       <x:c r="L108" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M108" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N108" s="0" t="s">
-        <x:v>1871</x:v>
-      </x:c>
     </x:row>
     <x:row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A109" s="0" t="s">
@@ -10988,12 +10520,6 @@
       <x:c r="L109" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M109" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N109" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A110" s="0" t="s">
@@ -11032,12 +10558,6 @@
       <x:c r="L110" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M110" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N110" s="0" t="s">
-        <x:v>1876</x:v>
-      </x:c>
     </x:row>
     <x:row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A111" s="0" t="s">
@@ -11076,12 +10596,6 @@
       <x:c r="L111" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M111" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N111" s="0" t="s">
-        <x:v>1873</x:v>
-      </x:c>
     </x:row>
     <x:row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A112" s="0" t="s">
@@ -11120,12 +10634,6 @@
       <x:c r="L112" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M112" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N112" s="0" t="s">
-        <x:v>1868</x:v>
-      </x:c>
     </x:row>
     <x:row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A113" s="0" t="s">
@@ -11164,12 +10672,6 @@
       <x:c r="L113" s="0" t="s">
         <x:v>855</x:v>
       </x:c>
-      <x:c r="M113" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N113" s="0" t="s">
-        <x:v>1899</x:v>
-      </x:c>
     </x:row>
     <x:row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A114" s="0" t="s">
@@ -11208,12 +10710,6 @@
       <x:c r="L114" s="0" t="s">
         <x:v>855</x:v>
       </x:c>
-      <x:c r="M114" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N114" s="0" t="s">
-        <x:v>1878</x:v>
-      </x:c>
     </x:row>
     <x:row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A115" s="0" t="s">
@@ -11252,12 +10748,6 @@
       <x:c r="L115" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M115" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N115" s="0" t="s">
-        <x:v>1879</x:v>
-      </x:c>
     </x:row>
     <x:row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A116" s="0" t="s">
@@ -11296,12 +10786,6 @@
       <x:c r="L116" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M116" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N116" s="0" t="s">
-        <x:v>1844</x:v>
-      </x:c>
     </x:row>
     <x:row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A117" s="0" t="s">
@@ -11340,12 +10824,6 @@
       <x:c r="L117" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M117" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N117" s="0" t="s">
-        <x:v>1885</x:v>
-      </x:c>
     </x:row>
     <x:row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A118" s="0" t="s">
@@ -11381,12 +10859,6 @@
       <x:c r="L118" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M118" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N118" s="0" t="s">
-        <x:v>1886</x:v>
-      </x:c>
     </x:row>
     <x:row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A119" s="0" t="s">
@@ -11425,12 +10897,6 @@
       <x:c r="L119" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M119" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N119" s="0" t="s">
-        <x:v>1880</x:v>
-      </x:c>
     </x:row>
     <x:row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A120" s="0" t="s">
@@ -11469,12 +10935,6 @@
       <x:c r="L120" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M120" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N120" s="0" t="s">
-        <x:v>1893</x:v>
-      </x:c>
     </x:row>
     <x:row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A121" s="0" t="s">
@@ -11513,12 +10973,6 @@
       <x:c r="L121" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M121" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N121" s="0" t="s">
-        <x:v>1877</x:v>
-      </x:c>
     </x:row>
     <x:row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A122" s="0" t="s">
@@ -11554,12 +11008,6 @@
       <x:c r="L122" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M122" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N122" s="0" t="s">
-        <x:v>1874</x:v>
-      </x:c>
     </x:row>
     <x:row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A123" s="0" t="s">
@@ -11595,12 +11043,6 @@
       <x:c r="L123" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M123" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N123" s="0" t="s">
-        <x:v>1884</x:v>
-      </x:c>
     </x:row>
     <x:row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A124" s="0" t="s">
@@ -11639,12 +11081,6 @@
       <x:c r="L124" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M124" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N124" s="0" t="s">
-        <x:v>1883</x:v>
-      </x:c>
     </x:row>
     <x:row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A125" s="0" t="s">
@@ -11680,12 +11116,6 @@
       <x:c r="L125" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M125" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N125" s="0" t="s">
-        <x:v>1887</x:v>
-      </x:c>
     </x:row>
     <x:row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A126" s="0" t="s">
@@ -11722,10 +11152,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M126" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N126" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:14" x14ac:dyDescent="0.25">
@@ -11765,12 +11195,6 @@
       <x:c r="L127" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M127" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N127" s="0" t="s">
-        <x:v>1904</x:v>
-      </x:c>
     </x:row>
     <x:row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A128" s="0" t="s">
@@ -11809,12 +11233,6 @@
       <x:c r="L128" s="0" t="s">
         <x:v>855</x:v>
       </x:c>
-      <x:c r="M128" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N128" s="0" t="s">
-        <x:v>1903</x:v>
-      </x:c>
     </x:row>
     <x:row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A129" s="0" t="s">
@@ -11853,12 +11271,6 @@
       <x:c r="L129" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M129" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N129" s="0" t="s">
-        <x:v>1894</x:v>
-      </x:c>
     </x:row>
     <x:row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A130" s="0" t="s">
@@ -11897,12 +11309,6 @@
       <x:c r="L130" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M130" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N130" s="0" t="s">
-        <x:v>1900</x:v>
-      </x:c>
     </x:row>
     <x:row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A131" s="0" t="s">
@@ -11942,10 +11348,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M131" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N131" s="0" t="s">
-        <x:v>1890</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -11985,12 +11391,6 @@
       <x:c r="L132" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M132" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N132" s="0" t="s">
-        <x:v>1889</x:v>
-      </x:c>
     </x:row>
     <x:row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A133" s="0" t="s">
@@ -12029,12 +11429,6 @@
       <x:c r="L133" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M133" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N133" s="0" t="s">
-        <x:v>1882</x:v>
-      </x:c>
     </x:row>
     <x:row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A134" s="0" t="s">
@@ -12073,12 +11467,6 @@
       <x:c r="L134" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M134" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N134" s="0" t="s">
-        <x:v>1905</x:v>
-      </x:c>
     </x:row>
     <x:row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A135" s="0" t="s">
@@ -12117,12 +11505,6 @@
       <x:c r="L135" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M135" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N135" s="0" t="s">
-        <x:v>1891</x:v>
-      </x:c>
     </x:row>
     <x:row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A136" s="0" t="s">
@@ -12161,12 +11543,6 @@
       <x:c r="L136" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M136" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N136" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A137" s="0" t="s">
@@ -12205,12 +11581,6 @@
       <x:c r="L137" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M137" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N137" s="0" t="s">
-        <x:v>1897</x:v>
-      </x:c>
     </x:row>
     <x:row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A138" s="0" t="s">
@@ -12249,12 +11619,6 @@
       <x:c r="L138" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M138" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N138" s="0" t="s">
-        <x:v>1911</x:v>
-      </x:c>
     </x:row>
     <x:row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A139" s="0" t="s">
@@ -12294,10 +11658,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M139" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N139" s="0" t="s">
-        <x:v>1895</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -12337,12 +11701,6 @@
       <x:c r="L140" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M140" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N140" s="0" t="s">
-        <x:v>1913</x:v>
-      </x:c>
     </x:row>
     <x:row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A141" s="0" t="s">
@@ -12381,12 +11739,6 @@
       <x:c r="L141" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M141" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N141" s="0" t="s">
-        <x:v>1896</x:v>
-      </x:c>
     </x:row>
     <x:row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A142" s="0" t="s">
@@ -12429,7 +11781,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N142" s="0" t="s">
-        <x:v>1892</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -12469,12 +11821,6 @@
       <x:c r="L143" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M143" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N143" s="0" t="s">
-        <x:v>1898</x:v>
-      </x:c>
     </x:row>
     <x:row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A144" s="0" t="s">
@@ -12513,12 +11859,6 @@
       <x:c r="L144" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M144" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N144" s="0" t="s">
-        <x:v>1909</x:v>
-      </x:c>
     </x:row>
     <x:row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A145" s="0" t="s">
@@ -12557,12 +11897,6 @@
       <x:c r="L145" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M145" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N145" s="0" t="s">
-        <x:v>1908</x:v>
-      </x:c>
     </x:row>
     <x:row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A146" s="0" t="s">
@@ -12601,12 +11935,6 @@
       <x:c r="L146" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M146" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N146" s="0" t="s">
-        <x:v>1901</x:v>
-      </x:c>
     </x:row>
     <x:row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A147" s="0" t="s">
@@ -12646,10 +11974,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M147" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N147" s="0" t="s">
-        <x:v>1919</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:14" x14ac:dyDescent="0.25">
@@ -12689,12 +12017,6 @@
       <x:c r="L148" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M148" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N148" s="0" t="s">
-        <x:v>1906</x:v>
-      </x:c>
     </x:row>
     <x:row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A149" s="0" t="s">
@@ -12733,12 +12055,6 @@
       <x:c r="L149" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M149" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N149" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A150" s="0" t="s">
@@ -12777,12 +12093,6 @@
       <x:c r="L150" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M150" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N150" s="0" t="s">
-        <x:v>1912</x:v>
-      </x:c>
     </x:row>
     <x:row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A151" s="0" t="s">
@@ -12821,12 +12131,6 @@
       <x:c r="L151" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M151" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N151" s="0" t="s">
-        <x:v>1916</x:v>
-      </x:c>
     </x:row>
     <x:row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A152" s="0" t="s">
@@ -12865,12 +12169,6 @@
       <x:c r="L152" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M152" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N152" s="0" t="s">
-        <x:v>1915</x:v>
-      </x:c>
     </x:row>
     <x:row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A153" s="0" t="s">
@@ -12909,12 +12207,6 @@
       <x:c r="L153" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M153" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N153" s="0" t="s">
-        <x:v>1910</x:v>
-      </x:c>
     </x:row>
     <x:row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A154" s="0" t="s">
@@ -12953,12 +12245,6 @@
       <x:c r="L154" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M154" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N154" s="0" t="s">
-        <x:v>1929</x:v>
-      </x:c>
     </x:row>
     <x:row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A155" s="0" t="s">
@@ -12997,12 +12283,6 @@
       <x:c r="L155" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M155" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N155" s="0" t="s">
-        <x:v>1918</x:v>
-      </x:c>
     </x:row>
     <x:row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A156" s="0" t="s">
@@ -13041,12 +12321,6 @@
       <x:c r="L156" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M156" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N156" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A157" s="0" t="s">
@@ -13085,12 +12359,6 @@
       <x:c r="L157" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M157" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N157" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A158" s="0" t="s">
@@ -13129,12 +12397,6 @@
       <x:c r="L158" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M158" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N158" s="0" t="s">
-        <x:v>1902</x:v>
-      </x:c>
     </x:row>
     <x:row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A159" s="0" t="s">
@@ -13173,12 +12435,6 @@
       <x:c r="L159" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M159" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N159" s="0" t="s">
-        <x:v>1844</x:v>
-      </x:c>
     </x:row>
     <x:row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A160" s="0" t="s">
@@ -13217,12 +12473,6 @@
       <x:c r="L160" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M160" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N160" s="0" t="s">
-        <x:v>1921</x:v>
-      </x:c>
     </x:row>
     <x:row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A161" s="0" t="s">
@@ -13261,12 +12511,6 @@
       <x:c r="L161" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M161" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N161" s="0" t="s">
-        <x:v>1907</x:v>
-      </x:c>
     </x:row>
     <x:row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A162" s="0" t="s">
@@ -13305,12 +12549,6 @@
       <x:c r="L162" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M162" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N162" s="0" t="s">
-        <x:v>1923</x:v>
-      </x:c>
     </x:row>
     <x:row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A163" s="0" t="s">
@@ -13349,12 +12587,6 @@
       <x:c r="L163" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M163" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N163" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A164" s="0" t="s">
@@ -13393,12 +12625,6 @@
       <x:c r="L164" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M164" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N164" s="0" t="s">
-        <x:v>1924</x:v>
-      </x:c>
     </x:row>
     <x:row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A165" s="0" t="s">
@@ -13437,12 +12663,6 @@
       <x:c r="L165" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M165" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N165" s="0" t="s">
-        <x:v>1914</x:v>
-      </x:c>
     </x:row>
     <x:row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A166" s="0" t="s">
@@ -13481,12 +12701,6 @@
       <x:c r="L166" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M166" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N166" s="0" t="s">
-        <x:v>1922</x:v>
-      </x:c>
     </x:row>
     <x:row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A167" s="0" t="s">
@@ -13525,12 +12739,6 @@
       <x:c r="L167" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M167" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N167" s="0" t="s">
-        <x:v>1917</x:v>
-      </x:c>
     </x:row>
     <x:row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A168" s="0" t="s">
@@ -13569,12 +12777,6 @@
       <x:c r="L168" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M168" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N168" s="0" t="s">
-        <x:v>1928</x:v>
-      </x:c>
     </x:row>
     <x:row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A169" s="0" t="s">
@@ -13613,12 +12815,6 @@
       <x:c r="L169" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M169" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N169" s="0" t="s">
-        <x:v>1926</x:v>
-      </x:c>
     </x:row>
     <x:row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A170" s="0" t="s">
@@ -13657,12 +12853,6 @@
       <x:c r="L170" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M170" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N170" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A171" s="0" t="s">
@@ -13701,12 +12891,6 @@
       <x:c r="L171" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M171" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N171" s="0" t="s">
-        <x:v>1920</x:v>
-      </x:c>
     </x:row>
     <x:row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A172" s="0" t="s">
@@ -13745,12 +12929,6 @@
       <x:c r="L172" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M172" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N172" s="0" t="s">
-        <x:v>1934</x:v>
-      </x:c>
     </x:row>
     <x:row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A173" s="0" t="s">
@@ -13789,12 +12967,6 @@
       <x:c r="L173" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M173" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N173" s="0" t="s">
-        <x:v>1803</x:v>
-      </x:c>
     </x:row>
     <x:row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A174" s="0" t="s">
@@ -13833,12 +13005,6 @@
       <x:c r="L174" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M174" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N174" s="0" t="s">
-        <x:v>1931</x:v>
-      </x:c>
     </x:row>
     <x:row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A175" s="0" t="s">
@@ -13877,12 +13043,6 @@
       <x:c r="L175" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M175" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N175" s="0" t="s">
-        <x:v>1925</x:v>
-      </x:c>
     </x:row>
     <x:row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A176" s="0" t="s">
@@ -13921,12 +13081,6 @@
       <x:c r="L176" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M176" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N176" s="0" t="s">
-        <x:v>1844</x:v>
-      </x:c>
     </x:row>
     <x:row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A177" s="0" t="s">
@@ -13965,12 +13119,6 @@
       <x:c r="L177" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M177" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N177" s="0" t="s">
-        <x:v>1938</x:v>
-      </x:c>
     </x:row>
     <x:row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A178" s="0" t="s">
@@ -14009,12 +13157,6 @@
       <x:c r="L178" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M178" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N178" s="0" t="s">
-        <x:v>1927</x:v>
-      </x:c>
     </x:row>
     <x:row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A179" s="0" t="s">
@@ -14053,12 +13195,6 @@
       <x:c r="L179" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M179" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N179" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A180" s="0" t="s">
@@ -14097,12 +13233,6 @@
       <x:c r="L180" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M180" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N180" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A181" s="0" t="s">
@@ -14141,12 +13271,6 @@
       <x:c r="L181" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M181" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N181" s="0" t="s">
-        <x:v>1932</x:v>
-      </x:c>
     </x:row>
     <x:row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A182" s="0" t="s">
@@ -14185,12 +13309,6 @@
       <x:c r="L182" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M182" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N182" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A183" s="0" t="s">
@@ -14229,12 +13347,6 @@
       <x:c r="L183" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M183" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N183" s="0" t="s">
-        <x:v>1940</x:v>
-      </x:c>
     </x:row>
     <x:row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A184" s="0" t="s">
@@ -14273,12 +13385,6 @@
       <x:c r="L184" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M184" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N184" s="0" t="s">
-        <x:v>1937</x:v>
-      </x:c>
     </x:row>
     <x:row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A185" s="0" t="s">
@@ -14317,12 +13423,6 @@
       <x:c r="L185" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M185" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N185" s="0" t="s">
-        <x:v>1930</x:v>
-      </x:c>
     </x:row>
     <x:row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A186" s="0" t="s">
@@ -14361,12 +13461,6 @@
       <x:c r="L186" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M186" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N186" s="0" t="s">
-        <x:v>1942</x:v>
-      </x:c>
     </x:row>
     <x:row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A187" s="0" t="s">
@@ -14405,12 +13499,6 @@
       <x:c r="L187" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M187" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N187" s="0" t="s">
-        <x:v>1941</x:v>
-      </x:c>
     </x:row>
     <x:row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A188" s="0" t="s">
@@ -14449,12 +13537,6 @@
       <x:c r="L188" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M188" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N188" s="0" t="s">
-        <x:v>1803</x:v>
-      </x:c>
     </x:row>
     <x:row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A189" s="0" t="s">
@@ -14493,12 +13575,6 @@
       <x:c r="L189" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M189" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N189" s="0" t="s">
-        <x:v>1933</x:v>
-      </x:c>
     </x:row>
     <x:row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A190" s="0" t="s">
@@ -14537,12 +13613,6 @@
       <x:c r="L190" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M190" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N190" s="0" t="s">
-        <x:v>1935</x:v>
-      </x:c>
     </x:row>
     <x:row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A191" s="0" t="s">
@@ -14581,12 +13651,6 @@
       <x:c r="L191" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M191" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N191" s="0" t="s">
-        <x:v>1945</x:v>
-      </x:c>
     </x:row>
     <x:row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A192" s="0" t="s">
@@ -14625,12 +13689,6 @@
       <x:c r="L192" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M192" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N192" s="0" t="s">
-        <x:v>1939</x:v>
-      </x:c>
     </x:row>
     <x:row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A193" s="0" t="s">
@@ -14669,12 +13727,6 @@
       <x:c r="L193" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M193" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N193" s="0" t="s">
-        <x:v>1944</x:v>
-      </x:c>
     </x:row>
     <x:row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A194" s="0" t="s">
@@ -14713,12 +13765,6 @@
       <x:c r="L194" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M194" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N194" s="0" t="s">
-        <x:v>1943</x:v>
-      </x:c>
     </x:row>
     <x:row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A195" s="0" t="s">
@@ -14757,12 +13803,6 @@
       <x:c r="L195" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M195" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N195" s="0" t="s">
-        <x:v>1967</x:v>
-      </x:c>
     </x:row>
     <x:row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A196" s="0" t="s">
@@ -14801,12 +13841,6 @@
       <x:c r="L196" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M196" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N196" s="0" t="s">
-        <x:v>1936</x:v>
-      </x:c>
     </x:row>
     <x:row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A197" s="0" t="s">
@@ -14845,12 +13879,6 @@
       <x:c r="L197" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M197" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N197" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A198" s="0" t="s">
@@ -14889,12 +13917,6 @@
       <x:c r="L198" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M198" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N198" s="0" t="s">
-        <x:v>1954</x:v>
-      </x:c>
     </x:row>
     <x:row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A199" s="0" t="s">
@@ -14933,12 +13955,6 @@
       <x:c r="L199" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M199" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N199" s="0" t="s">
-        <x:v>1950</x:v>
-      </x:c>
     </x:row>
     <x:row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A200" s="0" t="s">
@@ -14977,12 +13993,6 @@
       <x:c r="L200" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M200" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N200" s="0" t="s">
-        <x:v>1946</x:v>
-      </x:c>
     </x:row>
     <x:row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A201" s="0" t="s">
@@ -15021,12 +14031,6 @@
       <x:c r="L201" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M201" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N201" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A202" s="0" t="s">
@@ -15065,12 +14069,6 @@
       <x:c r="L202" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M202" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N202" s="0" t="s">
-        <x:v>1948</x:v>
-      </x:c>
     </x:row>
     <x:row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A203" s="0" t="s">
@@ -15109,12 +14107,6 @@
       <x:c r="L203" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M203" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N203" s="0" t="s">
-        <x:v>1949</x:v>
-      </x:c>
     </x:row>
     <x:row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A204" s="0" t="s">
@@ -15153,12 +14145,6 @@
       <x:c r="L204" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M204" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N204" s="0" t="s">
-        <x:v>1953</x:v>
-      </x:c>
     </x:row>
     <x:row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A205" s="0" t="s">
@@ -15197,12 +14183,6 @@
       <x:c r="L205" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M205" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N205" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A206" s="0" t="s">
@@ -15241,12 +14221,6 @@
       <x:c r="L206" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M206" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N206" s="0" t="s">
-        <x:v>1963</x:v>
-      </x:c>
     </x:row>
     <x:row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A207" s="0" t="s">
@@ -15285,12 +14259,6 @@
       <x:c r="L207" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M207" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N207" s="0" t="s">
-        <x:v>1955</x:v>
-      </x:c>
     </x:row>
     <x:row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A208" s="0" t="s">
@@ -15329,12 +14297,6 @@
       <x:c r="L208" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M208" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N208" s="0" t="s">
-        <x:v>1952</x:v>
-      </x:c>
     </x:row>
     <x:row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A209" s="0" t="s">
@@ -15373,12 +14335,6 @@
       <x:c r="L209" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M209" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N209" s="0" t="s">
-        <x:v>1951</x:v>
-      </x:c>
     </x:row>
     <x:row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A210" s="0" t="s">
@@ -15417,12 +14373,6 @@
       <x:c r="L210" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M210" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N210" s="0" t="s">
-        <x:v>1806</x:v>
-      </x:c>
     </x:row>
     <x:row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A211" s="0" t="s">
@@ -15461,12 +14411,6 @@
       <x:c r="L211" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M211" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N211" s="0" t="s">
-        <x:v>1956</x:v>
-      </x:c>
     </x:row>
     <x:row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A212" s="0" t="s">
@@ -15505,12 +14449,6 @@
       <x:c r="L212" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M212" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N212" s="0" t="s">
-        <x:v>1804</x:v>
-      </x:c>
     </x:row>
     <x:row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A213" s="0" t="s">
@@ -15549,12 +14487,6 @@
       <x:c r="L213" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M213" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N213" s="0" t="s">
-        <x:v>1961</x:v>
-      </x:c>
     </x:row>
     <x:row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A214" s="0" t="s">
@@ -15593,12 +14525,6 @@
       <x:c r="L214" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M214" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N214" s="0" t="s">
-        <x:v>1965</x:v>
-      </x:c>
     </x:row>
     <x:row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A215" s="0" t="s">
@@ -15637,12 +14563,6 @@
       <x:c r="L215" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M215" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N215" s="0" t="s">
-        <x:v>1960</x:v>
-      </x:c>
     </x:row>
     <x:row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A216" s="0" t="s">
@@ -15681,12 +14601,6 @@
       <x:c r="L216" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M216" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N216" s="0" t="s">
-        <x:v>1959</x:v>
-      </x:c>
     </x:row>
     <x:row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A217" s="0" t="s">
@@ -15725,12 +14639,6 @@
       <x:c r="L217" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M217" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N217" s="0" t="s">
-        <x:v>1957</x:v>
-      </x:c>
     </x:row>
     <x:row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A218" s="0" t="s">
@@ -15769,12 +14677,6 @@
       <x:c r="L218" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M218" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N218" s="0" t="s">
-        <x:v>1947</x:v>
-      </x:c>
     </x:row>
     <x:row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A219" s="0" t="s">
@@ -15813,12 +14715,6 @@
       <x:c r="L219" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="M219" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N219" s="0" t="s">
-        <x:v>1964</x:v>
-      </x:c>
     </x:row>
     <x:row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A220" s="0" t="s">
@@ -15857,12 +14753,6 @@
       <x:c r="L220" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M220" s="0" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="N220" s="0" t="s">
-        <x:v>1966</x:v>
-      </x:c>
     </x:row>
     <x:row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A221" s="0" t="s">
@@ -15901,12 +14791,6 @@
       <x:c r="L221" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M221" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N221" s="0" t="s">
-        <x:v>1958</x:v>
-      </x:c>
     </x:row>
     <x:row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A222" s="0" t="s">
@@ -15945,12 +14829,6 @@
       <x:c r="L222" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="M222" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="N222" s="0" t="s">
-        <x:v>1803</x:v>
-      </x:c>
     </x:row>
     <x:row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A223" s="0" t="s">
@@ -15988,12 +14866,6 @@
       </x:c>
       <x:c r="L223" s="0" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="M223" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="N223" s="0" t="s">
-        <x:v>1962</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
+++ b/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
@@ -5426,139 +5426,520 @@
     <x:t>Builds custom advanced manufacturing systems with a focus on high-speed assembly, test, and inspection of automotive electronics components</x:t>
   </x:si>
   <x:si>
-    <x:t>Manufactures automotive wire harnesses and sensors, indicating in-house test/quality control functions that require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Site explicitly lists 'testing' as a core capability alongside design and manufacturing of electronics, indicating in-house test engineers.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Automotive supplier of seating and electrical systems; no clear evidence of in-house electronic test or R&amp;D labs that would use oscilloscopes or similar equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No clear evidence of in-house electronic test or measurement work, just metal foil processing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>States parts undergo advanced testing (vibration, thermal shock) but unclear if they have in-house labs or just resell sensors; no explicit engineering/R&amp;D team mentioned.</x:t>
+    <x:t>They are a global leader in research, development, and delivery of vehicle power and data solutions, producing wire harnesses, sensors, and driver information systems, which implies in-house engineering and manufacturing requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states expertise in design, manufacturing, and testing of advanced electronics, indicating a need for test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 403 Forbidden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform advanced post-production testing on their parts, including chemical resistance, vibration, and thermal shock, indicating an in-house quality and testing function.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company manufactures metal foils for shielding and thermal management in electronic applications, but there is no clear evidence of in-house electronic testing or engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>As a manufacturer of electronic automotive components, they would have in-house engineering and quality control teams that use test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch)</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: HTTP 301 Moved Permanently</x:t>
   </x:si>
   <x:si>
-    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures electronic components like voltage regulators and rectifiers, implying in-house production testing with equipment like oscilloscopes or power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: HTTP 403 Forbidden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures LED lighting and smart trailer systems, implying in-house electronics R&amp;D and testing.</x:t>
+    <x:t>The company states it is a global leader in the development and manufacturing of innovative LED lighting and safety systems, indicating in-house engineering and production that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in the repair, refurbishment, and remanufacturing of automotive electronic modules, which requires in-house diagnostic and testing capabilities.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company states they are a manufacturer of high-performance mobile electronics and have been crafting products for decades, implying in-house design, manufacturing, and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The site mentions 'driving innovation' and 'brands' of finished electronic products, but lacks clear evidence of in-house engineering, R&amp;D, manufacturing, or repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company primarily installs and resells finished automotive electronic products, with no clear evidence of current in-house engineering, manufacturing, or complex electronic hardware diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-house repair, diagnostics, and calibration of electronic instrument clusters and other vehicle electronics, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop, design, and manufacture automotive wiring harnesses and electronic components, indicating in-house engineering and R&amp;D that would use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company manufactures custom-engineered solutions, including sensors and electrical components, and has dedicated engineering facilities, indicating in-house testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a developer and manufacturer of automotive and electronic components, indicating in-house engineering and production testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company sells finished electronic products for vehicles and mentions patented technology, but there is no clear evidence of in-house engineering, R&amp;D, or repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and sell an electronic product, but there is no explicit mention of in-house engineering, R&amp;D, manufacturing, or testing facilities that would use test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (Authentication failed because the remote party sent a TLS alert: 'ProtocolVersion'.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They state they are an innovator in designing and engineering vehicle electronics and components, indicating in-house R&amp;D and manufacturing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house diagnostics and calibration of vehicle electronic systems, which requires test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop and produce stamped and plated electrical connectors, indicating in-house engineering and manufacturing that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform repair, remanufacturing, calibration, and re-qualification testing of automotive electronics, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer developing and engineering automotive electronic components, which implies in-house R&amp;D and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an upfitter installing electronics, but the text does not indicate in-house engineering, diagnostics, or repair of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly mentions R&amp;D for autonomous driving, advanced driver-assist, and in-vehicle infotainment systems, indicating in-house engineering and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs remanufacturing, engineering, innovation, and calibration of automotive electronic components, indicating in-house testing and diagnostic needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch, RemoteCertificateChainErrors)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The scraped website content was unreadable and insufficient to make a determination.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They emphasize 'deep engineering expertise' and 'design, development, and manufacture' of advanced lighting and electronics systems, indicating in-house R&amp;D and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states they perform in-house design, engineering, prototype development, and rigorous testing of their wire harnesses.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company sells and equips vehicles with aftermarket electronic accessories, but there is no evidence of in-house engineering, R&amp;D, or repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stoneridge designs and manufactures highly engineered electrical and electronic systems, including new ECU technology and advanced vision systems, indicating in-house engineering and R&amp;D.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EEPod develops advanced vehicle diagnostic tools and ECU test/reprogramming stations, explicitly targeting automotive engineers for vehicle development, diagnostics, testing, and reprogramming workflows.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They sell plug-and-play electronic kits, but there is no clear evidence of in-house engineering, R&amp;D, or repair work requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform thorough testing, reprogramming, flashing, and tuning of electronic control modules, indicating in-house diagnostic and engineering work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company manufactures mechanical automotive components and mentions 'precision-engineered solutions', but there is no explicit mention of electronic hardware, R&amp;D, or testing functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in remanufacturing and repair of automotive electronic components and systems, indicating a need for diagnostic and test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in vehicle electronics installation, but it's unclear if they perform component-level diagnostics or repair requiring test equipment, or if they only install finished units.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house development and updates to their 'tuning and electronics' and conduct extensive testing, including '80 dyno pulls' and 'our findings', indicating a need for diagnostic and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NAL develops and manufactures automotive lighting systems, hires engineers and technicians, and focuses on innovative lighting technology, indicating a need for electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states they are involved in "automotive electronics engineering" and are a "manufacturer" of their products, indicating in-house design and production.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop advanced electronic systems like Vision &amp; Radar Systems, Advanced Sensors &amp; Mechatronics, and new control devices, indicating in-house engineering and R&amp;D requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company specializes in the development and testing of LED lighting solutions at its tech centers and performs in-house manufacturing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house electronics manufacturing, PCB assembly, engineering, and system integration from prototype to production.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>As a Tier One automotive supplier creating components and systems, they likely have in-house engineering and manufacturing requiring electronic test and measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company has R&amp;D facilities and mentions in-house innovation, design, and advanced electronics for their control systems and components, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They operate as a satellite design and development center and are a global leader in electrical components manufacturing, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is driven by engineering, has vertically integrated electronic manufacturing capabilities, and a continuous flow of new product introductions, indicating in-house R&amp;D and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house development of OBD tuning solutions and influence vehicle electronics and hardware through automotive engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are involved in engineering and manufacturing automotive systems and mechatronics, and have a Technical Center, indicating in-house electronic hardware development and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an automotive supplier with manufacturing operations and product development and engineering centers, indicating in-house electronic hardware development and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Page body was empty after parsing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They have an extensive team of engineers and technicians who perform rigorous testing and development of new electrical products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture intelligent controls, electronics, software, and brushless DC motors, indicating in-house engineering and development.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in conceiving and engineering proprietary electronic sensor and control systems, indicating in-house R&amp;D and development.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ampere EV performs in-house design, engineering, testing, and calibration of electronic hardware for their EV powertrain systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (Received an unexpected EOF or 0 bytes from the transport stream.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company specializes in repair and remanufacturing of electronic instrument clusters, including odometer programming, indicating in-house diagnostic and repair work on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They remanufacture high-precision automotive components, which may involve some electronic testing or diagnostics, but the text primarily focuses on mechanical aspects.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company provides technical resources and support for installing vehicle electronics, but there is no clear evidence of in-house hardware engineering, R&amp;D, or repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They primarily upfit, sell, and install finished public safety vehicle equipment, with no clear evidence of in-house electronic hardware engineering, R&amp;D, or component-level repair.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states they have "expert in-house engineers" committed to innovation and seamless integration of automotive technology, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states "Automotive Lighting Design and Manufacturing" and describes advanced manufacturing processes for electronic lighting products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a trade association focused on software and data standards for automotive OTA, with no clear evidence of in-house hardware engineering or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a full-service manufacturer with explicit 'Engineering' and 'Testing' capabilities for electronic and electromechanical components.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop and integrate plastic components with control units and power electronics, indicating in-house engineering and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs advanced testing, precision control with real-time current monitoring, and engineering implementation for their digitally-switched power systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture automotive semiconductors and engine control units, which requires significant in-house electronic engineering and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: HTTP 406 Not Acceptable</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They sell automotive accessories, including a precision pressure gauge, but there is no evidence of in-house electronic engineering, R&amp;D, or testing requiring specialized electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide a platform for electronics manufacturing optimization and defect detection, but it's unclear if their own staff performs in-house hardware testing or repair.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is a wholesale distributor of automotive parts and chemicals, which may include some electronic components, but there is no clear evidence of in-house engineering or diagnostic work on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is a wholesale distributor of automotive parts with no visible evidence of in-house electronic engineering, testing, or repair functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company develops automotive tools and offers 'Test Products' and 'Service Equipment', but it's unclear if this involves electronic hardware engineering or just mechanical testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop and engineer mechatronics products and actuators, utilizing simulation, prototyping, and extensive R&amp;D, indicating a need for electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They create innovative, next-generation electronic products and new technologies, indicating in-house engineering and R&amp;D that would use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Putco designs and manufactures automotive LED lighting and accessories, indicating in-house engineering and manufacturing that would require electronic test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company focuses on metal wool and fiber technology for automotive and industrial applications, with R&amp;D experts, but no clear indication of electronic hardware engineering or testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in vintage vehicles and climate control systems, which may involve some electrical diagnostics, but there is no clear evidence of in-house electronic hardware engineering or component-level repair.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company primarily deals with automotive chemicals, but their Petra Cares initiative trains individuals in auto repair, which may involve some electronic diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (omron.com:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They sell automotive batteries and mention 'Strategic Global Sourcing &amp; Rigorous Quality Control' but it's unclear if this involves in-house electronic testing or just supplier vetting.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop, engineer, and manufacture their own LED emergency vehicle lighting products, indicating in-house electronic design and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design, engineer, and manufacture their own Bluetooth-enabled transmission control units and custom harnesses in-house.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide engineering and prototyping services to create testable designs, indicating in-house electronic development and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company manufactures electronic brake and safety systems and electronic controls, indicating in-house production and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They have an R&amp;D team working on 'automotive technology' for chemical additives, but it's unclear if this involves in-house testing or diagnostics of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer custom design, manufacturing support, and private label solutions for automotive equipment, indicating in-house engineering and development.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They mention 'Power Engineering' and 'prototype optimization' but their primary focus is structural automotive components, making electronic hardware testing unclear.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house design, development, manufacture, and R&amp;D of electronic solutions for the automotive industry.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (shinko.co.jp:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They install and program finished electronic accessories, but there is no clear evidence of in-house engineering, R&amp;D, or component-level diagnostics requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company engages in innovation, design, and manufacturing of proprietary electrical solutions, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer Engineering &amp; Design Services and have an Engineering Manager, indicating in-house engineering and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TTM Technologies manufactures complex electronic components like PCBs and RF assemblies, indicating in-house engineering, R&amp;D, and manufacturing that require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an electronic components manufacturer's representative, providing solutions by connecting customers with components, with no visible in-house engineering or test function.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITW is a global multi-industry manufacturing leader that designs and innovates industrial products and mechatronics, indicating a need for in-house engineering and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They sell 'LIKE NEW' and 'USED' diagnostic equipment, implying refurbishment and testing, and offer 'Custom Test Leads' which suggests in-house design/testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Safari Circuits provides end-to-end engineering services, advanced manufacturing, and rapid prototyping for electronic circuit design and assembly, which requires test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company states they are 'Investing in Innovation' and 'Bringing Innovative Technologies to Market', indicating in-house R&amp;D and engineering functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide coating services for PCBs and develop coating processes, but the text does not explicitly indicate in-house electronic hardware design, functional testing, or diagnostics requiring advanced test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-house design, engineering, prototyping, testing, troubleshooting, and repair of electronic circuits and products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: Error while copying content to a stream. (The response ended prematurely. (ResponseEnded))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is an EMS provider performing PCB assembly, box-builds, and electro-mechanical assembly, with processes like SPI/AOI and prototype board manufacturing, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly mentions R&amp;D, manufacturing, engineering, and repair/reconditioning of electronic control systems, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is a distributor and supply chain solutions provider for electronic components, with no clear evidence of in-house engineering, R&amp;D, manufacturing, or repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>As a manufacturer of printed circuit boards, they clearly have in-house engineering and quality control functions that require electronic test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and build highly engineered electronic connectors and receptacles for critical applications, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer powertrain calibration and embedded systems development, indicating a need for electronic test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a contract electronics manufacturer that performs in-circuit testing, functional testing, and burn-in testing on PCB assemblies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (Authentication failed because the remote party sent a TLS alert: 'HandshakeFailure'.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (hosiden.com:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (foster-electric.com:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cohu designs and manufactures semiconductor test equipment and ATE platforms, indicating in-house engineering and R&amp;D that would use test and measurement gear.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer sales representative providing technical sales and engineering support, but it's unclear if they perform in-house hardware testing or R&amp;D.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They state they develop all their products from the ground up and perform extensive testing tailored to specific application requirements.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QMS is an Electronics Manufacturing Services provider offering in-house engineering, manufacturing, testing, DFT, and repair depot services.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PalPilot provides integrated engineering and manufacturing solutions for PCBs, interconnects, and semiconductors, including design, DFM, and prototype to production support, indicating in-house testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They supply mechanical components and assemblies to electronic industries, but it's unclear if their in-house engineering team performs electronic hardware testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Methode designs, engineers, develops, and manufactures custom mechatronic and electronic products, with mentions of R&amp;D departments and laboratories.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toshiba is involved in R&amp;D, design, and manufacturing of semiconductors, power electronics, and other advanced electronic products, including operating a research laboratory.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide engineering R&amp;D support services to electronics design companies, but it's unclear if they perform in-house testing or design themselves.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectroCraft provides application-engineered custom OEM solutions for motors and motion control products, explicitly stating they have deep engineering resources and design experience.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an electronic contract manufacturer that explicitly offers design, prototyping, PCBA manufacturing, system assembly, repairs, rework, and 'Testing &amp; Quality Assurance' services.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company provides contract manufacturing and engineering services, including design, prototyping, and R&amp;D for electronic components like sensors and connectors.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nidec manufactures a wide range of electronic devices and automotive components, and mentions 'Smart Factory' and 'Inspection and measuring equipment', indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ark Electronics offers design engineering, PCBA manufacturing, and develops custom electronic modules, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sanmina provides design and engineering, test system development, manufacturing, and repair services for electronic systems, indicating a clear need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform electronic design, PCB layout, R&amp;D, and electronic manufacturing, including DV and PPAP builds, all of which require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a component supplier with staff having engineering backgrounds, but they outsource quality testing to external labs rather than performing in-house hardware diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They conduct rigorous performance testing, engineering, and analytical testing of their proprietary PCB materials.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house electronic design, hardware re-engineering, rapid prototyping, calibration, and diagnostics, including EMI/EMC pre-screening.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>While they manufacture electronic audio devices, the website content is entirely consumer-facing and does not show evidence of in-house engineering, R&amp;D, or testing labs that would use test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide Electronic Manufacturing Services (EMS) including PCB assembly, prototype development, and production, indicating in-house engineering and manufacturing that requires test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer engineering services including design, prototyping, and testing, and perform quality control for electronics manufacturing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a contract electronics manufacturer building PCBA, wire harnesses, and cable assemblies, which requires in-house testing and quality control.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs electronic equipment design, development, manufacturing, assembly, and reverse-engineering, all of which require in-house test and measurement capabilities.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corelis develops and sells hardware and software for embedded hardware testing, debugging, and programming, indicating strong in-house engineering and test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company provides turnkey design, engineering, and manufacturing services for electronic solutions and sub-assemblies, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide additive manufacturing solutions for applications like power electronics, but the website does not show clear evidence of in-house electronic hardware testing or diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company offers electronic design and circuit board assembly services, explicitly mentioning "Advanced Test Engineering" and "Engineering and NPI" in their services.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company develops and manufactures advanced nano coatings for PCBs, mentioning in-house engineering teams, R&amp;D, and concerns like signal integrity and accurate signal monitoring.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer's representative providing technical expertise and product distribution, but there is no clear evidence of in-house electronic hardware engineering, R&amp;D, or testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CheckSum designs and engineers complex automated test systems and fixtures, indicating in-house engineering and manufacturing that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BPM Microsystems designs and manufactures automated device programming solutions, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an "Engineering Driven Manufacturer" of custom electro-mechanical assemblies and wire harnesses for the electronics, medical, and analytical instrumentation industries, implying in-house testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kyocera AVX is a global manufacturer of advanced electronic components with in-house research, development, engineering, and manufacturing facilities, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company specializes in automotive audio/visual electronics and consumer goods, but the scraped content does not clearly indicate in-house engineering, R&amp;D, or repair work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide advanced electronics manufacturing services, including NPI, prototyping, and engineering services, which require in-house testing and measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop and launch new coating equipment and upgrade existing series, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They engineer, manufacture, and rigorously test custom magnetics and electronic assemblies, including thermal shock, dielectric, and corona testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer electrical assembly services backed by extensive testing protocols, indicating in-house electronic testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lectronix performs in-house hardware engineering, product development, PCB assembly, and functional testing for complex electronic systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a PCB manufacturer with in-house engineering, prototype development, DFM feedback, and advanced manufacturing processes that require testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sheldahl designs and develops flexible circuits and electronic materials, employs engineers, and has a Director of Innovation and Technology, indicating in-house R&amp;D and manufacturing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer PCB design, electronics manufacturing services, and have in-house hardware experts, PCB designers, and technicians who would use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HED designs and engineers their own electronic control systems and states they have engineers who provide solutions, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture flexible circuits, which implies in-house engineering and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company offers electronic design, PCB design, PCB assembly, design for test, and electronics testing services, indicating in-house engineering and test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: No connection could be made because the target machine actively refused it. (jebconet.com:443) (No connection could be made because the target machine actively refused it.)</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Request timed out after 15s</x:t>
   </x:si>
   <x:si>
-    <x:t>Repair and refurbishment of automotive electronic control units likely requires in-house use of test equipment like oscilloscopes and power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped content shows product categories but no evidence of in-house engineering or test lab; they design/integrate automotive electronics but it's unclear if they own test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Only consumer-facing sales of finished car audio products visible; no evidence of in-house engineering, R&amp;D, or test labs on this page.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: HTTP 429 Too Many Requests</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Performs in-house repair and calibration of electronic instrument clusters, PCMs, and modules, requiring electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house design, development, and manufacturing of automotive electronics and wiring harnesses likely requires test equipment for validation and quality assurance.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: HTTP 520 &lt;none&gt;</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Installs finished auto electronics (alarms, audio) with no evidence of in-house engineering, testing, or repair that requires T&amp;M equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Site suggests product development but no clear evidence of in-house engineering or test hardware usage.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Manufactures electronic automotive parts (sensors, engine management) at their engineering and manufacturing facilities, indicating in-house R&amp;D and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>In-house manufacturing and development of electronic components like wire harnesses and battery sensors requires R&amp;D and test equipment such as oscilloscopes and power supplies.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Performs in-house repair, remanufacturing, calibration, and testing of automotive electronics, indicating use of test equipment like oscilloscopes and signal generators.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, develop, and manufacture automotive electronics, ECUs, and provide testing services; their MxSuite integrates with test equipment, indicating in-house use of measurement gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Primarily installs finished electronic components into vehicles, with no visible in-house engineering or test lab for electronic diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Provides vehicle electronics diagnostics and calibration services, but not clear if they use general-purpose test equipment; likely uses specialized automotive tools.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They remanufacture electronic control modules and perform calibration, indicating in-house test and diagnostic work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Site shows they design and sell automotive performance electronics but no clear evidence of in-house engineering lab or test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch, RemoteCertificateChainErrors)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Develops and produces connectors; development may involve testing, but no explicit test/engineering lab or equipment use is evident.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTCA R&amp;D center develops ADAS and infotainment systems, and manufacturing includes hybrid battery modules, indicating in-house electronic testing and calibration.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: An error occurred while sending the request. (The response ended prematurely. (ResponseEnded))</x:t>
-  </x:si>
-  <x:si>
-    <x:t>U.S. manufacturer of electronic control systems; likely has in-house R&amp;D/engineering that uses test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Designs and manufactures electronic systems, implying in-house R&amp;D and testing that requires test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scraped text shows deep engineering expertise and custom manufacturing, suggesting in-house electronic design and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: HTTP 502 Bad Gateway</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sells pre-programmed automotive control modules and offers reprogramming, but no clear evidence of in-house engineering or hardware-level diagnostics requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FlexStation-IOT ECU test station and custom ECU development indicate in-house hardware engineering likely using test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Describes in-house engineering and manufacturing of automotive electronics, implying need for test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Primarily mechanical component manufacturer; no evidence of in-house electronics testing or R&amp;D requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Installs finished vehicle electronics, no visible engineering or test function.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Primarily resells and installs aftermarket automotive accessories, no indication of in-house engineering or testing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Automotive lighting manufacturer with in-house engineering and R&amp;D, likely using test equipment for design and validation of electronic lighting components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Page body was empty after parsing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Cancelled by user</x:t>
+    <x:t>They are a sales representative for electronic components with a staff of sales professionals, showing no evidence of in-house engineering or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide remanufacturing and repair solutions for automotive and consumer electronics, which requires in-house diagnostics and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide digital optical inspection systems used in the electronics industry, but there is no clear evidence of their own in-house electronic hardware engineering or test function.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kelco Industries designs and manufactures custom-engineered electronic components and assemblies, with in-house engineering expertise and dedicated testing labs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Network error: No such host is known. (flex.com:443) (No such host is known.)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design, build, and debug custom automated systems for testing and inspection of automotive electronics, indicating in-house engineering and test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unigen performs in-house design, engineering, prototyping, PCB assembly &amp; test, and offers "Test-as-a-Service" for complex electronic products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture their own radar detectors, indicating in-house engineering, R&amp;D, and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide manufacturing services for electronic assemblies, semiconductors, and micro-components, which implies in-house electronic testing and measurement.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -6931,10 +7312,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M24" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N24" s="0" t="s">
-        <x:v>1805</x:v>
+        <x:v>1804</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -6975,7 +7356,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M25" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N25" s="0" t="s">
         <x:v>1803</x:v>
@@ -7022,7 +7403,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N26" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1805</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -7066,7 +7447,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N27" s="0" t="s">
-        <x:v>1811</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -7110,7 +7491,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N28" s="0" t="s">
-        <x:v>1808</x:v>
+        <x:v>1806</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -7154,7 +7535,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>1810</x:v>
+        <x:v>1809</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -7242,7 +7623,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N31" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1808</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -7286,7 +7667,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1810</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -7330,7 +7711,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N33" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -7371,10 +7752,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M34" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>1814</x:v>
+        <x:v>1811</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -7418,7 +7799,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N35" s="0" t="s">
-        <x:v>1813</x:v>
+        <x:v>1812</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -7462,7 +7843,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
-        <x:v>1819</x:v>
+        <x:v>1813</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -7503,7 +7884,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
-        <x:v>1816</x:v>
+        <x:v>1814</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -7547,7 +7928,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N38" s="0" t="s">
-        <x:v>1817</x:v>
+        <x:v>1815</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -7591,7 +7972,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N39" s="0" t="s">
-        <x:v>1821</x:v>
+        <x:v>1816</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -7635,7 +8016,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>1820</x:v>
+        <x:v>1818</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -7679,7 +8060,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N41" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1808</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -7717,10 +8098,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M42" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N42" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1819</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -7764,7 +8145,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>1822</x:v>
+        <x:v>1817</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -7805,10 +8186,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M44" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>1826</x:v>
+        <x:v>1822</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -7849,10 +8230,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M45" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1821</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -7893,7 +8274,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>1825</x:v>
+        <x:v>1826</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -7934,10 +8315,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M47" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N47" s="0" t="s">
-        <x:v>1824</x:v>
+        <x:v>1820</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -7978,10 +8359,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M48" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>1830</x:v>
+        <x:v>1823</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -8019,10 +8400,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M49" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N49" s="0" t="s">
-        <x:v>1828</x:v>
+        <x:v>1825</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -8063,7 +8444,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N50" s="0" t="s">
-        <x:v>1823</x:v>
+        <x:v>1824</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -8107,7 +8488,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>1827</x:v>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -8151,7 +8532,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>1831</x:v>
+        <x:v>1827</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -8195,7 +8576,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N53" s="0" t="s">
-        <x:v>1811</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -8236,10 +8617,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M54" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N54" s="0" t="s">
-        <x:v>1833</x:v>
+        <x:v>1830</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -8283,7 +8664,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N55" s="0" t="s">
-        <x:v>1842</x:v>
+        <x:v>1833</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -8324,7 +8705,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>1835</x:v>
+        <x:v>1831</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -8368,7 +8749,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N57" s="0" t="s">
-        <x:v>1811</x:v>
+        <x:v>1829</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -8456,7 +8837,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N59" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1843</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -8497,7 +8878,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M60" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N60" s="0" t="s">
         <x:v>1832</x:v>
@@ -8541,7 +8922,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N61" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1820</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -8579,7 +8960,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M62" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N62" s="0" t="s">
         <x:v>1837</x:v>
@@ -8664,10 +9045,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M64" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1836</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -8711,7 +9092,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>1838</x:v>
+        <x:v>1835</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -8755,7 +9136,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N66" s="0" t="s">
-        <x:v>1840</x:v>
+        <x:v>1838</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -8795,6 +9176,12 @@
       <x:c r="L67" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M67" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N67" s="0" t="s">
+        <x:v>1841</x:v>
+      </x:c>
     </x:row>
     <x:row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A68" s="0" t="s">
@@ -8834,10 +9221,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M68" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1839</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -8881,7 +9268,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>1841</x:v>
+        <x:v>1840</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -8922,10 +9309,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N70" s="0" t="s">
-        <x:v>1836</x:v>
+        <x:v>1847</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -8969,7 +9356,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N71" s="0" t="s">
-        <x:v>1843</x:v>
+        <x:v>1842</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -9009,6 +9396,12 @@
       <x:c r="L72" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M72" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N72" s="0" t="s">
+        <x:v>1844</x:v>
+      </x:c>
     </x:row>
     <x:row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A73" s="0" t="s">
@@ -9048,10 +9441,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M73" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N73" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -9091,6 +9484,12 @@
       <x:c r="L74" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M74" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N74" s="0" t="s">
+        <x:v>1846</x:v>
+      </x:c>
     </x:row>
     <x:row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A75" s="0" t="s">
@@ -9129,6 +9528,12 @@
       <x:c r="L75" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M75" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N75" s="0" t="s">
+        <x:v>1848</x:v>
+      </x:c>
     </x:row>
     <x:row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A76" s="0" t="s">
@@ -9167,6 +9572,12 @@
       <x:c r="L76" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M76" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N76" s="0" t="s">
+        <x:v>1850</x:v>
+      </x:c>
     </x:row>
     <x:row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A77" s="0" t="s">
@@ -9206,10 +9617,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M77" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N77" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1851</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -9249,6 +9660,12 @@
       <x:c r="L78" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M78" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N78" s="0" t="s">
+        <x:v>1853</x:v>
+      </x:c>
     </x:row>
     <x:row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A79" s="0" t="s">
@@ -9287,6 +9704,12 @@
       <x:c r="L79" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M79" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N79" s="0" t="s">
+        <x:v>1849</x:v>
+      </x:c>
     </x:row>
     <x:row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A80" s="0" t="s">
@@ -9325,6 +9748,12 @@
       <x:c r="L80" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M80" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N80" s="0" t="s">
+        <x:v>1852</x:v>
+      </x:c>
     </x:row>
     <x:row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A81" s="0" t="s">
@@ -9363,6 +9792,12 @@
       <x:c r="L81" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M81" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N81" s="0" t="s">
+        <x:v>1863</x:v>
+      </x:c>
     </x:row>
     <x:row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A82" s="0" t="s">
@@ -9405,7 +9840,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N82" s="0" t="s">
-        <x:v>1844</x:v>
+        <x:v>1854</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -9449,7 +9884,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N83" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1803</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -9489,6 +9924,12 @@
       <x:c r="L84" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M84" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N84" s="0" t="s">
+        <x:v>1855</x:v>
+      </x:c>
     </x:row>
     <x:row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A85" s="0" t="s">
@@ -9524,6 +9965,12 @@
       <x:c r="L85" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M85" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N85" s="0" t="s">
+        <x:v>1856</x:v>
+      </x:c>
     </x:row>
     <x:row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A86" s="0" t="s">
@@ -9562,6 +10009,12 @@
       <x:c r="L86" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M86" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N86" s="0" t="s">
+        <x:v>1858</x:v>
+      </x:c>
     </x:row>
     <x:row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A87" s="0" t="s">
@@ -9597,6 +10050,12 @@
       <x:c r="L87" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M87" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N87" s="0" t="s">
+        <x:v>1862</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A88" s="0" t="s">
@@ -9633,10 +10092,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M88" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N88" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1861</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -9674,10 +10133,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M89" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N89" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1860</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -9715,10 +10174,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M90" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N90" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1857</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -9756,10 +10215,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M91" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N91" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1864</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -9797,10 +10256,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M92" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N92" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1865</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -9841,10 +10300,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M93" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N93" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1866</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -9888,7 +10347,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N94" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1859</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -9929,10 +10388,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M95" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N95" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -9976,7 +10435,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N96" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1829</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -10017,10 +10476,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M97" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N97" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1868</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -10061,10 +10520,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M98" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N98" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1873</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -10105,10 +10564,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M99" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N99" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1869</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -10149,10 +10608,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M100" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N100" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1867</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -10193,10 +10652,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M101" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N101" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1875</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -10237,10 +10696,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M102" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N102" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1872</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -10281,10 +10740,10 @@
         <x:v>855</x:v>
       </x:c>
       <x:c r="M103" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N103" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1874</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -10325,10 +10784,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M104" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N104" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1876</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -10368,6 +10827,12 @@
       <x:c r="L105" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M105" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N105" s="0" t="s">
+        <x:v>1879</x:v>
+      </x:c>
     </x:row>
     <x:row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A106" s="0" t="s">
@@ -10406,6 +10871,12 @@
       <x:c r="L106" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M106" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N106" s="0" t="s">
+        <x:v>1871</x:v>
+      </x:c>
     </x:row>
     <x:row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A107" s="0" t="s">
@@ -10444,6 +10915,12 @@
       <x:c r="L107" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M107" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N107" s="0" t="s">
+        <x:v>1878</x:v>
+      </x:c>
     </x:row>
     <x:row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A108" s="0" t="s">
@@ -10482,6 +10959,12 @@
       <x:c r="L108" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M108" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N108" s="0" t="s">
+        <x:v>1877</x:v>
+      </x:c>
     </x:row>
     <x:row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A109" s="0" t="s">
@@ -10520,6 +11003,12 @@
       <x:c r="L109" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M109" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N109" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A110" s="0" t="s">
@@ -10558,6 +11047,12 @@
       <x:c r="L110" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M110" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N110" s="0" t="s">
+        <x:v>1884</x:v>
+      </x:c>
     </x:row>
     <x:row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A111" s="0" t="s">
@@ -10596,6 +11091,12 @@
       <x:c r="L111" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M111" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N111" s="0" t="s">
+        <x:v>1881</x:v>
+      </x:c>
     </x:row>
     <x:row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A112" s="0" t="s">
@@ -10634,6 +11135,12 @@
       <x:c r="L112" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M112" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N112" s="0" t="s">
+        <x:v>1880</x:v>
+      </x:c>
     </x:row>
     <x:row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A113" s="0" t="s">
@@ -10672,6 +11179,12 @@
       <x:c r="L113" s="0" t="s">
         <x:v>855</x:v>
       </x:c>
+      <x:c r="M113" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N113" s="0" t="s">
+        <x:v>1889</x:v>
+      </x:c>
     </x:row>
     <x:row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A114" s="0" t="s">
@@ -10710,6 +11223,12 @@
       <x:c r="L114" s="0" t="s">
         <x:v>855</x:v>
       </x:c>
+      <x:c r="M114" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N114" s="0" t="s">
+        <x:v>1882</x:v>
+      </x:c>
     </x:row>
     <x:row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A115" s="0" t="s">
@@ -10748,6 +11267,12 @@
       <x:c r="L115" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M115" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N115" s="0" t="s">
+        <x:v>1891</x:v>
+      </x:c>
     </x:row>
     <x:row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A116" s="0" t="s">
@@ -10786,6 +11311,12 @@
       <x:c r="L116" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M116" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N116" s="0" t="s">
+        <x:v>1854</x:v>
+      </x:c>
     </x:row>
     <x:row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A117" s="0" t="s">
@@ -10824,6 +11355,12 @@
       <x:c r="L117" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M117" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N117" s="0" t="s">
+        <x:v>1890</x:v>
+      </x:c>
     </x:row>
     <x:row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A118" s="0" t="s">
@@ -10859,6 +11396,12 @@
       <x:c r="L118" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M118" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N118" s="0" t="s">
+        <x:v>1885</x:v>
+      </x:c>
     </x:row>
     <x:row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A119" s="0" t="s">
@@ -10897,6 +11440,12 @@
       <x:c r="L119" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M119" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N119" s="0" t="s">
+        <x:v>1886</x:v>
+      </x:c>
     </x:row>
     <x:row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A120" s="0" t="s">
@@ -10935,6 +11484,12 @@
       <x:c r="L120" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M120" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N120" s="0" t="s">
+        <x:v>1888</x:v>
+      </x:c>
     </x:row>
     <x:row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A121" s="0" t="s">
@@ -10973,6 +11528,12 @@
       <x:c r="L121" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M121" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N121" s="0" t="s">
+        <x:v>1887</x:v>
+      </x:c>
     </x:row>
     <x:row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A122" s="0" t="s">
@@ -11008,6 +11569,12 @@
       <x:c r="L122" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M122" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N122" s="0" t="s">
+        <x:v>1883</x:v>
+      </x:c>
     </x:row>
     <x:row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A123" s="0" t="s">
@@ -11043,6 +11610,12 @@
       <x:c r="L123" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M123" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N123" s="0" t="s">
+        <x:v>1900</x:v>
+      </x:c>
     </x:row>
     <x:row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A124" s="0" t="s">
@@ -11081,6 +11654,12 @@
       <x:c r="L124" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M124" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N124" s="0" t="s">
+        <x:v>1895</x:v>
+      </x:c>
     </x:row>
     <x:row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A125" s="0" t="s">
@@ -11116,6 +11695,12 @@
       <x:c r="L125" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M125" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N125" s="0" t="s">
+        <x:v>1894</x:v>
+      </x:c>
     </x:row>
     <x:row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A126" s="0" t="s">
@@ -11152,10 +11737,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M126" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N126" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1892</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:14" x14ac:dyDescent="0.25">
@@ -11195,6 +11780,12 @@
       <x:c r="L127" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M127" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N127" s="0" t="s">
+        <x:v>1903</x:v>
+      </x:c>
     </x:row>
     <x:row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A128" s="0" t="s">
@@ -11233,6 +11824,12 @@
       <x:c r="L128" s="0" t="s">
         <x:v>855</x:v>
       </x:c>
+      <x:c r="M128" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N128" s="0" t="s">
+        <x:v>1898</x:v>
+      </x:c>
     </x:row>
     <x:row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A129" s="0" t="s">
@@ -11271,6 +11868,12 @@
       <x:c r="L129" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M129" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N129" s="0" t="s">
+        <x:v>1897</x:v>
+      </x:c>
     </x:row>
     <x:row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A130" s="0" t="s">
@@ -11309,6 +11912,12 @@
       <x:c r="L130" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M130" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N130" s="0" t="s">
+        <x:v>1899</x:v>
+      </x:c>
     </x:row>
     <x:row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A131" s="0" t="s">
@@ -11348,10 +11957,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M131" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N131" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1896</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -11391,6 +12000,12 @@
       <x:c r="L132" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M132" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N132" s="0" t="s">
+        <x:v>1901</x:v>
+      </x:c>
     </x:row>
     <x:row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A133" s="0" t="s">
@@ -11429,6 +12044,12 @@
       <x:c r="L133" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M133" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N133" s="0" t="s">
+        <x:v>1893</x:v>
+      </x:c>
     </x:row>
     <x:row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A134" s="0" t="s">
@@ -11467,6 +12088,12 @@
       <x:c r="L134" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M134" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N134" s="0" t="s">
+        <x:v>1902</x:v>
+      </x:c>
     </x:row>
     <x:row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A135" s="0" t="s">
@@ -11505,6 +12132,12 @@
       <x:c r="L135" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M135" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N135" s="0" t="s">
+        <x:v>1905</x:v>
+      </x:c>
     </x:row>
     <x:row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A136" s="0" t="s">
@@ -11543,6 +12176,12 @@
       <x:c r="L136" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M136" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N136" s="0" t="s">
+        <x:v>1807</x:v>
+      </x:c>
     </x:row>
     <x:row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A137" s="0" t="s">
@@ -11581,6 +12220,12 @@
       <x:c r="L137" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M137" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N137" s="0" t="s">
+        <x:v>1908</x:v>
+      </x:c>
     </x:row>
     <x:row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A138" s="0" t="s">
@@ -11619,6 +12264,12 @@
       <x:c r="L138" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M138" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N138" s="0" t="s">
+        <x:v>1910</x:v>
+      </x:c>
     </x:row>
     <x:row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A139" s="0" t="s">
@@ -11658,10 +12309,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M139" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N139" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1912</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -11701,6 +12352,12 @@
       <x:c r="L140" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M140" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N140" s="0" t="s">
+        <x:v>1916</x:v>
+      </x:c>
     </x:row>
     <x:row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A141" s="0" t="s">
@@ -11739,6 +12396,12 @@
       <x:c r="L141" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M141" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N141" s="0" t="s">
+        <x:v>1904</x:v>
+      </x:c>
     </x:row>
     <x:row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A142" s="0" t="s">
@@ -11778,10 +12441,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M142" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N142" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1911</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -11821,6 +12484,12 @@
       <x:c r="L143" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M143" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N143" s="0" t="s">
+        <x:v>1907</x:v>
+      </x:c>
     </x:row>
     <x:row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A144" s="0" t="s">
@@ -11859,6 +12528,12 @@
       <x:c r="L144" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M144" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N144" s="0" t="s">
+        <x:v>1906</x:v>
+      </x:c>
     </x:row>
     <x:row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A145" s="0" t="s">
@@ -11897,6 +12572,12 @@
       <x:c r="L145" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M145" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N145" s="0" t="s">
+        <x:v>1909</x:v>
+      </x:c>
     </x:row>
     <x:row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A146" s="0" t="s">
@@ -11935,6 +12616,12 @@
       <x:c r="L146" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M146" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N146" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A147" s="0" t="s">
@@ -11974,10 +12661,10 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="M147" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N147" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1921</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:14" x14ac:dyDescent="0.25">
@@ -12017,6 +12704,12 @@
       <x:c r="L148" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M148" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N148" s="0" t="s">
+        <x:v>1918</x:v>
+      </x:c>
     </x:row>
     <x:row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A149" s="0" t="s">
@@ -12055,6 +12748,12 @@
       <x:c r="L149" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M149" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N149" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A150" s="0" t="s">
@@ -12093,6 +12792,12 @@
       <x:c r="L150" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M150" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N150" s="0" t="s">
+        <x:v>1919</x:v>
+      </x:c>
     </x:row>
     <x:row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A151" s="0" t="s">
@@ -12131,6 +12836,12 @@
       <x:c r="L151" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M151" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N151" s="0" t="s">
+        <x:v>1920</x:v>
+      </x:c>
     </x:row>
     <x:row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A152" s="0" t="s">
@@ -12169,6 +12880,12 @@
       <x:c r="L152" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M152" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N152" s="0" t="s">
+        <x:v>1923</x:v>
+      </x:c>
     </x:row>
     <x:row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A153" s="0" t="s">
@@ -12207,6 +12924,12 @@
       <x:c r="L153" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M153" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N153" s="0" t="s">
+        <x:v>1922</x:v>
+      </x:c>
     </x:row>
     <x:row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A154" s="0" t="s">
@@ -12245,6 +12968,12 @@
       <x:c r="L154" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M154" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N154" s="0" t="s">
+        <x:v>1932</x:v>
+      </x:c>
     </x:row>
     <x:row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A155" s="0" t="s">
@@ -12283,6 +13012,12 @@
       <x:c r="L155" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M155" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N155" s="0" t="s">
+        <x:v>1917</x:v>
+      </x:c>
     </x:row>
     <x:row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A156" s="0" t="s">
@@ -12321,6 +13056,12 @@
       <x:c r="L156" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M156" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N156" s="0" t="s">
+        <x:v>1807</x:v>
+      </x:c>
     </x:row>
     <x:row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A157" s="0" t="s">
@@ -12359,6 +13100,12 @@
       <x:c r="L157" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M157" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N157" s="0" t="s">
+        <x:v>1913</x:v>
+      </x:c>
     </x:row>
     <x:row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A158" s="0" t="s">
@@ -12397,6 +13144,12 @@
       <x:c r="L158" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M158" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N158" s="0" t="s">
+        <x:v>1914</x:v>
+      </x:c>
     </x:row>
     <x:row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A159" s="0" t="s">
@@ -12435,6 +13188,12 @@
       <x:c r="L159" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M159" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N159" s="0" t="s">
+        <x:v>1854</x:v>
+      </x:c>
     </x:row>
     <x:row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A160" s="0" t="s">
@@ -12473,6 +13232,12 @@
       <x:c r="L160" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M160" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N160" s="0" t="s">
+        <x:v>1924</x:v>
+      </x:c>
     </x:row>
     <x:row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A161" s="0" t="s">
@@ -12511,6 +13276,12 @@
       <x:c r="L161" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M161" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N161" s="0" t="s">
+        <x:v>1915</x:v>
+      </x:c>
     </x:row>
     <x:row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A162" s="0" t="s">
@@ -12549,6 +13320,12 @@
       <x:c r="L162" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M162" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N162" s="0" t="s">
+        <x:v>1928</x:v>
+      </x:c>
     </x:row>
     <x:row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A163" s="0" t="s">
@@ -12587,6 +13364,12 @@
       <x:c r="L163" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M163" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N163" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A164" s="0" t="s">
@@ -12625,6 +13408,12 @@
       <x:c r="L164" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M164" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N164" s="0" t="s">
+        <x:v>1927</x:v>
+      </x:c>
     </x:row>
     <x:row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A165" s="0" t="s">
@@ -12663,6 +13452,12 @@
       <x:c r="L165" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M165" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N165" s="0" t="s">
+        <x:v>1925</x:v>
+      </x:c>
     </x:row>
     <x:row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A166" s="0" t="s">
@@ -12701,6 +13496,12 @@
       <x:c r="L166" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M166" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N166" s="0" t="s">
+        <x:v>1929</x:v>
+      </x:c>
     </x:row>
     <x:row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A167" s="0" t="s">
@@ -12739,6 +13540,12 @@
       <x:c r="L167" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M167" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N167" s="0" t="s">
+        <x:v>1926</x:v>
+      </x:c>
     </x:row>
     <x:row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A168" s="0" t="s">
@@ -12777,6 +13584,12 @@
       <x:c r="L168" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M168" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N168" s="0" t="s">
+        <x:v>1933</x:v>
+      </x:c>
     </x:row>
     <x:row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A169" s="0" t="s">
@@ -12815,6 +13628,12 @@
       <x:c r="L169" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M169" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N169" s="0" t="s">
+        <x:v>1943</x:v>
+      </x:c>
     </x:row>
     <x:row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A170" s="0" t="s">
@@ -12853,6 +13672,12 @@
       <x:c r="L170" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M170" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N170" s="0" t="s">
+        <x:v>1820</x:v>
+      </x:c>
     </x:row>
     <x:row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A171" s="0" t="s">
@@ -12891,6 +13716,12 @@
       <x:c r="L171" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M171" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N171" s="0" t="s">
+        <x:v>1930</x:v>
+      </x:c>
     </x:row>
     <x:row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A172" s="0" t="s">
@@ -12929,6 +13760,12 @@
       <x:c r="L172" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M172" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N172" s="0" t="s">
+        <x:v>1935</x:v>
+      </x:c>
     </x:row>
     <x:row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A173" s="0" t="s">
@@ -12967,6 +13804,12 @@
       <x:c r="L173" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M173" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N173" s="0" t="s">
+        <x:v>1931</x:v>
+      </x:c>
     </x:row>
     <x:row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A174" s="0" t="s">
@@ -13005,6 +13848,12 @@
       <x:c r="L174" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M174" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N174" s="0" t="s">
+        <x:v>1934</x:v>
+      </x:c>
     </x:row>
     <x:row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A175" s="0" t="s">
@@ -13043,6 +13892,12 @@
       <x:c r="L175" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M175" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N175" s="0" t="s">
+        <x:v>1939</x:v>
+      </x:c>
     </x:row>
     <x:row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A176" s="0" t="s">
@@ -13081,6 +13936,12 @@
       <x:c r="L176" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M176" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N176" s="0" t="s">
+        <x:v>1854</x:v>
+      </x:c>
     </x:row>
     <x:row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A177" s="0" t="s">
@@ -13119,6 +13980,12 @@
       <x:c r="L177" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M177" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N177" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A178" s="0" t="s">
@@ -13157,6 +14024,12 @@
       <x:c r="L178" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M178" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N178" s="0" t="s">
+        <x:v>1936</x:v>
+      </x:c>
     </x:row>
     <x:row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A179" s="0" t="s">
@@ -13195,6 +14068,12 @@
       <x:c r="L179" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M179" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N179" s="0" t="s">
+        <x:v>1807</x:v>
+      </x:c>
     </x:row>
     <x:row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A180" s="0" t="s">
@@ -13233,6 +14112,12 @@
       <x:c r="L180" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M180" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N180" s="0" t="s">
+        <x:v>1963</x:v>
+      </x:c>
     </x:row>
     <x:row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A181" s="0" t="s">
@@ -13271,6 +14156,12 @@
       <x:c r="L181" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M181" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N181" s="0" t="s">
+        <x:v>1940</x:v>
+      </x:c>
     </x:row>
     <x:row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A182" s="0" t="s">
@@ -13309,6 +14200,12 @@
       <x:c r="L182" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M182" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N182" s="0" t="s">
+        <x:v>1820</x:v>
+      </x:c>
     </x:row>
     <x:row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A183" s="0" t="s">
@@ -13347,6 +14244,12 @@
       <x:c r="L183" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M183" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N183" s="0" t="s">
+        <x:v>1945</x:v>
+      </x:c>
     </x:row>
     <x:row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A184" s="0" t="s">
@@ -13385,6 +14288,12 @@
       <x:c r="L184" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M184" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N184" s="0" t="s">
+        <x:v>1937</x:v>
+      </x:c>
     </x:row>
     <x:row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A185" s="0" t="s">
@@ -13423,6 +14332,12 @@
       <x:c r="L185" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M185" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N185" s="0" t="s">
+        <x:v>1941</x:v>
+      </x:c>
     </x:row>
     <x:row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A186" s="0" t="s">
@@ -13461,6 +14376,12 @@
       <x:c r="L186" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M186" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N186" s="0" t="s">
+        <x:v>1942</x:v>
+      </x:c>
     </x:row>
     <x:row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A187" s="0" t="s">
@@ -13499,6 +14420,12 @@
       <x:c r="L187" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M187" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N187" s="0" t="s">
+        <x:v>1960</x:v>
+      </x:c>
     </x:row>
     <x:row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A188" s="0" t="s">
@@ -13537,6 +14464,12 @@
       <x:c r="L188" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M188" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N188" s="0" t="s">
+        <x:v>1938</x:v>
+      </x:c>
     </x:row>
     <x:row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A189" s="0" t="s">
@@ -13575,6 +14508,12 @@
       <x:c r="L189" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M189" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N189" s="0" t="s">
+        <x:v>1944</x:v>
+      </x:c>
     </x:row>
     <x:row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A190" s="0" t="s">
@@ -13613,6 +14552,12 @@
       <x:c r="L190" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M190" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N190" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A191" s="0" t="s">
@@ -13651,6 +14596,12 @@
       <x:c r="L191" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M191" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N191" s="0" t="s">
+        <x:v>1946</x:v>
+      </x:c>
     </x:row>
     <x:row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A192" s="0" t="s">
@@ -13689,6 +14640,12 @@
       <x:c r="L192" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M192" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N192" s="0" t="s">
+        <x:v>1949</x:v>
+      </x:c>
     </x:row>
     <x:row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A193" s="0" t="s">
@@ -13727,6 +14684,12 @@
       <x:c r="L193" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M193" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N193" s="0" t="s">
+        <x:v>1955</x:v>
+      </x:c>
     </x:row>
     <x:row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A194" s="0" t="s">
@@ -13765,6 +14728,12 @@
       <x:c r="L194" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M194" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N194" s="0" t="s">
+        <x:v>1947</x:v>
+      </x:c>
     </x:row>
     <x:row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A195" s="0" t="s">
@@ -13803,6 +14772,12 @@
       <x:c r="L195" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M195" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N195" s="0" t="s">
+        <x:v>1956</x:v>
+      </x:c>
     </x:row>
     <x:row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A196" s="0" t="s">
@@ -13841,6 +14816,12 @@
       <x:c r="L196" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M196" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N196" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A197" s="0" t="s">
@@ -13879,6 +14860,12 @@
       <x:c r="L197" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M197" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N197" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A198" s="0" t="s">
@@ -13917,6 +14904,12 @@
       <x:c r="L198" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M198" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N198" s="0" t="s">
+        <x:v>1952</x:v>
+      </x:c>
     </x:row>
     <x:row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A199" s="0" t="s">
@@ -13955,6 +14948,12 @@
       <x:c r="L199" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M199" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N199" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A200" s="0" t="s">
@@ -13993,6 +14992,12 @@
       <x:c r="L200" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M200" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N200" s="0" t="s">
+        <x:v>1958</x:v>
+      </x:c>
     </x:row>
     <x:row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A201" s="0" t="s">
@@ -14031,6 +15036,12 @@
       <x:c r="L201" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M201" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N201" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A202" s="0" t="s">
@@ -14069,6 +15080,12 @@
       <x:c r="L202" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M202" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N202" s="0" t="s">
+        <x:v>1953</x:v>
+      </x:c>
     </x:row>
     <x:row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A203" s="0" t="s">
@@ -14107,6 +15124,12 @@
       <x:c r="L203" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M203" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N203" s="0" t="s">
+        <x:v>1948</x:v>
+      </x:c>
     </x:row>
     <x:row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A204" s="0" t="s">
@@ -14145,6 +15168,12 @@
       <x:c r="L204" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M204" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N204" s="0" t="s">
+        <x:v>1951</x:v>
+      </x:c>
     </x:row>
     <x:row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A205" s="0" t="s">
@@ -14183,6 +15212,12 @@
       <x:c r="L205" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M205" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N205" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A206" s="0" t="s">
@@ -14221,6 +15256,12 @@
       <x:c r="L206" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M206" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N206" s="0" t="s">
+        <x:v>1950</x:v>
+      </x:c>
     </x:row>
     <x:row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A207" s="0" t="s">
@@ -14259,6 +15300,12 @@
       <x:c r="L207" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M207" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N207" s="0" t="s">
+        <x:v>1954</x:v>
+      </x:c>
     </x:row>
     <x:row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A208" s="0" t="s">
@@ -14297,6 +15344,12 @@
       <x:c r="L208" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M208" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N208" s="0" t="s">
+        <x:v>1957</x:v>
+      </x:c>
     </x:row>
     <x:row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A209" s="0" t="s">
@@ -14335,6 +15388,12 @@
       <x:c r="L209" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M209" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N209" s="0" t="s">
+        <x:v>1959</x:v>
+      </x:c>
     </x:row>
     <x:row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A210" s="0" t="s">
@@ -14373,6 +15432,12 @@
       <x:c r="L210" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M210" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N210" s="0" t="s">
+        <x:v>1807</x:v>
+      </x:c>
     </x:row>
     <x:row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A211" s="0" t="s">
@@ -14411,6 +15476,12 @@
       <x:c r="L211" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M211" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N211" s="0" t="s">
+        <x:v>1961</x:v>
+      </x:c>
     </x:row>
     <x:row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A212" s="0" t="s">
@@ -14449,6 +15520,12 @@
       <x:c r="L212" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M212" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N212" s="0" t="s">
+        <x:v>1803</x:v>
+      </x:c>
     </x:row>
     <x:row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A213" s="0" t="s">
@@ -14487,6 +15564,12 @@
       <x:c r="L213" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M213" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N213" s="0" t="s">
+        <x:v>1964</x:v>
+      </x:c>
     </x:row>
     <x:row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A214" s="0" t="s">
@@ -14525,6 +15608,12 @@
       <x:c r="L214" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M214" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="N214" s="0" t="s">
+        <x:v>1966</x:v>
+      </x:c>
     </x:row>
     <x:row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A215" s="0" t="s">
@@ -14563,6 +15652,12 @@
       <x:c r="L215" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M215" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N215" s="0" t="s">
+        <x:v>1965</x:v>
+      </x:c>
     </x:row>
     <x:row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A216" s="0" t="s">
@@ -14601,6 +15696,12 @@
       <x:c r="L216" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M216" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N216" s="0" t="s">
+        <x:v>1970</x:v>
+      </x:c>
     </x:row>
     <x:row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A217" s="0" t="s">
@@ -14639,6 +15740,12 @@
       <x:c r="L217" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M217" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N217" s="0" t="s">
+        <x:v>1967</x:v>
+      </x:c>
     </x:row>
     <x:row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A218" s="0" t="s">
@@ -14677,6 +15784,12 @@
       <x:c r="L218" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M218" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N218" s="0" t="s">
+        <x:v>1962</x:v>
+      </x:c>
     </x:row>
     <x:row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A219" s="0" t="s">
@@ -14715,6 +15828,12 @@
       <x:c r="L219" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="M219" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N219" s="0" t="s">
+        <x:v>1972</x:v>
+      </x:c>
     </x:row>
     <x:row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A220" s="0" t="s">
@@ -14753,6 +15872,12 @@
       <x:c r="L220" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M220" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N220" s="0" t="s">
+        <x:v>1963</x:v>
+      </x:c>
     </x:row>
     <x:row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A221" s="0" t="s">
@@ -14791,6 +15916,12 @@
       <x:c r="L221" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M221" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N221" s="0" t="s">
+        <x:v>1968</x:v>
+      </x:c>
     </x:row>
     <x:row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A222" s="0" t="s">
@@ -14829,6 +15960,12 @@
       <x:c r="L222" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
+      <x:c r="M222" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N222" s="0" t="s">
+        <x:v>1971</x:v>
+      </x:c>
     </x:row>
     <x:row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <x:c r="A223" s="0" t="s">
@@ -14866,6 +16003,12 @@
       </x:c>
       <x:c r="L223" s="0" t="s">
         <x:v>23</x:v>
+      </x:c>
+      <x:c r="M223" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="N223" s="0" t="s">
+        <x:v>1969</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
+++ b/check-target-net/src/cursor_grading_web/wwwroot/uploads/companies_graded.xlsx
@@ -5426,22 +5426,22 @@
     <x:t>Builds custom advanced manufacturing systems with a focus on high-speed assembly, test, and inspection of automotive electronics components</x:t>
   </x:si>
   <x:si>
-    <x:t>They are a global leader in research, development, and delivery of vehicle power and data solutions, producing wire harnesses, sensors, and driver information systems, which implies in-house engineering and manufacturing requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states expertise in design, manufacturing, and testing of advanced electronics, indicating a need for test &amp; measurement equipment.</x:t>
+    <x:t>Yazaki is a global leader in the research, development, and delivery of automotive power, data, and display technologies, indicating in-house engineering and manufacturing that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states expertise in design, manufacturing, and testing of electronic products, indicating a need for test &amp; measurement equipment.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: HTTP 403 Forbidden</x:t>
   </x:si>
   <x:si>
-    <x:t>They perform advanced post-production testing on their parts, including chemical resistance, vibration, and thermal shock, indicating an in-house quality and testing function.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company manufactures metal foils for shielding and thermal management in electronic applications, but there is no clear evidence of in-house electronic testing or engineering.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>As a manufacturer of electronic automotive components, they would have in-house engineering and quality control teams that use test and measurement equipment.</x:t>
+    <x:t>They engineer and manufacture automotive electronic parts and perform advanced testing and quality checks on them.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company manufactures metal foils for shielding and thermal management in electronic applications, but there is no clear evidence of in-house electronic engineering, R&amp;D, or testing functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a major manufacturer of electronic automotive components, which implies in-house engineering, R&amp;D, and quality control requiring test and measurement equipment.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch)</x:t>
@@ -5450,316 +5450,316 @@
     <x:t>Scrape failed: HTTP 301 Moved Permanently</x:t>
   </x:si>
   <x:si>
-    <x:t>The company states it is a global leader in the development and manufacturing of innovative LED lighting and safety systems, indicating in-house engineering and production that would require test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in the repair, refurbishment, and remanufacturing of automotive electronic modules, which requires in-house diagnostic and testing capabilities.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they are a manufacturer of high-performance mobile electronics and have been crafting products for decades, implying in-house design, manufacturing, and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The site mentions 'driving innovation' and 'brands' of finished electronic products, but lacks clear evidence of in-house engineering, R&amp;D, manufacturing, or repair requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company primarily installs and resells finished automotive electronic products, with no clear evidence of current in-house engineering, manufacturing, or complex electronic hardware diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house repair, diagnostics, and calibration of electronic instrument clusters and other vehicle electronics, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop, design, and manufacture automotive wiring harnesses and electronic components, indicating in-house engineering and R&amp;D that would use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company manufactures custom-engineered solutions, including sensors and electrical components, and has dedicated engineering facilities, indicating in-house testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a developer and manufacturer of automotive and electronic components, indicating in-house engineering and production testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company sells finished electronic products for vehicles and mentions patented technology, but there is no clear evidence of in-house engineering, R&amp;D, or repair requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and sell an electronic product, but there is no explicit mention of in-house engineering, R&amp;D, manufacturing, or testing facilities that would use test &amp; measurement equipment.</x:t>
+    <x:t>Their core business of repairing and remanufacturing automotive electronic modules requires in-house diagnostics and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company states it is a global leader in the development and manufacturing of innovative LED lighting systems, indicating in-house engineering and R&amp;D.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer crafting premium car audio products, implying in-house engineering, design, and quality control functions that would use test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The website content suggests they primarily distribute and integrate finished automotive electronic products, with no clear evidence of in-house engineering, R&amp;D, or repair functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-house repair, calibration, and diagnostics of electronic instrument clusters, speedometers, and other vehicle electronics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They primarily install and service finished automotive electronic systems, with no clear evidence of in-house electronic engineering, R&amp;D, or component-level diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company states it designs, develops, and manufactures products, including advanced product development, which requires electronic test and measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a developer and manufacturer of automotive and electronic products with innovative engineering and manufacturing operations, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is a manufacturer and custom-engineered solutions provider for automotive parts, including sensors and electrical components, indicating in-house engineering and production that requires test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs diagnostics, programming, and calibration of vehicle electronic systems, which requires test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They manufacture an electronic product, but the website lacks clear evidence of in-house engineering, R&amp;D, or testing labs for their hardware.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (Authentication failed because the remote party sent a TLS alert: 'ProtocolVersion'.)</x:t>
   </x:si>
   <x:si>
-    <x:t>They state they are an innovator in designing and engineering vehicle electronics and components, indicating in-house R&amp;D and manufacturing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house diagnostics and calibration of vehicle electronic systems, which requires test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and produce stamped and plated electrical connectors, indicating in-house engineering and manufacturing that would require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform repair, remanufacturing, calibration, and re-qualification testing of automotive electronics, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a manufacturer developing and engineering automotive electronic components, which implies in-house R&amp;D and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an upfitter installing electronics, but the text does not indicate in-house engineering, diagnostics, or repair of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly mentions R&amp;D for autonomous driving, advanced driver-assist, and in-vehicle infotainment systems, indicating in-house engineering and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs remanufacturing, engineering, innovation, and calibration of automotive electronic components, indicating in-house testing and diagnostic needs.</x:t>
+    <x:t>The company explicitly states they are involved in designing, engineering, and manufacturing vehicle electronics and components, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Their patented 360° technology for vehicle electronics suggests in-house R&amp;D and hardware engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They install and maintain finished electronic systems in vehicles, but there is no clear evidence of in-house engineering, R&amp;D, or component-level diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in repair, remanufacturing, re-qualification testing, validation, and calibration of automotive electronics, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company develops and produces stamped and plated electrical connectors, indicating in-house engineering and manufacturing that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company states they are a manufacturer developing high-quality automotive electronic components, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company remanufactures automotive electronic components and mentions in-house engineering, innovation, and calibration of parts like throttle bodies, indicating a need for test and measurement equipment.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (The remote certificate is invalid according to the validation procedure: RemoteCertificateNameMismatch, RemoteCertificateChainErrors)</x:t>
   </x:si>
   <x:si>
+    <x:t>The company has an R&amp;D center focused on autonomous driving, ADAS, and in-vehicle infotainment, indicating in-house engineering and testing of complex electronic systems.</x:t>
+  </x:si>
+  <x:si>
     <x:t>The scraped website content was unreadable and insufficient to make a determination.</x:t>
   </x:si>
   <x:si>
-    <x:t>They emphasize 'deep engineering expertise' and 'design, development, and manufacture' of advanced lighting and electronics systems, indicating in-house R&amp;D and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states they perform in-house design, engineering, prototype development, and rigorous testing of their wire harnesses.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company sells and equips vehicles with aftermarket electronic accessories, but there is no evidence of in-house engineering, R&amp;D, or repair requiring test equipment.</x:t>
+    <x:t>They sell and equip vehicles with finished electronic systems but show no evidence of in-house engineering, R&amp;D, or complex diagnostics requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-house design, engineering, prototype development, and rigorous testing of wire harnesses, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They explicitly state 'deep engineering expertise' and 'design, development, and manufacture of advanced lighting and electronics systems' for custom solutions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house testing, reprogramming, flashing, and tuning of electronic control modules, indicating a need for test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They sell plug-and-play electronic kits, but there is no clear evidence of in-house engineering, R&amp;D, or repair of the electronic hardware itself.</x:t>
   </x:si>
   <x:si>
     <x:t>Stoneridge designs and manufactures highly engineered electrical and electronic systems, including new ECU technology and advanced vision systems, indicating in-house engineering and R&amp;D.</x:t>
   </x:si>
   <x:si>
-    <x:t>EEPod develops advanced vehicle diagnostic tools and ECU test/reprogramming stations, explicitly targeting automotive engineers for vehicle development, diagnostics, testing, and reprogramming workflows.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They sell plug-and-play electronic kits, but there is no clear evidence of in-house engineering, R&amp;D, or repair work requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform thorough testing, reprogramming, flashing, and tuning of electronic control modules, indicating in-house diagnostic and engineering work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company manufactures mechanical automotive components and mentions 'precision-engineered solutions', but there is no explicit mention of electronic hardware, R&amp;D, or testing functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in remanufacturing and repair of automotive electronic components and systems, indicating a need for diagnostic and test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in vehicle electronics installation, but it's unclear if they perform component-level diagnostics or repair requiring test equipment, or if they only install finished units.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house development and updates to their 'tuning and electronics' and conduct extensive testing, including '80 dyno pulls' and 'our findings', indicating a need for diagnostic and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NAL develops and manufactures automotive lighting systems, hires engineers and technicians, and focuses on innovative lighting technology, indicating a need for electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states they are involved in "automotive electronics engineering" and are a "manufacturer" of their products, indicating in-house design and production.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop advanced electronic systems like Vision &amp; Radar Systems, Advanced Sensors &amp; Mechatronics, and new control devices, indicating in-house engineering and R&amp;D requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company specializes in the development and testing of LED lighting solutions at its tech centers and performs in-house manufacturing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house electronics manufacturing, PCB assembly, engineering, and system integration from prototype to production.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>As a Tier One automotive supplier creating components and systems, they likely have in-house engineering and manufacturing requiring electronic test and measurement.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company has R&amp;D facilities and mentions in-house innovation, design, and advanced electronics for their control systems and components, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They operate as a satellite design and development center and are a global leader in electrical components manufacturing, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is driven by engineering, has vertically integrated electronic manufacturing capabilities, and a continuous flow of new product introductions, indicating in-house R&amp;D and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house development of OBD tuning solutions and influence vehicle electronics and hardware through automotive engineering.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are involved in engineering and manufacturing automotive systems and mechatronics, and have a Technical Center, indicating in-house electronic hardware development and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an automotive supplier with manufacturing operations and product development and engineering centers, indicating in-house electronic hardware development and testing.</x:t>
+    <x:t>They develop custom ECUs and provide ECU test, simulation, and reprogramming stations, indicating in-house electronic hardware development and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They state they are an automotive electronics engineering company and a manufacturer of OEM integration components, indicating in-house design and production.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company manufactures precision-engineered automotive components and performs design/development, but there is no explicit mention of electronic hardware or related testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform remanufacturing and repair of automotive electronic components, which requires diagnostics, testing, and engineering expertise.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in installing vehicle electronics but do not show evidence of in-house engineering, R&amp;D, or repair of the electronic hardware itself.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NAL manufactures automotive lighting systems, hires engineers and technicians, and develops innovative lighting technologies, indicating in-house engineering and manufacturing functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform engine calibration and tuning, develop their own 'FutureFlex Technology' and 'electronics', and conduct 'dyno pulls' and 'findings', indicating in-house R&amp;D and diagnostics on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company emphasizes innovation, next-generation technologies, advanced sensors, mechatronics, and new control devices, indicating in-house R&amp;D and engineering of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company specializes in the development, testing, and manufacturing of innovative automotive LED lighting systems, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house electronics manufacturing, PCB assembly, ODM/EMS, and engineering for integrated electronic systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house development, automotive engineering, and design and production of electronic hardware and tuning solutions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>As a Tier One automotive supplier creating complex components and systems, they likely have in-house R&amp;D and manufacturing involving electronic hardware testing.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Page body was empty after parsing</x:t>
   </x:si>
   <x:si>
+    <x:t>The company states they are driven by engineering, have vertically integrated electronic manufacturing capabilities, and a continuous flow of new product introductions, indicating in-house R&amp;D and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company has product development, engineering, and manufacturing operations for automotive lighting systems, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They operate as a satellite design and development center and are involved in manufacturing electrical and automotive components, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They have R&amp;D and manufacturing facilities that develop and produce advanced electronic control systems, solenoids, and sensor technology.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company engages in engineering and manufacturing of automotive systems and mechatronics, and has a Technical Center, indicating in-house electronic hardware development and testing.</x:t>
+  </x:si>
+  <x:si>
     <x:t>They have an extensive team of engineers and technicians who perform rigorous testing and development of new electrical products.</x:t>
   </x:si>
   <x:si>
-    <x:t>They design and manufacture intelligent controls, electronics, software, and brushless DC motors, indicating in-house engineering and development.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in conceiving and engineering proprietary electronic sensor and control systems, indicating in-house R&amp;D and development.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ampere EV performs in-house design, engineering, testing, and calibration of electronic hardware for their EV powertrain systems.</x:t>
+    <x:t>They perform vehicle upfitting, equipment sales, service, and installation, but it's unclear if their 'service' includes component-level electronic repair or diagnostics requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture electronics, intelligent controls, and BLDC motors, indicating in-house engineering and development work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company specializes in repair and remanufacturing of electronic instrument clusters, indicating in-house diagnostic and repair work on electronic hardware.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (Received an unexpected EOF or 0 bytes from the transport stream.)</x:t>
   </x:si>
   <x:si>
-    <x:t>The company specializes in repair and remanufacturing of electronic instrument clusters, including odometer programming, indicating in-house diagnostic and repair work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They remanufacture high-precision automotive components, which may involve some electronic testing or diagnostics, but the text primarily focuses on mechanical aspects.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides technical resources and support for installing vehicle electronics, but there is no clear evidence of in-house hardware engineering, R&amp;D, or repair requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They primarily upfit, sell, and install finished public safety vehicle equipment, with no clear evidence of in-house electronic hardware engineering, R&amp;D, or component-level repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states they have "expert in-house engineers" committed to innovation and seamless integration of automotive technology, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly states "Automotive Lighting Design and Manufacturing" and describes advanced manufacturing processes for electronic lighting products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a trade association focused on software and data standards for automotive OTA, with no clear evidence of in-house hardware engineering or test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a full-service manufacturer with explicit 'Engineering' and 'Testing' capabilities for electronic and electromechanical components.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and integrate plastic components with control units and power electronics, indicating in-house engineering and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs advanced testing, precision control with real-time current monitoring, and engineering implementation for their digitally-switched power systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture automotive semiconductors and engine control units, which requires significant in-house electronic engineering and testing.</x:t>
+    <x:t>Ampere EV explicitly states they perform in-house design, engineering, testing, and calibration of electronic hardware for their EV powertrain systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They specialize in conceiving and engineering proprietary electronic sensor and control systems, indicating in-house R&amp;D and development that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide technical resources and products for vehicle electronics installation, including firmware solutions, but there is no clear evidence of in-house hardware engineering, R&amp;D, or deep diagnostics requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company designs and manufactures automotive lighting products, including modular electronic assemblies, indicating in-house engineering and manufacturing processes.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states they have "expert in-house engineers" committed to innovation and seamless integration of automotive electronic solutions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>This is a non-profit trade association focused on standardizing software updates and data gathering for automotive electronics, with no clear evidence of in-house hardware engineering, testing, or repair functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Their primary products include automotive semiconductors and engine control units, which require extensive in-house engineering, manufacturing, and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop unique solutions for plastic components with integrated control units and power electronics, indicating in-house engineering and R&amp;D that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Instrumental provides an AI platform for electronics manufacturing optimization, but they do not appear to perform in-house physical testing or repair of electronic hardware themselves.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs advanced testing on their digitally-swswitched power systems for industry certifications, indicating in-house engineering and test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They remanufacture complex diesel injection systems, which are electro-mechanical, implying a potential need for electronic diagnostics and testing, though not explicitly stated.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a full-service manufacturer with in-house engineering and testing capabilities for electronic and electromechanical components and wire harnesses.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: HTTP 406 Not Acceptable</x:t>
   </x:si>
   <x:si>
-    <x:t>They sell automotive accessories, including a precision pressure gauge, but there is no evidence of in-house electronic engineering, R&amp;D, or testing requiring specialized electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide a platform for electronics manufacturing optimization and defect detection, but it's unclear if their own staff performs in-house hardware testing or repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is a wholesale distributor of automotive parts and chemicals, which may include some electronic components, but there is no clear evidence of in-house engineering or diagnostic work on electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is a wholesale distributor of automotive parts with no visible evidence of in-house electronic engineering, testing, or repair functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company develops automotive tools and offers 'Test Products' and 'Service Equipment', but it's unclear if this involves electronic hardware engineering or just mechanical testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and engineer mechatronics products and actuators, utilizing simulation, prototyping, and extensive R&amp;D, indicating a need for electronic test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They create innovative, next-generation electronic products and new technologies, indicating in-house engineering and R&amp;D that would use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Putco designs and manufactures automotive LED lighting and accessories, indicating in-house engineering and manufacturing that would require electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company focuses on metal wool and fiber technology for automotive and industrial applications, with R&amp;D experts, but no clear indication of electronic hardware engineering or testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They specialize in vintage vehicles and climate control systems, which may involve some electrical diagnostics, but there is no clear evidence of in-house electronic hardware engineering or component-level repair.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company primarily deals with automotive chemicals, but their Petra Cares initiative trains individuals in auto repair, which may involve some electronic diagnostics.</x:t>
+    <x:t>The company primarily distributes automotive parts and chemicals, with no clear indication of in-house electronic engineering, R&amp;D, manufacturing, or repair requiring test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company sells mechanical automotive accessories and does not show evidence of in-house electronic engineering, R&amp;D, or repair work, but they do sell a 'Precision Pressure Gauge' which might imply some level of calibration or testing of their own products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a wholesale distributor of automotive parts with no visible in-house engineering or test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company develops automotive tools and 'test products' but there is no clear evidence of in-house electronic hardware engineering, R&amp;D, or repair work that would require general electronic test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They state they "create new technologies and solutions" and unveil "next-generation automotive accessories," indicating in-house R&amp;D and engineering.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company designs, engineers, prototypes, and manufactures mechatronics products and highly engineered solutions for the automotive industry, indicating a need for electronic test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Putco states they are a designer and manufacturer of LED lighting, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company has R&amp;D experts innovating in metal wool and fiber technology, but there is no clear evidence of work on electronic hardware that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company primarily deals with automotive chemicals and mechanical parts, with no clear indication of in-house electronic hardware engineering, R&amp;D, or testing, though their 'auto repair' initiative could involve some diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They supply automotive parts and mention 'engine diagnostics' as a service their customers offer, but there's no clear evidence they perform in-house electronic hardware engineering or complex diagnostics themselves.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (omron.com:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
   </x:si>
   <x:si>
-    <x:t>They sell automotive batteries and mention 'Strategic Global Sourcing &amp; Rigorous Quality Control' but it's unclear if this involves in-house electronic testing or just supplier vetting.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop, engineer, and manufacture their own LED emergency vehicle lighting products, indicating in-house electronic design and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design, engineer, and manufacture their own Bluetooth-enabled transmission control units and custom harnesses in-house.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide engineering and prototyping services to create testable designs, indicating in-house electronic development and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company manufactures electronic brake and safety systems and electronic controls, indicating in-house production and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They have an R&amp;D team working on 'automotive technology' for chemical additives, but it's unclear if this involves in-house testing or diagnostics of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer custom design, manufacturing support, and private label solutions for automotive equipment, indicating in-house engineering and development.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They mention 'Power Engineering' and 'prototype optimization' but their primary focus is structural automotive components, making electronic hardware testing unclear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house design, development, manufacture, and R&amp;D of electronic solutions for the automotive industry.</x:t>
+    <x:t>The scraped content is too brief to determine if they perform in-house electronic engineering, diagnostics, or repair beyond basic installation.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop, engineer, and manufacture their own LED emergency vehicle lighting products in-house, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture their own electronic control units and custom engineer harnesses, indicating in-house engineering and production.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They have engineers for design innovation and prototype optimization, but their primary focus is on structural automotive components, with no explicit mention of electronic hardware engineering or testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide engineering and prototyping services to create testable designs, indicating in-house development and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer custom design, patented products, and manufacturing support for automotive equipment, indicating in-house engineering and development.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They have an R&amp;D team and manufacture chemical additives for the automotive industry, but there is no clear evidence of in-house electronic hardware engineering, testing, or repair.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is involved in the production of electronic brake and safety systems and other automotive components, which implies in-house manufacturing and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house design, development, and manufacturing of electronic solutions, and have R&amp;D innovation, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They install and program vehicle electronics and keys, but there is no clear evidence of in-house engineering, R&amp;D, or component-level electronic diagnostics.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (shinko.co.jp:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
   </x:si>
   <x:si>
-    <x:t>They install and program finished electronic accessories, but there is no clear evidence of in-house engineering, R&amp;D, or component-level diagnostics requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company engages in innovation, design, and manufacturing of proprietary electrical solutions, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer Engineering &amp; Design Services and have an Engineering Manager, indicating in-house engineering and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TTM Technologies manufactures complex electronic components like PCBs and RF assemblies, indicating in-house engineering, R&amp;D, and manufacturing that require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an electronic components manufacturer's representative, providing solutions by connecting customers with components, with no visible in-house engineering or test function.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITW is a global multi-industry manufacturing leader that designs and innovates industrial products and mechatronics, indicating a need for in-house engineering and testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They sell 'LIKE NEW' and 'USED' diagnostic equipment, implying refurbishment and testing, and offer 'Custom Test Leads' which suggests in-house design/testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Safari Circuits provides end-to-end engineering services, advanced manufacturing, and rapid prototyping for electronic circuit design and assembly, which requires test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company states they are 'Investing in Innovation' and 'Bringing Innovative Technologies to Market', indicating in-house R&amp;D and engineering functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide coating services for PCBs and develop coating processes, but the text does not explicitly indicate in-house electronic hardware design, functional testing, or diagnostics requiring advanced test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs in-house design, engineering, prototyping, testing, troubleshooting, and repair of electronic circuits and products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Scrape failed: Network error: Error while copying content to a stream. (The response ended prematurely. (ResponseEnded))</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is an EMS provider performing PCB assembly, box-builds, and electro-mechanical assembly, with processes like SPI/AOI and prototype board manufacturing, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company explicitly mentions R&amp;D, manufacturing, engineering, and repair/reconditioning of electronic control systems, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company is a distributor and supply chain solutions provider for electronic components, with no clear evidence of in-house engineering, R&amp;D, manufacturing, or repair requiring test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>As a manufacturer of printed circuit boards, they clearly have in-house engineering and quality control functions that require electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and build highly engineered electronic connectors and receptacles for critical applications, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer powertrain calibration and embedded systems development, indicating a need for electronic test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a contract electronics manufacturer that performs in-circuit testing, functional testing, and burn-in testing on PCB assemblies.</x:t>
+    <x:t>TTM Technologies is a global manufacturer of PCBs, RF components, and microelectronic assemblies, with in-house manufacturing facilities and technical qualifications indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states involvement in innovation, design, and manufacturing of advanced electrical solutions, indicating in-house engineering and testing functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITW is a multi-industry manufacturing leader that designs and produces complex solutions like automotive mechatronics, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide Electronics Manufacturing Services (EMS) and Engineering &amp; Design Services, and employ Engineering Managers, indicating in-house design, manufacturing, and testing of electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They create custom test leads, indicating in-house engineering and testing capabilities for electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company states they are "Investing in Innovation" and "Bringing Innovative Technologies to Market," indicating in-house R&amp;D and engineering work.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company provides end-to-end electronic circuit design and assembly services, including engineering and manufacturing for high-reliability sectors.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide coating services for PCBs and mention prototypes and manufacturing processes, but it's unclear if they perform in-house electronic testing or diagnostics on the hardware itself.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide custom electronic hardware design and development services, including prototyping and design verification, which requires test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer's representative for electronic components, providing solutions to design challenges, but do not explicitly state they perform in-house engineering, testing, or repair.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company engages in R&amp;D, engineering, manufacturing, and repairs of electronic control systems, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company explicitly states they offer design, engineering, prototyping, testing, troubleshooting, and repair of electronic circuits and products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-circuit testing, functional testing, burn-in testing, AOI, and 3D X-ray inspection to validate PCB assemblies and products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an EMS company performing printed circuit board assembly with in-house manufacturing processes like SMT, SPI, and AOI, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>As a printed circuit board manufacturer, they would have in-house engineering and quality control teams that use test and measurement equipment for fabrication and diagnostics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>World Micro is a distributor of electronic components and ground support equipment, but there is no clear evidence of in-house engineering, R&amp;D, manufacturing, or repair work that would require test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and build connectors for electronic systems, but their core business appears to be precision metal stamping and casting, with no explicit mention of electronic hardware engineering or testing beyond the physical components.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They supply mechanical components to industries like EV and consumer electronics, but there is no clear evidence of in-house electronic hardware engineering or testing.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: The SSL connection could not be established, see inner exception. (Authentication failed because the remote party sent a TLS alert: 'HandshakeFailure'.)</x:t>
@@ -5768,178 +5768,181 @@
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (hosiden.com:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
   </x:si>
   <x:si>
+    <x:t>The scraped website content was insufficient to make a determination.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Scrape failed: Network error: The requested name is valid, but no data of the requested type was found. (foster-electric.com:443) (The requested name is valid, but no data of the requested type was found.)</x:t>
   </x:si>
   <x:si>
-    <x:t>Cohu designs and manufactures semiconductor test equipment and ATE platforms, indicating in-house engineering and R&amp;D that would use test and measurement gear.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a manufacturer sales representative providing technical sales and engineering support, but it's unclear if they perform in-house hardware testing or R&amp;D.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They state they develop all their products from the ground up and perform extensive testing tailored to specific application requirements.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QMS is an Electronics Manufacturing Services provider offering in-house engineering, manufacturing, testing, DFT, and repair depot services.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PalPilot provides integrated engineering and manufacturing solutions for PCBs, interconnects, and semiconductors, including design, DFM, and prototype to production support, indicating in-house testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They supply mechanical components and assemblies to electronic industries, but it's unclear if their in-house engineering team performs electronic hardware testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Methode designs, engineers, develops, and manufactures custom mechatronic and electronic products, with mentions of R&amp;D departments and laboratories.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Toshiba is involved in R&amp;D, design, and manufacturing of semiconductors, power electronics, and other advanced electronic products, including operating a research laboratory.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide engineering R&amp;D support services to electronics design companies, but it's unclear if they perform in-house testing or design themselves.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ElectroCraft provides application-engineered custom OEM solutions for motors and motion control products, explicitly stating they have deep engineering resources and design experience.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an electronic contract manufacturer that explicitly offers design, prototyping, PCBA manufacturing, system assembly, repairs, rework, and 'Testing &amp; Quality Assurance' services.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides contract manufacturing and engineering services, including design, prototyping, and R&amp;D for electronic components like sensors and connectors.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nidec manufactures a wide range of electronic devices and automotive components, and mentions 'Smart Factory' and 'Inspection and measuring equipment', indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ark Electronics offers design engineering, PCBA manufacturing, and develops custom electronic modules, indicating in-house engineering and testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sanmina provides design and engineering, test system development, manufacturing, and repair services for electronic systems, indicating a clear need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform electronic design, PCB layout, R&amp;D, and electronic manufacturing, including DV and PPAP builds, all of which require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a component supplier with staff having engineering backgrounds, but they outsource quality testing to external labs rather than performing in-house hardware diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They conduct rigorous performance testing, engineering, and analytical testing of their proprietary PCB materials.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They perform in-house electronic design, hardware re-engineering, rapid prototyping, calibration, and diagnostics, including EMI/EMC pre-screening.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>While they manufacture electronic audio devices, the website content is entirely consumer-facing and does not show evidence of in-house engineering, R&amp;D, or testing labs that would use test &amp; measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide Electronic Manufacturing Services (EMS) including PCB assembly, prototype development, and production, indicating in-house engineering and manufacturing that requires test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer engineering services including design, prototyping, and testing, and perform quality control for electronics manufacturing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a contract electronics manufacturer building PCBA, wire harnesses, and cable assemblies, which requires in-house testing and quality control.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company performs electronic equipment design, development, manufacturing, assembly, and reverse-engineering, all of which require in-house test and measurement capabilities.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corelis develops and sells hardware and software for embedded hardware testing, debugging, and programming, indicating strong in-house engineering and test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company provides turnkey design, engineering, and manufacturing services for electronic solutions and sub-assemblies, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide additive manufacturing solutions for applications like power electronics, but the website does not show clear evidence of in-house electronic hardware testing or diagnostics.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company offers electronic design and circuit board assembly services, explicitly mentioning "Advanced Test Engineering" and "Engineering and NPI" in their services.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company develops and manufactures advanced nano coatings for PCBs, mentioning in-house engineering teams, R&amp;D, and concerns like signal integrity and accurate signal monitoring.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a manufacturer's representative providing technical expertise and product distribution, but there is no clear evidence of in-house electronic hardware engineering, R&amp;D, or testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CheckSum designs and engineers complex automated test systems and fixtures, indicating in-house engineering and manufacturing that would require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BPM Microsystems designs and manufactures automated device programming solutions, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are an "Engineering Driven Manufacturer" of custom electro-mechanical assemblies and wire harnesses for the electronics, medical, and analytical instrumentation industries, implying in-house testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kyocera AVX is a global manufacturer of advanced electronic components with in-house research, development, engineering, and manufacturing facilities, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company specializes in automotive audio/visual electronics and consumer goods, but the scraped content does not clearly indicate in-house engineering, R&amp;D, or repair work.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide advanced electronics manufacturing services, including NPI, prototyping, and engineering services, which require in-house testing and measurement.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They develop and launch new coating equipment and upgrade existing series, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They engineer, manufacture, and rigorously test custom magnetics and electronic assemblies, including thermal shock, dielectric, and corona testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer electrical assembly services backed by extensive testing protocols, indicating in-house electronic testing needs.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Lectronix performs in-house hardware engineering, product development, PCB assembly, and functional testing for complex electronic systems.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They are a PCB manufacturer with in-house engineering, prototype development, DFM feedback, and advanced manufacturing processes that require testing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sheldahl designs and develops flexible circuits and electronic materials, employs engineers, and has a Director of Innovation and Technology, indicating in-house R&amp;D and manufacturing.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They offer PCB design, electronics manufacturing services, and have in-house hardware experts, PCB designers, and technicians who would use test equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HED designs and engineers their own electronic control systems and states they have engineers who provide solutions, indicating a need for test and measurement equipment.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture flexible circuits, which implies in-house engineering and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The company offers electronic design, PCB design, PCB assembly, design for test, and electronics testing services, indicating in-house engineering and test functions.</x:t>
+    <x:t>They develop all their products from the ground up and perform extensive in-house testing tailored to specific application requirements.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PalPilot provides integrated engineering and manufacturing solutions for PCBs and electronic components, including design, prototyping, and production, which requires in-house testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a manufacturer sales representative providing technical sales and engineering support, but there is no clear evidence their own staff perform hands-on hardware testing or measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toshiba designs, engineers, manufactures, and innovates semiconductors, power devices, and electronic systems, indicating a strong need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Methode designs, engineers, develops, and manufactures custom mechatronic products, with explicit mentions of R&amp;D departments, laboratories, and design engineers.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an Electronics Manufacturing Services (EMS) provider with in-house engineering, manufacturing, testing, and a repair depot.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide engineering R&amp;D support services to other companies that design electronics, but do not clearly state they perform in-house design or testing themselves.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company provides contract manufacturing and engineering services, including design, prototyping, and a dedicated R&amp;D center for electronic components and assemblies.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ElectroCraft provides application-engineered custom OEM solutions for motors and motion control, indicating in-house engineering and design work on electronic hardware.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an electronics contract manufacturer that explicitly offers prototype development, manufacturing, testing &amp; quality assurance, and repair services, all of which require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company operates a 'Smart Factory' and lists 'Inspection and measuring equipment' and 'Electronic devices' among its products, indicating in-house engineering and manufacturing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sanmina provides design, engineering, test system development, manufacturing, and repair services for complex electronic hardware, indicating a clear need for test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-house electronic design, R&amp;D, PCB layout, embedded firmware development, and PCA manufacturing, all of which require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer design engineering, PCB design, and electronics manufacturing services, indicating in-house engineering and test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company conducts rigorous performance testing, proprietary resin formulation, and analytical testing for their PCB materials, indicating in-house engineering and R&amp;D.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform electronic design, rapid prototyping, hardware calibration, troubleshooting, and EMI/EMC pre-screening, indicating a need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The website focuses on selling and distributing finished car audio products, with no visible evidence of in-house engineering, R&amp;D, manufacturing, or repair operations that would require test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer electronic design, circuit board assembly, and advanced test engineering services, indicating a clear need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer in-house engineering services including design, prototyping, and testing of electronic products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Their staff has electronics engineering background and experience, and they operate an AS6081 counterfeit avoidance program that likely involves component testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company performs in-house electronics design, development, manufacturing, and reverse-engineering, which requires test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide Electronic Manufacturing Services (EMS) including PCB assembly, prototype development, and production, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corelis develops and provides embedded hardware test and development solutions, indicating in-house engineering and R&amp;D that would utilize test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture flexible and rigid-flex circuit boards, which requires in-house engineering and testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a contract electronics manufacturer building wire harnesses, cable assemblies, and PCBAs, which requires in-house testing and measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They explicitly state they provide design, engineering, product development, and manufacturing services for electronic hardware, indicating a need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company is a manufacturer's representative and distributor, providing technical expertise and solutions from partners, but does not explicitly state in-house engineering, R&amp;D, or testing functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop and apply advanced nano coatings for PCBs, with in-house engineering teams and R&amp;D focused on signal integrity and environmental protection for complex electronics.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a global manufacturer of advanced electronic components with extensive R&amp;D, design, engineering, and manufacturing facilities, indicating a clear need for test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide additive manufacturing solutions for various industries, including those that use electronics, but do not explicitly state in-house electronic hardware R&amp;D or testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CheckSum designs and engineers complex automated test systems for electronics manufacturing, indicating in-house R&amp;D and engineering that would use test &amp; measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are an "Engineering Driven Manufacturer" of "electro-mechanical assemblies" and "custom cable, wire harness" for the electronics, medical, and analytical instrumentation industries, indicating a need for in-house testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lectronix performs in-house hardware engineering, product development, PCB assembly, system integration, and functional testing of electronic products.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide advanced electronics manufacturing, prototyping, NPI, and engineering services, which require in-house testing and quality control.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They develop and upgrade their own specialized coating equipment, indicating in-house engineering and manufacturing that would require test and measurement.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They are a PCB manufacturer with in-house engineering, prototype development, and quality control, indicating a need for electronic test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture complex automated programming systems, indicating in-house engineering and R&amp;D that would require test and measurement equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They engineer, manufacture, and rigorously test custom magnetics and electronic assemblies, explicitly mentioning thermal shock, dielectric, and corona testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They perform in-house PCB design, hardware engineering, and electronics manufacturing services, indicating a need for test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"grade": "GOOD", "reason": "The company designs, develops, and manufactures flexible circuits and electronic materials, explicitly mentioning "our engineers" and a Director of Innovation and Technolo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HED designs, engineers, and manufactures electronic control systems, explicitly stating 'Our engineers provide pragmatic solutions' for vehicle systems.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They offer electrical assembly services backed by extensive testing protocols, indicating in-house electronic testing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The company offers electronic design, PCB design, PCB assembly, and explicit electronics testing services, indicating in-house engineering and testing needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The website content suggests they primarily sell and distribute finished consumer electronics, with no visible signs of in-house engineering, R&amp;D, or repair work.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: No connection could be made because the target machine actively refused it. (jebconet.com:443) (No connection could be made because the target machine actively refused it.)</x:t>
   </x:si>
   <x:si>
-    <x:t>Scrape failed: Request timed out after 15s</x:t>
-  </x:si>
-  <x:si>
     <x:t>They are a sales representative for electronic components with a staff of sales professionals, showing no evidence of in-house engineering or test functions.</x:t>
   </x:si>
   <x:si>
     <x:t>They provide remanufacturing and repair solutions for automotive and consumer electronics, which requires in-house diagnostics and testing.</x:t>
   </x:si>
   <x:si>
-    <x:t>They provide digital optical inspection systems used in the electronics industry, but there is no clear evidence of their own in-house electronic hardware engineering or test function.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Kelco Industries designs and manufactures custom-engineered electronic components and assemblies, with in-house engineering expertise and dedicated testing labs.</x:t>
+    <x:t>Kelco Industries performs in-house engineering, prototyping, and dedicated testing of custom-engineered electronic components like solenoids, relays, and switches.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They provide digital inspection systems used in electronics manufacturing, but the text does not indicate their own in-house electronic engineering, R&amp;D, or repair needs.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unigen is a global leader in the design and manufacture of OEM electronic products and offers comprehensive EMS capabilities including design, engineering, prototyping, assembly, and test services.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design, build, and debug custom automated systems for testing and inspection of automotive electronics, indicating in-house engineering and test functions.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prototek manufactures electronic assemblies, semiconductors, and micro-components, and their engineers provide design for manufacturability feedback, indicating a need for in-house testing expertise.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standex invents and produces electronic parts for critical industries like automotive and space, indicating in-house engineering and manufacturing that requires test equipment.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>They design and manufacture their own radar and laser detectors, indicating in-house engineering, R&amp;D, and ongoing testing of electronic hardware.</x:t>
   </x:si>
   <x:si>
     <x:t>Scrape failed: Network error: No such host is known. (flex.com:443) (No such host is known.)</x:t>
   </x:si>
   <x:si>
-    <x:t>They design, build, and debug custom automated systems for testing and inspection of automotive electronics, indicating in-house engineering and test functions.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unigen performs in-house design, engineering, prototyping, PCB assembly &amp; test, and offers "Test-as-a-Service" for complex electronic products.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They design and manufacture their own radar detectors, indicating in-house engineering, R&amp;D, and testing of electronic hardware.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>They provide manufacturing services for electronic assemblies, semiconductors, and micro-components, which implies in-house electronic testing and measurement.</x:t>
+    <x:t>Scrape failed: Network error: An error occurred while sending the request. (The response ended prematurely. (ResponseEnded))</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scrape failed: Request timed out after 45s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -7535,7 +7538,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N29" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -7667,7 +7670,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N32" s="0" t="s">
-        <x:v>1810</x:v>
+        <x:v>1809</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -7843,7 +7846,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N36" s="0" t="s">
-        <x:v>1813</x:v>
+        <x:v>1814</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -7884,7 +7887,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
-        <x:v>1814</x:v>
+        <x:v>1813</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -7972,7 +7975,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N39" s="0" t="s">
-        <x:v>1816</x:v>
+        <x:v>1817</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -8013,10 +8016,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N40" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1822</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -8145,7 +8148,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N43" s="0" t="s">
-        <x:v>1817</x:v>
+        <x:v>1816</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -8189,7 +8192,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>1822</x:v>
+        <x:v>1818</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -8274,7 +8277,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>1826</x:v>
+        <x:v>1823</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -8362,7 +8365,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N48" s="0" t="s">
-        <x:v>1823</x:v>
+        <x:v>1825</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -8403,7 +8406,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N49" s="0" t="s">
-        <x:v>1825</x:v>
+        <x:v>1826</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -8488,7 +8491,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>1828</x:v>
+        <x:v>1827</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -8532,7 +8535,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>1827</x:v>
+        <x:v>1829</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -8664,7 +8667,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N55" s="0" t="s">
-        <x:v>1833</x:v>
+        <x:v>1831</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -8705,7 +8708,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>1831</x:v>
+        <x:v>1833</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -8749,7 +8752,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N57" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -8793,7 +8796,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N58" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -8837,7 +8840,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N59" s="0" t="s">
-        <x:v>1843</x:v>
+        <x:v>1838</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -8963,7 +8966,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N62" s="0" t="s">
-        <x:v>1837</x:v>
+        <x:v>1834</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -9007,7 +9010,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N63" s="0" t="s">
-        <x:v>1834</x:v>
+        <x:v>1836</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -9048,7 +9051,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>1836</x:v>
+        <x:v>1835</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -9092,7 +9095,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N65" s="0" t="s">
-        <x:v>1835</x:v>
+        <x:v>1837</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -9136,7 +9139,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N66" s="0" t="s">
-        <x:v>1838</x:v>
+        <x:v>1839</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -9180,7 +9183,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N67" s="0" t="s">
-        <x:v>1841</x:v>
+        <x:v>1843</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -9224,7 +9227,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N68" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1840</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -9268,7 +9271,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N69" s="0" t="s">
-        <x:v>1840</x:v>
+        <x:v>1841</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -9312,7 +9315,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N70" s="0" t="s">
-        <x:v>1847</x:v>
+        <x:v>1848</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -9532,7 +9535,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N75" s="0" t="s">
-        <x:v>1848</x:v>
+        <x:v>1853</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:14" x14ac:dyDescent="0.25">
@@ -9620,7 +9623,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N77" s="0" t="s">
-        <x:v>1851</x:v>
+        <x:v>1847</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -9664,7 +9667,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N78" s="0" t="s">
-        <x:v>1853</x:v>
+        <x:v>1851</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -9708,7 +9711,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N79" s="0" t="s">
-        <x:v>1849</x:v>
+        <x:v>1852</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -9752,7 +9755,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N80" s="0" t="s">
-        <x:v>1852</x:v>
+        <x:v>1854</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -9796,7 +9799,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N81" s="0" t="s">
-        <x:v>1863</x:v>
+        <x:v>1856</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -9840,7 +9843,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N82" s="0" t="s">
-        <x:v>1854</x:v>
+        <x:v>1849</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -9969,7 +9972,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N85" s="0" t="s">
-        <x:v>1856</x:v>
+        <x:v>1857</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -10013,7 +10016,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N86" s="0" t="s">
-        <x:v>1858</x:v>
+        <x:v>1860</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -10095,7 +10098,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N88" s="0" t="s">
-        <x:v>1861</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -10136,7 +10139,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N89" s="0" t="s">
-        <x:v>1860</x:v>
+        <x:v>1858</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -10177,7 +10180,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N90" s="0" t="s">
-        <x:v>1857</x:v>
+        <x:v>1861</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -10259,7 +10262,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N92" s="0" t="s">
-        <x:v>1865</x:v>
+        <x:v>1863</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -10303,7 +10306,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N93" s="0" t="s">
-        <x:v>1866</x:v>
+        <x:v>1865</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -10391,7 +10394,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N95" s="0" t="s">
-        <x:v>1870</x:v>
+        <x:v>1866</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -10435,7 +10438,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N96" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1828</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -10479,7 +10482,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N97" s="0" t="s">
-        <x:v>1868</x:v>
+        <x:v>1867</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -10523,7 +10526,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N98" s="0" t="s">
-        <x:v>1873</x:v>
+        <x:v>1868</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -10611,7 +10614,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N100" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1871</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -10699,7 +10702,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N102" s="0" t="s">
-        <x:v>1872</x:v>
+        <x:v>1874</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -10743,7 +10746,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N103" s="0" t="s">
-        <x:v>1874</x:v>
+        <x:v>1873</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -10875,7 +10878,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N106" s="0" t="s">
-        <x:v>1871</x:v>
+        <x:v>1872</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:14" x14ac:dyDescent="0.25">
@@ -10919,7 +10922,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N107" s="0" t="s">
-        <x:v>1878</x:v>
+        <x:v>1877</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -10963,7 +10966,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N108" s="0" t="s">
-        <x:v>1877</x:v>
+        <x:v>1878</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -11051,7 +11054,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N110" s="0" t="s">
-        <x:v>1884</x:v>
+        <x:v>1882</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -11092,10 +11095,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M111" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N111" s="0" t="s">
-        <x:v>1881</x:v>
+        <x:v>1884</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:14" x14ac:dyDescent="0.25">
@@ -11183,7 +11186,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N113" s="0" t="s">
-        <x:v>1889</x:v>
+        <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -11227,7 +11230,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N114" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1881</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:14" x14ac:dyDescent="0.25">
@@ -11271,7 +11274,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N115" s="0" t="s">
-        <x:v>1891</x:v>
+        <x:v>1887</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:14" x14ac:dyDescent="0.25">
@@ -11315,7 +11318,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N116" s="0" t="s">
-        <x:v>1854</x:v>
+        <x:v>1849</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:14" x14ac:dyDescent="0.25">
@@ -11359,7 +11362,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N117" s="0" t="s">
-        <x:v>1890</x:v>
+        <x:v>1889</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:14" x14ac:dyDescent="0.25">
@@ -11488,7 +11491,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N120" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1891</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:14" x14ac:dyDescent="0.25">
@@ -11532,7 +11535,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N121" s="0" t="s">
-        <x:v>1887</x:v>
+        <x:v>1888</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:14" x14ac:dyDescent="0.25">
@@ -11614,7 +11617,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N123" s="0" t="s">
-        <x:v>1900</x:v>
+        <x:v>1899</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -11658,7 +11661,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N124" s="0" t="s">
-        <x:v>1895</x:v>
+        <x:v>1896</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -11699,7 +11702,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N125" s="0" t="s">
-        <x:v>1894</x:v>
+        <x:v>1893</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:14" x14ac:dyDescent="0.25">
@@ -11784,7 +11787,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N127" s="0" t="s">
-        <x:v>1903</x:v>
+        <x:v>1902</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:14" x14ac:dyDescent="0.25">
@@ -11828,7 +11831,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N128" s="0" t="s">
-        <x:v>1898</x:v>
+        <x:v>1904</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -11872,7 +11875,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N129" s="0" t="s">
-        <x:v>1897</x:v>
+        <x:v>1895</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:14" x14ac:dyDescent="0.25">
@@ -11916,7 +11919,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N130" s="0" t="s">
-        <x:v>1899</x:v>
+        <x:v>1897</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:14" x14ac:dyDescent="0.25">
@@ -11960,7 +11963,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N131" s="0" t="s">
-        <x:v>1896</x:v>
+        <x:v>1898</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -12048,7 +12051,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N133" s="0" t="s">
-        <x:v>1893</x:v>
+        <x:v>1894</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:14" x14ac:dyDescent="0.25">
@@ -12092,7 +12095,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N134" s="0" t="s">
-        <x:v>1902</x:v>
+        <x:v>1900</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:14" x14ac:dyDescent="0.25">
@@ -12133,10 +12136,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M135" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N135" s="0" t="s">
-        <x:v>1905</x:v>
+        <x:v>1903</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -12224,7 +12227,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N137" s="0" t="s">
-        <x:v>1908</x:v>
+        <x:v>1910</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:14" x14ac:dyDescent="0.25">
@@ -12265,10 +12268,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M138" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="N138" s="0" t="s">
-        <x:v>1910</x:v>
+        <x:v>1911</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:14" x14ac:dyDescent="0.25">
@@ -12312,7 +12315,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N139" s="0" t="s">
-        <x:v>1912</x:v>
+        <x:v>1907</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -12353,10 +12356,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M140" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N140" s="0" t="s">
-        <x:v>1916</x:v>
+        <x:v>1973</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:14" x14ac:dyDescent="0.25">
@@ -12400,7 +12403,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N141" s="0" t="s">
-        <x:v>1904</x:v>
+        <x:v>1906</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:14" x14ac:dyDescent="0.25">
@@ -12441,10 +12444,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M142" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N142" s="0" t="s">
-        <x:v>1911</x:v>
+        <x:v>1915</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -12488,7 +12491,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N143" s="0" t="s">
-        <x:v>1907</x:v>
+        <x:v>1905</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:14" x14ac:dyDescent="0.25">
@@ -12532,7 +12535,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N144" s="0" t="s">
-        <x:v>1906</x:v>
+        <x:v>1908</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:14" x14ac:dyDescent="0.25">
@@ -12664,7 +12667,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N147" s="0" t="s">
-        <x:v>1921</x:v>
+        <x:v>1912</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:14" x14ac:dyDescent="0.25">
@@ -12708,7 +12711,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N148" s="0" t="s">
-        <x:v>1918</x:v>
+        <x:v>1917</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:14" x14ac:dyDescent="0.25">
@@ -12796,7 +12799,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N150" s="0" t="s">
-        <x:v>1919</x:v>
+        <x:v>1922</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:14" x14ac:dyDescent="0.25">
@@ -12840,7 +12843,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N151" s="0" t="s">
-        <x:v>1920</x:v>
+        <x:v>1918</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:14" x14ac:dyDescent="0.25">
@@ -12884,7 +12887,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N152" s="0" t="s">
-        <x:v>1923</x:v>
+        <x:v>1920</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:14" x14ac:dyDescent="0.25">
@@ -12928,7 +12931,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N153" s="0" t="s">
-        <x:v>1922</x:v>
+        <x:v>1921</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:14" x14ac:dyDescent="0.25">
@@ -12969,10 +12972,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M154" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N154" s="0" t="s">
-        <x:v>1932</x:v>
+        <x:v>1936</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:14" x14ac:dyDescent="0.25">
@@ -13016,7 +13019,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N155" s="0" t="s">
-        <x:v>1917</x:v>
+        <x:v>1919</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:14" x14ac:dyDescent="0.25">
@@ -13192,7 +13195,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N159" s="0" t="s">
-        <x:v>1854</x:v>
+        <x:v>1849</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:14" x14ac:dyDescent="0.25">
@@ -13236,7 +13239,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N160" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1923</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:14" x14ac:dyDescent="0.25">
@@ -13280,7 +13283,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N161" s="0" t="s">
-        <x:v>1915</x:v>
+        <x:v>1916</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:14" x14ac:dyDescent="0.25">
@@ -13324,7 +13327,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N162" s="0" t="s">
-        <x:v>1928</x:v>
+        <x:v>1927</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:14" x14ac:dyDescent="0.25">
@@ -13412,7 +13415,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N164" s="0" t="s">
-        <x:v>1927</x:v>
+        <x:v>1924</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:14" x14ac:dyDescent="0.25">
@@ -13500,7 +13503,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N166" s="0" t="s">
-        <x:v>1929</x:v>
+        <x:v>1930</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:14" x14ac:dyDescent="0.25">
@@ -13588,7 +13591,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N168" s="0" t="s">
-        <x:v>1933</x:v>
+        <x:v>1931</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:14" x14ac:dyDescent="0.25">
@@ -13632,7 +13635,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N169" s="0" t="s">
-        <x:v>1943</x:v>
+        <x:v>1934</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:14" x14ac:dyDescent="0.25">
@@ -13720,7 +13723,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N171" s="0" t="s">
-        <x:v>1930</x:v>
+        <x:v>1928</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:14" x14ac:dyDescent="0.25">
@@ -13764,7 +13767,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N172" s="0" t="s">
-        <x:v>1935</x:v>
+        <x:v>1933</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:14" x14ac:dyDescent="0.25">
@@ -13808,7 +13811,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N173" s="0" t="s">
-        <x:v>1931</x:v>
+        <x:v>1929</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:14" x14ac:dyDescent="0.25">
@@ -13852,7 +13855,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N174" s="0" t="s">
-        <x:v>1934</x:v>
+        <x:v>1932</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:14" x14ac:dyDescent="0.25">
@@ -13896,7 +13899,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N175" s="0" t="s">
-        <x:v>1939</x:v>
+        <x:v>1937</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:14" x14ac:dyDescent="0.25">
@@ -13940,7 +13943,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N176" s="0" t="s">
-        <x:v>1854</x:v>
+        <x:v>1849</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:14" x14ac:dyDescent="0.25">
@@ -14028,7 +14031,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N178" s="0" t="s">
-        <x:v>1936</x:v>
+        <x:v>1938</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:14" x14ac:dyDescent="0.25">
@@ -14116,7 +14119,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N180" s="0" t="s">
-        <x:v>1963</x:v>
+        <x:v>1972</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:14" x14ac:dyDescent="0.25">
@@ -14160,7 +14163,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N181" s="0" t="s">
-        <x:v>1940</x:v>
+        <x:v>1939</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:14" x14ac:dyDescent="0.25">
@@ -14248,7 +14251,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N183" s="0" t="s">
-        <x:v>1945</x:v>
+        <x:v>1943</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -14292,7 +14295,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N184" s="0" t="s">
-        <x:v>1937</x:v>
+        <x:v>1935</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:14" x14ac:dyDescent="0.25">
@@ -14336,7 +14339,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N185" s="0" t="s">
-        <x:v>1941</x:v>
+        <x:v>1942</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:14" x14ac:dyDescent="0.25">
@@ -14380,7 +14383,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N186" s="0" t="s">
-        <x:v>1942</x:v>
+        <x:v>1946</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -14424,7 +14427,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N187" s="0" t="s">
-        <x:v>1960</x:v>
+        <x:v>1940</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:14" x14ac:dyDescent="0.25">
@@ -14468,7 +14471,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N188" s="0" t="s">
-        <x:v>1938</x:v>
+        <x:v>1941</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:14" x14ac:dyDescent="0.25">
@@ -14600,7 +14603,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N191" s="0" t="s">
-        <x:v>1946</x:v>
+        <x:v>1947</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:14" x14ac:dyDescent="0.25">
@@ -14644,7 +14647,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N192" s="0" t="s">
-        <x:v>1949</x:v>
+        <x:v>1945</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:14" x14ac:dyDescent="0.25">
@@ -14688,7 +14691,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N193" s="0" t="s">
-        <x:v>1955</x:v>
+        <x:v>1949</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:14" x14ac:dyDescent="0.25">
@@ -14732,7 +14735,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N194" s="0" t="s">
-        <x:v>1947</x:v>
+        <x:v>1953</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:14" x14ac:dyDescent="0.25">
@@ -14776,7 +14779,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N195" s="0" t="s">
-        <x:v>1956</x:v>
+        <x:v>1952</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -14908,7 +14911,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N198" s="0" t="s">
-        <x:v>1952</x:v>
+        <x:v>1951</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:14" x14ac:dyDescent="0.25">
@@ -14996,7 +14999,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N200" s="0" t="s">
-        <x:v>1958</x:v>
+        <x:v>1955</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -15084,7 +15087,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N202" s="0" t="s">
-        <x:v>1953</x:v>
+        <x:v>1954</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:14" x14ac:dyDescent="0.25">
@@ -15172,7 +15175,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N204" s="0" t="s">
-        <x:v>1951</x:v>
+        <x:v>1950</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:14" x14ac:dyDescent="0.25">
@@ -15260,7 +15263,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N206" s="0" t="s">
-        <x:v>1950</x:v>
+        <x:v>1960</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:14" x14ac:dyDescent="0.25">
@@ -15304,7 +15307,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N207" s="0" t="s">
-        <x:v>1954</x:v>
+        <x:v>1958</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:14" x14ac:dyDescent="0.25">
@@ -15348,7 +15351,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N208" s="0" t="s">
-        <x:v>1957</x:v>
+        <x:v>1956</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:14" x14ac:dyDescent="0.25">
@@ -15392,7 +15395,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N209" s="0" t="s">
-        <x:v>1959</x:v>
+        <x:v>1957</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:14" x14ac:dyDescent="0.25">
@@ -15480,7 +15483,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N211" s="0" t="s">
-        <x:v>1961</x:v>
+        <x:v>1959</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:14" x14ac:dyDescent="0.25">
@@ -15568,7 +15571,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N213" s="0" t="s">
-        <x:v>1964</x:v>
+        <x:v>1962</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:14" x14ac:dyDescent="0.25">
@@ -15612,7 +15615,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="N214" s="0" t="s">
-        <x:v>1966</x:v>
+        <x:v>1965</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:14" x14ac:dyDescent="0.25">
@@ -15656,7 +15659,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N215" s="0" t="s">
-        <x:v>1965</x:v>
+        <x:v>1963</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:14" x14ac:dyDescent="0.25">
@@ -15700,7 +15703,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N216" s="0" t="s">
-        <x:v>1970</x:v>
+        <x:v>1966</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:14" x14ac:dyDescent="0.25">
@@ -15744,7 +15747,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N217" s="0" t="s">
-        <x:v>1967</x:v>
+        <x:v>1964</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:14" x14ac:dyDescent="0.25">
@@ -15788,7 +15791,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N218" s="0" t="s">
-        <x:v>1962</x:v>
+        <x:v>1961</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:14" x14ac:dyDescent="0.25">
@@ -15832,7 +15835,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N219" s="0" t="s">
-        <x:v>1972</x:v>
+        <x:v>1968</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:14" x14ac:dyDescent="0.25">
@@ -15873,10 +15876,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="M220" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="N220" s="0" t="s">
-        <x:v>1963</x:v>
+        <x:v>1969</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:14" x14ac:dyDescent="0.25">
@@ -15920,7 +15923,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="N221" s="0" t="s">
-        <x:v>1968</x:v>
+        <x:v>1971</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:14" x14ac:dyDescent="0.25">
@@ -15964,7 +15967,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N222" s="0" t="s">
-        <x:v>1971</x:v>
+        <x:v>1970</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:14" x14ac:dyDescent="0.25">
@@ -16008,7 +16011,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="N223" s="0" t="s">
-        <x:v>1969</x:v>
+        <x:v>1967</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
